--- a/docs/progress/显性目的进度_2026-10-20.xlsx
+++ b/docs/progress/显性目的进度_2026-10-20.xlsx
@@ -8565,7 +8565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J206"/>
+  <dimension ref="A1:J207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8700,16 +8700,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>64/74</t>
+          <t>65/75</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>KR 17/24 + 交付 47/50 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 17/24 + 交付 48/51 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
@@ -8846,7 +8846,7 @@
         <v>0.9118000000000001</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.8649</v>
+        <v>0.8667</v>
       </c>
     </row>
     <row r="13">
@@ -9798,26 +9798,26 @@
     </row>
     <row r="53">
       <c r="A53" s="17" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46315</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>D44</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
+          <t>V2 双面主控位流 0 违例, eram 196/280 (70%) 不用压 FIFO; 补 V2 双面仿真 两面各 311040 组 0 错; 主会话复验 9/0; 假设: V2 面 B 引脚沿用 V1 v3 + 2.5V; 风险: 面 B 1.2G 真余量约 0.08 ns</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 d22_reach/README.md</t>
+          <t>dr1v90 a53a88a</t>
         </is>
       </c>
     </row>
@@ -9825,24 +9825,24 @@
       <c r="A54" s="17" t="n">
         <v>46314</v>
       </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>D32</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
+          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>dr1v90</t>
+          <t>dr1v90 d22_reach/README.md</t>
         </is>
       </c>
     </row>
@@ -9850,9 +9850,9 @@
       <c r="A55" s="17" t="n">
         <v>46314</v>
       </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
+          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>progress/v0_accept/acc32_*.log</t>
+          <t>dr1v90</t>
         </is>
       </c>
     </row>
@@ -9875,24 +9875,24 @@
       <c r="A56" s="17" t="n">
         <v>46314</v>
       </c>
-      <c r="B56" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
+          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>progress/v0_accept/acc32_*.log</t>
         </is>
       </c>
     </row>
@@ -9900,24 +9900,24 @@
       <c r="A57" s="17" t="n">
         <v>46314</v>
       </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>补录</t>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>KR4.2</t>
+          <t>用户</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
+          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -9927,22 +9927,22 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>补录</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
+          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -9952,22 +9952,22 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
+          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 card03</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -9977,22 +9977,22 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
+          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 2b111f0</t>
+          <t>dr1v90 card03</t>
         </is>
       </c>
     </row>
@@ -10002,22 +10002,22 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
+          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
+          <t>dr1v90 2b111f0</t>
         </is>
       </c>
     </row>
@@ -10025,24 +10025,24 @@
       <c r="A62" s="17" t="n">
         <v>46314</v>
       </c>
-      <c r="B62" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
+          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
         </is>
       </c>
     </row>
@@ -10050,24 +10050,24 @@
       <c r="A63" s="17" t="n">
         <v>46314</v>
       </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
+          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 97a10cf</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -10077,22 +10077,22 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
+          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 7253608</t>
+          <t>dr1v90 97a10cf</t>
         </is>
       </c>
     </row>
@@ -10100,24 +10100,24 @@
       <c r="A65" s="17" t="n">
         <v>46314</v>
       </c>
-      <c r="B65" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D34</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
+          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 7253608</t>
         </is>
       </c>
     </row>
@@ -10125,24 +10125,24 @@
       <c r="A66" s="17" t="n">
         <v>46314</v>
       </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
+          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 23474c7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -10157,17 +10157,17 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
+          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 f2584d9</t>
+          <t>dr1v90 23474c7</t>
         </is>
       </c>
     </row>
@@ -10182,17 +10182,17 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>D38</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
+          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ad201f9</t>
+          <t>dr1v90 f2584d9</t>
         </is>
       </c>
     </row>
@@ -10202,22 +10202,22 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>V1主控</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
+          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>本机构建</t>
+          <t>dr1v90 ad201f9</t>
         </is>
       </c>
     </row>
@@ -10232,17 +10232,17 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V1主控</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
+          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d39-comm b69f6d8</t>
+          <t>本机构建</t>
         </is>
       </c>
     </row>
@@ -10252,22 +10252,22 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>V2-7</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
+          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ff1846a</t>
+          <t>dr1v90 task/d39-comm b69f6d8</t>
         </is>
       </c>
     </row>
@@ -10282,17 +10282,17 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V2-7</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
+          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 3ef6b06</t>
+          <t>dr1v90 ff1846a</t>
         </is>
       </c>
     </row>
@@ -10302,22 +10302,22 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
+          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>progress/d29_coldboot</t>
+          <t>dr1v90 3ef6b06</t>
         </is>
       </c>
     </row>
@@ -10325,24 +10325,24 @@
       <c r="A74" s="17" t="n">
         <v>46314</v>
       </c>
-      <c r="B74" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>D11;D39</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
+          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>用户 10-19</t>
+          <t>progress/d29_coldboot</t>
         </is>
       </c>
     </row>
@@ -10350,24 +10350,24 @@
       <c r="A75" s="17" t="n">
         <v>46314</v>
       </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D11;D39</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
+          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6333eb5</t>
+          <t>用户 10-19</t>
         </is>
       </c>
     </row>
@@ -10382,67 +10382,67 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>D42;D43</t>
+          <t>D41</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
+          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 8689db2 / 6e6d47b</t>
+          <t>dr1v90 6333eb5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="17" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D42;D43</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
+          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1017_03_24h</t>
+          <t>dr1v90 8689db2 / 6e6d47b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="17" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B78" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46313</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
+          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/SPEC.md</t>
+          <t>progress/soak_v0/1017_03_24h</t>
         </is>
       </c>
     </row>
@@ -10450,24 +10450,24 @@
       <c r="A79" s="17" t="n">
         <v>46312</v>
       </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>V2-5</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
+          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 v2_fmt/README.md</t>
+          <t>dr1v90 d27_link/SPEC.md</t>
         </is>
       </c>
     </row>
@@ -10482,17 +10482,17 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>D28b</t>
+          <t>V2-5</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
+          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/回板当天.md</t>
+          <t>dr1v90 v2_fmt/README.md</t>
         </is>
       </c>
     </row>
@@ -10500,24 +10500,24 @@
       <c r="A81" s="17" t="n">
         <v>46312</v>
       </c>
-      <c r="B81" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>进展</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>D27b</t>
+          <t>D28b</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
+          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/README.md</t>
+          <t>dr1v90 v1_bringup/回板当天.md</t>
         </is>
       </c>
     </row>
@@ -10525,24 +10525,24 @@
       <c r="A82" s="17" t="n">
         <v>46312</v>
       </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>V2-6</t>
+          <t>D27b</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
+          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 gw5a_bridge/p2/README.md</t>
+          <t>dr1v90 d27_link/README.md</t>
         </is>
       </c>
     </row>
@@ -10552,22 +10552,22 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>全套</t>
+          <t>V2-6</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
+          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ~/full_*.log</t>
+          <t>dr1v90 gw5a_bridge/p2/README.md</t>
         </is>
       </c>
     </row>
@@ -10577,22 +10577,22 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>修复</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>全套</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
+          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 slice/SPEC.md §13.2</t>
+          <t>dr1v90 ~/full_*.log</t>
         </is>
       </c>
     </row>
@@ -10602,22 +10602,22 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
+          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1016_wkend_24h</t>
+          <t>dr1v90 slice/SPEC.md §13.2</t>
         </is>
       </c>
     </row>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
@@ -10637,37 +10637,37 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
+          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1017_*.log</t>
+          <t>progress/soak_v0/1016_wkend_24h</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="17" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>部署</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
+          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>~/rv_d22c.board.log</t>
+          <t>progress/v0_accept/accept_1017_*.log</t>
         </is>
       </c>
     </row>
@@ -10675,9 +10675,9 @@
       <c r="A88" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B88" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
@@ -10687,12 +10687,12 @@
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
+          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d22c.board.log</t>
         </is>
       </c>
     </row>
@@ -10700,24 +10700,24 @@
       <c r="A89" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
+          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>~/rv_d21.board5.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -10725,9 +10725,9 @@
       <c r="A90" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B90" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
+          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d21.board5.log</t>
         </is>
       </c>
     </row>
@@ -10757,12 +10757,12 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
+          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
@@ -10775,9 +10775,9 @@
       <c r="A92" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
+          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>soak_runs/fps_A fps_B</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -10800,9 +10800,9 @@
       <c r="A93" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B93" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
+          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>soak_runs/fps_C</t>
+          <t>soak_runs/fps_A fps_B</t>
         </is>
       </c>
     </row>
@@ -10825,24 +10825,24 @@
       <c r="A94" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
+          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20d-ackrps db4ec93</t>
+          <t>soak_runs/fps_C</t>
         </is>
       </c>
     </row>
@@ -10857,17 +10857,17 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
+          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
+          <t>dr1v90 task/d20d-ackrps db4ec93</t>
         </is>
       </c>
     </row>
@@ -10877,22 +10877,22 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
+          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>soak_runs/fps_D</t>
+          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
         </is>
       </c>
     </row>
@@ -10900,9 +10900,9 @@
       <c r="A97" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
+          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>soak_runs/fps_D</t>
         </is>
       </c>
     </row>
@@ -10925,24 +10925,24 @@
       <c r="A98" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
+          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>~/rv_deploy.board.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -10950,24 +10950,24 @@
       <c r="A99" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B99" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
+          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_deploy.board.log</t>
         </is>
       </c>
     </row>
@@ -10975,24 +10975,24 @@
       <c r="A100" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>验收</t>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
+          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>progress/v0_accept/</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -11002,22 +11002,22 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>开工</t>
+          <t>验收</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>D20e/D23</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
+          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
+          <t>progress/v0_accept/</t>
         </is>
       </c>
     </row>
@@ -11025,24 +11025,24 @@
       <c r="A102" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B102" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>开工</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D20e/D23</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
+          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
         </is>
       </c>
     </row>
@@ -11050,24 +11050,24 @@
       <c r="A103" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B103" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
+          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -11082,12 +11082,12 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
+          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -11100,24 +11100,24 @@
       <c r="A105" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
+          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1016_d20e.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -11125,24 +11125,24 @@
       <c r="A106" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B106" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>KR7.3/D24</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
+          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>progress/v0_accept/accept_1016_d20e.log</t>
         </is>
       </c>
     </row>
@@ -11150,24 +11150,24 @@
       <c r="A107" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>KR7.3/D24</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
+          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>D:\card03</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -11175,24 +11175,24 @@
       <c r="A108" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B108" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>D25</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
+          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>D:\card03</t>
         </is>
       </c>
     </row>
@@ -11200,24 +11200,24 @@
       <c r="A109" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B109" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D25</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
+          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>D:\card03\cap_COM29.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -11232,17 +11232,17 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
+          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 d20d_ackrps d20c_fps</t>
+          <t>D:\card03\cap_COM29.log</t>
         </is>
       </c>
     </row>
@@ -11250,24 +11250,24 @@
       <c r="A111" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B111" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B111" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
+          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 d12_latency/RESULTS.md</t>
+          <t>dr1v90 d20d_ackrps d20c_fps</t>
         </is>
       </c>
     </row>
@@ -11282,17 +11282,17 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
+          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 d9_e2e/</t>
+          <t>dr1v90 d12_latency/RESULTS.md</t>
         </is>
       </c>
     </row>
@@ -11300,24 +11300,24 @@
       <c r="A113" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
+          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>D:\card03\boot03.log</t>
+          <t>dr1v90 d9_e2e/</t>
         </is>
       </c>
     </row>
@@ -11325,24 +11325,24 @@
       <c r="A114" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B114" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
+          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
+          <t>D:\card03\boot03.log</t>
         </is>
       </c>
     </row>
@@ -11350,24 +11350,24 @@
       <c r="A115" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>开工</t>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
+          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
+          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
         </is>
       </c>
     </row>
@@ -11377,22 +11377,22 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>方案</t>
+          <t>开工</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
+          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 d29_sdboot/PLAN.md</t>
+          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
         </is>
       </c>
     </row>
@@ -11400,24 +11400,24 @@
       <c r="A117" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B117" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>方案</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
+          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/</t>
+          <t>dr1v90 d29_sdboot/PLAN.md</t>
         </is>
       </c>
     </row>
@@ -11425,24 +11425,24 @@
       <c r="A118" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>修复</t>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
+          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
+          <t>dr1v90 v1_bringup/</t>
         </is>
       </c>
     </row>
@@ -11452,22 +11452,22 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>进展</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>V2-3</t>
+          <t>D30</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
+          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 v2_map/DESIGN.md</t>
+          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
         </is>
       </c>
     </row>
@@ -11477,47 +11477,47 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>评估</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>V2-3</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
+          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 d31_v1odd/REPORT.md</t>
+          <t>dr1v90 v2_map/DESIGN.md</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="17" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B121" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46311</v>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>评估</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D31</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
+          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>progress/soak_v0/report.md</t>
+          <t>dr1v90 d31_v1odd/REPORT.md</t>
         </is>
       </c>
     </row>
@@ -11525,24 +11525,24 @@
       <c r="A122" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>QoS</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
+          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>~/qos_runs</t>
+          <t>progress/soak_v0/report.md</t>
         </is>
       </c>
     </row>
@@ -11557,17 +11557,17 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>D16b</t>
+          <t>QoS</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
+          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16b-tile 7936b7e</t>
+          <t>~/qos_runs</t>
         </is>
       </c>
     </row>
@@ -11575,24 +11575,24 @@
       <c r="A124" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B124" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D16b</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
+          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>dr1v90 task/d16b-tile 7936b7e</t>
         </is>
       </c>
     </row>
@@ -11607,12 +11607,12 @@
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
+          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
@@ -11625,24 +11625,24 @@
       <c r="A126" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B126" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>V1/V2</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
+          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>budget/rpm_range_2026-10-15.md</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -11650,24 +11650,24 @@
       <c r="A127" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B127" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>V1/V2</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
+          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>progress/realspin_v0/</t>
+          <t>budget/rpm_range_2026-10-15.md</t>
         </is>
       </c>
     </row>
@@ -11675,19 +11675,19 @@
       <c r="A128" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B128" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
+          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
@@ -11700,24 +11700,24 @@
       <c r="A129" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B129" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
+          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20-smooth 83a5fd7</t>
+          <t>progress/realspin_v0/</t>
         </is>
       </c>
     </row>
@@ -11725,24 +11725,24 @@
       <c r="A130" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B130" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
+          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 e215176</t>
+          <t>dr1v90 task/d20-smooth 83a5fd7</t>
         </is>
       </c>
     </row>
@@ -11750,24 +11750,24 @@
       <c r="A131" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
+          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d19-halfrev 1beafa6</t>
+          <t>dr1v90 e215176</t>
         </is>
       </c>
     </row>
@@ -11782,17 +11782,17 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>D20b</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
+          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20b-sim 9081f62</t>
+          <t>dr1v90 task/d19-halfrev 1beafa6</t>
         </is>
       </c>
     </row>
@@ -11802,22 +11802,22 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D20b</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
+          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/merge-d19-d20 106364e</t>
+          <t>dr1v90 task/d20b-sim 9081f62</t>
         </is>
       </c>
     </row>
@@ -11825,24 +11825,24 @@
       <c r="A134" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B134" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>D19/D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
+          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/merge-d19-d20 106364e</t>
         </is>
       </c>
     </row>
@@ -11850,24 +11850,24 @@
       <c r="A135" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D19/D20</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
+          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband adeba44</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -11877,22 +11877,22 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>D20/D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
+          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>~/realspin/tcp</t>
+          <t>dr1v90 task/d21-nband adeba44</t>
         </is>
       </c>
     </row>
@@ -11900,24 +11900,24 @@
       <c r="A137" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B137" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D20/D22</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
+          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>~/realspin/tcp</t>
         </is>
       </c>
     </row>
@@ -11925,9 +11925,9 @@
       <c r="A138" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B138" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
@@ -11937,12 +11937,12 @@
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
+          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach ee4a55c</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -11957,17 +11957,17 @@
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
+          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20c-fps 338eaaf</t>
+          <t>dr1v90 task/d22-reach ee4a55c</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>复验</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
+          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>~/rv_d20c.v.log</t>
+          <t>dr1v90 task/d20c-fps 338eaaf</t>
         </is>
       </c>
     </row>
@@ -12002,22 +12002,22 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>复验</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
+          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d8-cosim 85dfe51</t>
+          <t>~/rv_d20c.v.log</t>
         </is>
       </c>
     </row>
@@ -12025,9 +12025,9 @@
       <c r="A142" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B142" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
+          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/d8-cosim 85dfe51</t>
         </is>
       </c>
     </row>
@@ -12050,24 +12050,24 @@
       <c r="A143" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>D22/D20</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
+          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>soak_runs/netdiag_1015_1814</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -12075,24 +12075,24 @@
       <c r="A144" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B144" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22/D20</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
+          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>~/rv_d21.board.log</t>
+          <t>soak_runs/netdiag_1015_1814</t>
         </is>
       </c>
     </row>
@@ -12107,17 +12107,17 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
+          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach</t>
+          <t>~/rv_d21.board.log</t>
         </is>
       </c>
     </row>
@@ -12137,7 +12137,7 @@
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
+          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
@@ -12150,9 +12150,9 @@
       <c r="A147" s="17" t="n">
         <v>46310</v>
       </c>
-      <c r="B147" s="6" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B147" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
+          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr">
         <is>
-          <t>~/rv_d22.board2.log</t>
+          <t>dr1v90 task/d22-reach</t>
         </is>
       </c>
     </row>
@@ -12177,22 +12177,22 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
+          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr">
         <is>
-          <t>~/d21b_forensic.log</t>
+          <t>~/rv_d22.board2.log</t>
         </is>
       </c>
     </row>
@@ -12207,17 +12207,17 @@
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
+          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach 0d1da09</t>
+          <t>~/d21b_forensic.log</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
+          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>~/rv_d22b.board.log</t>
+          <t>dr1v90 task/d22-reach 0d1da09</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
@@ -12262,12 +12262,12 @@
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
+          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach e438a12</t>
+          <t>~/rv_d22b.board.log</t>
         </is>
       </c>
     </row>
@@ -12277,47 +12277,47 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
+          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband 084bba3</t>
+          <t>dr1v90 task/d22-reach e438a12</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="17" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B153" s="11" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>dr1v90 task/d21-nband 084bba3</t>
         </is>
       </c>
     </row>
@@ -12325,24 +12325,24 @@
       <c r="A154" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B154" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -12350,24 +12350,24 @@
       <c r="A155" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B155" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B155" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
@@ -12400,24 +12400,24 @@
       <c r="A157" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B157" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B157" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -12425,24 +12425,24 @@
       <c r="A158" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B158" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B158" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -12450,9 +12450,9 @@
       <c r="A159" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B159" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B159" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
@@ -12462,12 +12462,12 @@
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -12475,9 +12475,9 @@
       <c r="A160" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B160" s="11" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B160" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -12500,24 +12500,24 @@
       <c r="A161" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B161" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -12525,24 +12525,24 @@
       <c r="A162" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B162" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B162" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -12550,24 +12550,24 @@
       <c r="A163" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B163" s="19" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B163" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -12575,24 +12575,24 @@
       <c r="A164" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B164" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B164" s="19" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -12600,9 +12600,9 @@
       <c r="A165" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B165" s="19" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B165" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C165" s="7" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -12625,24 +12625,24 @@
       <c r="A166" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B166" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B166" s="19" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -12650,9 +12650,9 @@
       <c r="A167" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B167" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B167" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C167" s="7" t="inlineStr">
@@ -12662,12 +12662,12 @@
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -12675,24 +12675,24 @@
       <c r="A168" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B168" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B168" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -12700,24 +12700,24 @@
       <c r="A169" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B169" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B169" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -12725,24 +12725,24 @@
       <c r="A170" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B170" s="6" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B170" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
@@ -12750,24 +12750,24 @@
       <c r="A171" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B171" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
@@ -12775,24 +12775,24 @@
       <c r="A172" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B172" s="6" t="inlineStr">
-        <is>
-          <t>开始</t>
+      <c r="B172" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E172" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -12800,24 +12800,24 @@
       <c r="A173" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B173" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
@@ -12825,49 +12825,49 @@
       <c r="A174" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B174" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B174" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C174" s="7" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B175" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B175" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C175" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -12882,17 +12882,17 @@
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E176" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -12907,17 +12907,17 @@
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -12925,9 +12925,9 @@
       <c r="A178" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B178" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B178" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C178" s="7" t="inlineStr">
@@ -12937,12 +12937,12 @@
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -12950,9 +12950,9 @@
       <c r="A179" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B179" s="11" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B179" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C179" s="7" t="inlineStr">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -12975,24 +12975,24 @@
       <c r="A180" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B180" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B180" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E180" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -13000,9 +13000,9 @@
       <c r="A181" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B181" s="11" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B181" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C181" s="7" t="inlineStr">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -13032,17 +13032,17 @@
       </c>
       <c r="C182" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E182" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -13050,9 +13050,9 @@
       <c r="A183" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B183" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B183" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C183" s="7" t="inlineStr">
@@ -13062,12 +13062,12 @@
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E183" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E184" s="7" t="inlineStr">
@@ -13100,24 +13100,24 @@
       <c r="A185" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B185" s="11" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B185" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C185" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -13125,24 +13125,24 @@
       <c r="A186" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B186" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B186" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C186" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E186" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -13150,24 +13150,24 @@
       <c r="A187" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B187" s="11" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B187" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C187" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E187" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -13182,17 +13182,17 @@
       </c>
       <c r="C188" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E188" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -13200,19 +13200,19 @@
       <c r="A189" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B189" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C189" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E189" s="7" t="inlineStr">
@@ -13225,9 +13225,9 @@
       <c r="A190" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B190" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B190" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C190" s="7" t="inlineStr">
@@ -13237,12 +13237,12 @@
       </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E190" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -13250,24 +13250,24 @@
       <c r="A191" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B191" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B191" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E191" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -13275,9 +13275,9 @@
       <c r="A192" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B192" s="19" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B192" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C192" s="7" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="D192" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E192" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -13300,9 +13300,9 @@
       <c r="A193" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B193" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B193" s="19" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
@@ -13312,12 +13312,12 @@
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E193" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -13325,24 +13325,24 @@
       <c r="A194" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B194" s="11" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B194" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C194" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E194" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -13350,24 +13350,24 @@
       <c r="A195" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B195" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B195" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C195" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E195" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -13380,15 +13380,19 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C196" s="7" t="inlineStr"/>
+      <c r="C196" s="7" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D196" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E196" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -13396,15 +13400,15 @@
       <c r="A197" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B197" s="19" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B197" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C197" s="7" t="inlineStr"/>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E197" s="7" t="inlineStr">
@@ -13417,20 +13421,20 @@
       <c r="A198" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B198" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B198" s="19" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C198" s="7" t="inlineStr"/>
       <c r="D198" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E198" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -13443,19 +13447,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C199" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="C199" s="7" t="inlineStr"/>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E199" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -13470,12 +13470,12 @@
       </c>
       <c r="C200" s="7" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E200" s="7" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="C201" s="7" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E201" s="7" t="inlineStr">
@@ -13520,12 +13520,12 @@
       </c>
       <c r="C202" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D202" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E202" s="7" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="C203" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E203" s="7" t="inlineStr">
@@ -13570,17 +13570,17 @@
       </c>
       <c r="C204" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D204" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E204" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -13588,24 +13588,24 @@
       <c r="A205" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B205" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B205" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
       <c r="E205" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
@@ -13613,18 +13613,43 @@
       <c r="A206" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B206" s="19" t="inlineStr">
+      <c r="B206" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B207" s="19" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C206" s="7" t="inlineStr"/>
-      <c r="D206" s="7" t="inlineStr">
+      <c r="C207" s="7" t="inlineStr"/>
+      <c r="D207" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E206" s="7" t="inlineStr">
+      <c r="E207" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -18367,7 +18392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -18411,7 +18436,7 @@
         <v>46307</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>5</v>
@@ -18425,7 +18450,7 @@
         <v>46308</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>7</v>
@@ -18439,7 +18464,7 @@
         <v>46309</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>8</v>
@@ -18453,7 +18478,7 @@
         <v>46310</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>12</v>
@@ -18467,7 +18492,7 @@
         <v>46311</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>20</v>
@@ -18481,7 +18506,7 @@
         <v>46312</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>28</v>
@@ -18495,7 +18520,7 @@
         <v>46313</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>28</v>
@@ -18509,7 +18534,7 @@
         <v>46314</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>32</v>
@@ -18523,13 +18548,13 @@
         <v>46315</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -18537,10 +18562,10 @@
         <v>46316</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" s="6" t="n"/>
     </row>
@@ -18549,10 +18574,10 @@
         <v>46317</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" s="6" t="n"/>
     </row>
@@ -18561,10 +18586,10 @@
         <v>46318</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" s="6" t="n"/>
     </row>
@@ -18573,10 +18598,10 @@
         <v>46319</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" s="6" t="n"/>
     </row>
@@ -20738,6 +20763,44 @@
       <c r="H80" s="7" t="inlineStr">
         <is>
           <t>dr1v90 6e6d47b (povnetd 1.3.1; net_robust 19/0 + selftest 22/0; 03 已部署)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>D44</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>V2 双面主控位流 (片上 RAM/时序评估)</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>2;3</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>2期</t>
+        </is>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F81" s="17" t="n">
+        <v>46315</v>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 a53a88a (0 违例; eram 70%; bin 55a2679b; 面 B 引脚沿用 V1 假设)</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-20.xlsx
+++ b/docs/progress/显性目的进度_2026-10-20.xlsx
@@ -8580,7 +8580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8694,7 +8694,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="49" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>② 数据处理</t>
@@ -8735,8 +8735,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>⚠ R5 2 期 DDR 带宽：16 bit 余量约 11%，32 bit 像素超限 — B 线 T2 板 32 bit DDR + PL 读口 ≥200 MHz/分端口
-⚠ R6 偶发慢读 133 µs &gt; 30 Hz 片窗 110 µs — D16 预取缓冲 + 降争用</t>
+          <t>⚠ R5 2 期 DDR 带宽：16 bit 余量约 11%，32 bit 像素超限 — B 线 T2 板 32 bit DDR + PL 读口 ≥200 MHz/分端口</t>
         </is>
       </c>
     </row>
@@ -8809,7 +8808,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>15/16</t>
+          <t>16/17</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -9539,7 +9538,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -10905,9 +10904,9 @@
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr"/>
-      <c r="G72" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>监控</t>
         </is>
       </c>
       <c r="H72" s="12" t="n">
@@ -13208,27 +13207,31 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D49</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr"/>
-      <c r="G129" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H129" s="12" t="n">
-        <v>46312</v>
+        <v>46315</v>
       </c>
       <c r="I129" s="4" t="inlineStr"/>
     </row>
@@ -13250,12 +13253,12 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
+          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr"/>
@@ -13265,7 +13268,7 @@
         </is>
       </c>
       <c r="H130" s="12" t="n">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="I130" s="4" t="inlineStr"/>
     </row>
@@ -13282,33 +13285,29 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
+          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr"/>
-      <c r="G131" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H131" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I131" s="4" t="inlineStr">
-        <is>
-          <t>T2 板留 eMMC、打胶</t>
-        </is>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="I131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -13318,7 +13317,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>开发环境</t>
+          <t>可靠性验证 (冷启动/长跑)</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -13328,24 +13327,65 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>D 盘 EIO（IP-guard 驱动）</t>
+          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr"/>
-      <c r="G132" s="8" t="inlineStr">
-        <is>
-          <t>监控</t>
+      <c r="G132" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H132" s="12" t="n">
         <v>46308</v>
       </c>
       <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>T2 板留 eMMC、打胶</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>④ 运维保障</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>开发环境</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>风险</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>D 盘 EIO（IP-guard 驱动）</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr"/>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>监控</t>
+        </is>
+      </c>
+      <c r="H133" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
         <is>
           <t>看门狗自动重挂 + 构建放 WSL 本地盘</t>
         </is>
@@ -13365,7 +13405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J207"/>
+  <dimension ref="A1:J208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13895,7 +13935,7 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>阶段出口清单 — V1 回板当天就绪  (已打勾 7/11；状态由关联项在当日是否完成/达标推出)</t>
+          <t>阶段出口清单 — V1 回板当天就绪  (已打勾 8/11；状态由关联项在当日是否完成/达标推出)</t>
         </is>
       </c>
     </row>
@@ -14121,9 +14161,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>⬜</t>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -14133,7 +14173,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>人工状态</t>
+          <t>D28 (1/1)</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -14398,28 +14438,28 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>监控</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
         <is>
           <t>偶发慢读 133 µs &gt; 30 Hz 片窗 110 µs</t>
         </is>
       </c>
-      <c r="D44" s="20" t="inlineStr">
+      <c r="D44" s="21" t="inlineStr">
         <is>
           <t>影响：偶发迟到掉片
 应对：D16 预取缓冲 + 降争用</t>
         </is>
       </c>
-      <c r="E44" s="20" t="inlineStr">
+      <c r="E44" s="21" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
@@ -14623,7 +14663,7 @@
     </row>
     <row r="54">
       <c r="A54" s="12" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
@@ -14632,17 +14672,17 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>D49</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
+          <t>看板按大功能重排: 顶部四块总览 (①8/8 ②11/11 ③19/22 ④15/16), 明细按大功能分组; 新增 categories.csv (新交付要补映射); 达成率改前后逐日一致。顺带: 回板就绪 ⑧ 关联 D28 置 ✅, R6 (慢读) 改监控 (D16 已兜底, 待 V2 上板)</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d22_reach/README.md</t>
+          <t>zynq_pov 254e998</t>
         </is>
       </c>
     </row>
@@ -14650,24 +14690,24 @@
       <c r="A55" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>D32</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
+          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>dr1v90</t>
+          <t>dr1v90 d22_reach/README.md</t>
         </is>
       </c>
     </row>
@@ -14675,9 +14715,9 @@
       <c r="A56" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -14687,12 +14727,12 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
+          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/acc32_*.log</t>
+          <t>dr1v90</t>
         </is>
       </c>
     </row>
@@ -14700,24 +14740,24 @@
       <c r="A57" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B57" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
+          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>progress/v0_accept/acc32_*.log</t>
         </is>
       </c>
     </row>
@@ -14725,24 +14765,24 @@
       <c r="A58" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>补录</t>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>KR4.2</t>
+          <t>用户</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
+          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -14752,22 +14792,22 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>补录</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
+          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -14777,22 +14817,22 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
+          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 card03</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -14802,22 +14842,22 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
+          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2b111f0</t>
+          <t>dr1v90 card03</t>
         </is>
       </c>
     </row>
@@ -14827,22 +14867,22 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
+          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
+          <t>dr1v90 2b111f0</t>
         </is>
       </c>
     </row>
@@ -14850,24 +14890,24 @@
       <c r="A63" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B63" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
+          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
         </is>
       </c>
     </row>
@@ -14875,24 +14915,24 @@
       <c r="A64" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
+          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 97a10cf</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -14902,22 +14942,22 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
+          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 7253608</t>
+          <t>dr1v90 97a10cf</t>
         </is>
       </c>
     </row>
@@ -14925,24 +14965,24 @@
       <c r="A66" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B66" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D34</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
+          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 7253608</t>
         </is>
       </c>
     </row>
@@ -14950,24 +14990,24 @@
       <c r="A67" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
+          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 23474c7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -14982,17 +15022,17 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
+          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 f2584d9</t>
+          <t>dr1v90 23474c7</t>
         </is>
       </c>
     </row>
@@ -15007,17 +15047,17 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>D38</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
+          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ad201f9</t>
+          <t>dr1v90 f2584d9</t>
         </is>
       </c>
     </row>
@@ -15027,22 +15067,22 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>V1主控</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
+          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>本机构建</t>
+          <t>dr1v90 ad201f9</t>
         </is>
       </c>
     </row>
@@ -15057,17 +15097,17 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V1主控</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
+          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d39-comm b69f6d8</t>
+          <t>本机构建</t>
         </is>
       </c>
     </row>
@@ -15077,22 +15117,22 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>V2-7</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
+          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ff1846a</t>
+          <t>dr1v90 task/d39-comm b69f6d8</t>
         </is>
       </c>
     </row>
@@ -15107,17 +15147,17 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V2-7</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
+          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3ef6b06</t>
+          <t>dr1v90 ff1846a</t>
         </is>
       </c>
     </row>
@@ -15127,22 +15167,22 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
+          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>progress/d29_coldboot</t>
+          <t>dr1v90 3ef6b06</t>
         </is>
       </c>
     </row>
@@ -15150,24 +15190,24 @@
       <c r="A75" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B75" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>D11;D39</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
+          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>用户 10-19</t>
+          <t>progress/d29_coldboot</t>
         </is>
       </c>
     </row>
@@ -15175,24 +15215,24 @@
       <c r="A76" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D11;D39</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
+          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6333eb5</t>
+          <t>用户 10-19</t>
         </is>
       </c>
     </row>
@@ -15207,67 +15247,67 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>D42;D43</t>
+          <t>D41</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
+          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 8689db2 / 6e6d47b</t>
+          <t>dr1v90 6333eb5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D42;D43</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
+          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1017_03_24h</t>
+          <t>dr1v90 8689db2 / 6e6d47b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46313</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
+          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/SPEC.md</t>
+          <t>progress/soak_v0/1017_03_24h</t>
         </is>
       </c>
     </row>
@@ -15275,24 +15315,24 @@
       <c r="A80" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>V2-5</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
+          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_fmt/README.md</t>
+          <t>dr1v90 d27_link/SPEC.md</t>
         </is>
       </c>
     </row>
@@ -15307,17 +15347,17 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>D28b</t>
+          <t>V2-5</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
+          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/回板当天.md</t>
+          <t>dr1v90 v2_fmt/README.md</t>
         </is>
       </c>
     </row>
@@ -15325,24 +15365,24 @@
       <c r="A82" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>进展</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>D27b</t>
+          <t>D28b</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
+          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/README.md</t>
+          <t>dr1v90 v1_bringup/回板当天.md</t>
         </is>
       </c>
     </row>
@@ -15350,24 +15390,24 @@
       <c r="A83" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>V2-6</t>
+          <t>D27b</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
+          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 gw5a_bridge/p2/README.md</t>
+          <t>dr1v90 d27_link/README.md</t>
         </is>
       </c>
     </row>
@@ -15377,22 +15417,22 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>全套</t>
+          <t>V2-6</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
+          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ~/full_*.log</t>
+          <t>dr1v90 gw5a_bridge/p2/README.md</t>
         </is>
       </c>
     </row>
@@ -15402,22 +15442,22 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>修复</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>全套</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
+          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 slice/SPEC.md §13.2</t>
+          <t>dr1v90 ~/full_*.log</t>
         </is>
       </c>
     </row>
@@ -15427,22 +15467,22 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
+          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1016_wkend_24h</t>
+          <t>dr1v90 slice/SPEC.md §13.2</t>
         </is>
       </c>
     </row>
@@ -15452,7 +15492,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -15462,37 +15502,37 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
+          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1017_*.log</t>
+          <t>progress/soak_v0/1016_wkend_24h</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>部署</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
+          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22c.board.log</t>
+          <t>progress/v0_accept/accept_1017_*.log</t>
         </is>
       </c>
     </row>
@@ -15500,9 +15540,9 @@
       <c r="A89" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -15512,12 +15552,12 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
+          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d22c.board.log</t>
         </is>
       </c>
     </row>
@@ -15525,24 +15565,24 @@
       <c r="A90" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
+          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board5.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15550,9 +15590,9 @@
       <c r="A91" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -15562,12 +15602,12 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
+          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d21.board5.log</t>
         </is>
       </c>
     </row>
@@ -15582,12 +15622,12 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
+          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -15600,9 +15640,9 @@
       <c r="A93" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -15612,12 +15652,12 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
+          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_A fps_B</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15625,9 +15665,9 @@
       <c r="A94" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -15637,12 +15677,12 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
+          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_C</t>
+          <t>soak_runs/fps_A fps_B</t>
         </is>
       </c>
     </row>
@@ -15650,24 +15690,24 @@
       <c r="A95" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
+          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20d-ackrps db4ec93</t>
+          <t>soak_runs/fps_C</t>
         </is>
       </c>
     </row>
@@ -15682,17 +15722,17 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
+          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
+          <t>dr1v90 task/d20d-ackrps db4ec93</t>
         </is>
       </c>
     </row>
@@ -15702,22 +15742,22 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
+          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_D</t>
+          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
         </is>
       </c>
     </row>
@@ -15725,9 +15765,9 @@
       <c r="A98" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -15737,12 +15777,12 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
+          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>soak_runs/fps_D</t>
         </is>
       </c>
     </row>
@@ -15750,24 +15790,24 @@
       <c r="A99" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
+          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>~/rv_deploy.board.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15775,24 +15815,24 @@
       <c r="A100" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
+          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_deploy.board.log</t>
         </is>
       </c>
     </row>
@@ -15800,24 +15840,24 @@
       <c r="A101" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>验收</t>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
+          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15827,22 +15867,22 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>开工</t>
+          <t>验收</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>D20e/D23</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
+          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
+          <t>progress/v0_accept/</t>
         </is>
       </c>
     </row>
@@ -15850,24 +15890,24 @@
       <c r="A103" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B103" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>开工</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D20e/D23</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
+          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
         </is>
       </c>
     </row>
@@ -15875,24 +15915,24 @@
       <c r="A104" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
+          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15907,12 +15947,12 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
+          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -15925,24 +15965,24 @@
       <c r="A106" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
+          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1016_d20e.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15950,24 +15990,24 @@
       <c r="A107" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>KR7.3/D24</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
+          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>progress/v0_accept/accept_1016_d20e.log</t>
         </is>
       </c>
     </row>
@@ -15975,24 +16015,24 @@
       <c r="A108" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>KR7.3/D24</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
+          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>D:\card03</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16000,24 +16040,24 @@
       <c r="A109" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>D25</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
+          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>D:\card03</t>
         </is>
       </c>
     </row>
@@ -16025,24 +16065,24 @@
       <c r="A110" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D25</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
+          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\cap_COM29.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16057,17 +16097,17 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
+          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20d_ackrps d20c_fps</t>
+          <t>D:\card03\cap_COM29.log</t>
         </is>
       </c>
     </row>
@@ -16075,24 +16115,24 @@
       <c r="A112" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
+          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d12_latency/RESULTS.md</t>
+          <t>dr1v90 d20d_ackrps d20c_fps</t>
         </is>
       </c>
     </row>
@@ -16107,17 +16147,17 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
+          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d9_e2e/</t>
+          <t>dr1v90 d12_latency/RESULTS.md</t>
         </is>
       </c>
     </row>
@@ -16125,24 +16165,24 @@
       <c r="A114" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
+          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\boot03.log</t>
+          <t>dr1v90 d9_e2e/</t>
         </is>
       </c>
     </row>
@@ -16150,24 +16190,24 @@
       <c r="A115" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
+          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
+          <t>D:\card03\boot03.log</t>
         </is>
       </c>
     </row>
@@ -16175,24 +16215,24 @@
       <c r="A116" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>开工</t>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
+          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
+          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
         </is>
       </c>
     </row>
@@ -16202,22 +16242,22 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>方案</t>
+          <t>开工</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
+          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d29_sdboot/PLAN.md</t>
+          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
         </is>
       </c>
     </row>
@@ -16225,24 +16265,24 @@
       <c r="A118" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>方案</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
+          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/</t>
+          <t>dr1v90 d29_sdboot/PLAN.md</t>
         </is>
       </c>
     </row>
@@ -16250,24 +16290,24 @@
       <c r="A119" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>修复</t>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
+          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
+          <t>dr1v90 v1_bringup/</t>
         </is>
       </c>
     </row>
@@ -16277,22 +16317,22 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>进展</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>V2-3</t>
+          <t>D30</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
+          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_map/DESIGN.md</t>
+          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
         </is>
       </c>
     </row>
@@ -16302,47 +16342,47 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>评估</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>V2-3</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
+          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d31_v1odd/REPORT.md</t>
+          <t>dr1v90 v2_map/DESIGN.md</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="12" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B122" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46311</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>评估</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D31</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
+          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/report.md</t>
+          <t>dr1v90 d31_v1odd/REPORT.md</t>
         </is>
       </c>
     </row>
@@ -16350,24 +16390,24 @@
       <c r="A123" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>QoS</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
+          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>~/qos_runs</t>
+          <t>progress/soak_v0/report.md</t>
         </is>
       </c>
     </row>
@@ -16382,17 +16422,17 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>D16b</t>
+          <t>QoS</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
+          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16b-tile 7936b7e</t>
+          <t>~/qos_runs</t>
         </is>
       </c>
     </row>
@@ -16400,24 +16440,24 @@
       <c r="A125" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B125" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D16b</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
+          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>dr1v90 task/d16b-tile 7936b7e</t>
         </is>
       </c>
     </row>
@@ -16432,12 +16472,12 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
+          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -16450,24 +16490,24 @@
       <c r="A127" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B127" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>V1/V2</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
+          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>budget/rpm_range_2026-10-15.md</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -16475,24 +16515,24 @@
       <c r="A128" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B128" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>V1/V2</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
+          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>progress/realspin_v0/</t>
+          <t>budget/rpm_range_2026-10-15.md</t>
         </is>
       </c>
     </row>
@@ -16500,19 +16540,19 @@
       <c r="A129" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B129" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
+          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -16525,24 +16565,24 @@
       <c r="A130" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
+          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20-smooth 83a5fd7</t>
+          <t>progress/realspin_v0/</t>
         </is>
       </c>
     </row>
@@ -16550,24 +16590,24 @@
       <c r="A131" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
+          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 e215176</t>
+          <t>dr1v90 task/d20-smooth 83a5fd7</t>
         </is>
       </c>
     </row>
@@ -16575,24 +16615,24 @@
       <c r="A132" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
+          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d19-halfrev 1beafa6</t>
+          <t>dr1v90 e215176</t>
         </is>
       </c>
     </row>
@@ -16607,17 +16647,17 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>D20b</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
+          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20b-sim 9081f62</t>
+          <t>dr1v90 task/d19-halfrev 1beafa6</t>
         </is>
       </c>
     </row>
@@ -16627,22 +16667,22 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D20b</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
+          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/merge-d19-d20 106364e</t>
+          <t>dr1v90 task/d20b-sim 9081f62</t>
         </is>
       </c>
     </row>
@@ -16650,24 +16690,24 @@
       <c r="A135" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B135" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>D19/D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
+          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/merge-d19-d20 106364e</t>
         </is>
       </c>
     </row>
@@ -16675,24 +16715,24 @@
       <c r="A136" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D19/D20</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
+          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband adeba44</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16702,22 +16742,22 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>D20/D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
+          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>~/realspin/tcp</t>
+          <t>dr1v90 task/d21-nband adeba44</t>
         </is>
       </c>
     </row>
@@ -16725,24 +16765,24 @@
       <c r="A138" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B138" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D20/D22</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
+          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>~/realspin/tcp</t>
         </is>
       </c>
     </row>
@@ -16750,9 +16790,9 @@
       <c r="A139" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B139" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -16762,12 +16802,12 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
+          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach ee4a55c</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -16782,17 +16822,17 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
+          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20c-fps 338eaaf</t>
+          <t>dr1v90 task/d22-reach ee4a55c</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16842,7 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>复验</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -16812,12 +16852,12 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
+          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d20c.v.log</t>
+          <t>dr1v90 task/d20c-fps 338eaaf</t>
         </is>
       </c>
     </row>
@@ -16827,22 +16867,22 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>复验</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
+          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d8-cosim 85dfe51</t>
+          <t>~/rv_d20c.v.log</t>
         </is>
       </c>
     </row>
@@ -16850,9 +16890,9 @@
       <c r="A143" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B143" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -16862,12 +16902,12 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
+          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/d8-cosim 85dfe51</t>
         </is>
       </c>
     </row>
@@ -16875,24 +16915,24 @@
       <c r="A144" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B144" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>D22/D20</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
+          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/netdiag_1015_1814</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16900,24 +16940,24 @@
       <c r="A145" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B145" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22/D20</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
+          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board.log</t>
+          <t>soak_runs/netdiag_1015_1814</t>
         </is>
       </c>
     </row>
@@ -16932,17 +16972,17 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
+          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach</t>
+          <t>~/rv_d21.board.log</t>
         </is>
       </c>
     </row>
@@ -16962,7 +17002,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
+          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -16975,9 +17015,9 @@
       <c r="A148" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B148" s="5" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -16987,12 +17027,12 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
+          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22.board2.log</t>
+          <t>dr1v90 task/d22-reach</t>
         </is>
       </c>
     </row>
@@ -17002,22 +17042,22 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
+          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>~/d21b_forensic.log</t>
+          <t>~/rv_d22.board2.log</t>
         </is>
       </c>
     </row>
@@ -17032,17 +17072,17 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
+          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach 0d1da09</t>
+          <t>~/d21b_forensic.log</t>
         </is>
       </c>
     </row>
@@ -17052,7 +17092,7 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -17062,12 +17102,12 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
+          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22b.board.log</t>
+          <t>dr1v90 task/d22-reach 0d1da09</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17117,7 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -17087,12 +17127,12 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
+          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach e438a12</t>
+          <t>~/rv_d22b.board.log</t>
         </is>
       </c>
     </row>
@@ -17102,47 +17142,47 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
+          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband 084bba3</t>
+          <t>dr1v90 task/d22-reach e438a12</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B154" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>dr1v90 task/d21-nband 084bba3</t>
         </is>
       </c>
     </row>
@@ -17150,24 +17190,24 @@
       <c r="A155" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B155" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -17175,24 +17215,24 @@
       <c r="A156" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B156" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B156" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -17212,7 +17252,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -17225,24 +17265,24 @@
       <c r="A158" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B158" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -17250,24 +17290,24 @@
       <c r="A159" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B159" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B159" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -17275,9 +17315,9 @@
       <c r="A160" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B160" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -17287,12 +17327,12 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -17300,9 +17340,9 @@
       <c r="A161" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B161" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B161" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -17312,12 +17352,12 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -17325,24 +17365,24 @@
       <c r="A162" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B162" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17350,24 +17390,24 @@
       <c r="A163" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B163" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B163" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -17375,24 +17415,24 @@
       <c r="A164" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B164" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B164" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -17400,24 +17440,24 @@
       <c r="A165" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B165" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B165" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17425,9 +17465,9 @@
       <c r="A166" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B166" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -17437,12 +17477,12 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -17450,24 +17490,24 @@
       <c r="A167" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B167" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B167" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -17475,9 +17515,9 @@
       <c r="A168" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B168" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B168" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -17487,12 +17527,12 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -17500,24 +17540,24 @@
       <c r="A169" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B169" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -17525,24 +17565,24 @@
       <c r="A170" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B170" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B170" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -17550,24 +17590,24 @@
       <c r="A171" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B171" s="5" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
@@ -17575,24 +17615,24 @@
       <c r="A172" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B172" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
@@ -17600,24 +17640,24 @@
       <c r="A173" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B173" s="5" t="inlineStr">
-        <is>
-          <t>开始</t>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -17625,24 +17665,24 @@
       <c r="A174" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B174" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
@@ -17650,49 +17690,49 @@
       <c r="A175" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B175" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B175" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B176" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B176" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -17707,17 +17747,17 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -17732,17 +17772,17 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -17750,9 +17790,9 @@
       <c r="A179" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B179" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -17762,12 +17802,12 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -17775,9 +17815,9 @@
       <c r="A180" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B180" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
@@ -17787,12 +17827,12 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -17800,24 +17840,24 @@
       <c r="A181" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B181" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -17825,9 +17865,9 @@
       <c r="A182" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B182" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B182" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -17837,12 +17877,12 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -17857,17 +17897,17 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -17875,9 +17915,9 @@
       <c r="A184" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B184" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -17887,12 +17927,12 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -17912,7 +17952,7 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
@@ -17925,24 +17965,24 @@
       <c r="A186" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B186" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B186" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -17950,24 +17990,24 @@
       <c r="A187" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B187" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -17975,24 +18015,24 @@
       <c r="A188" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B188" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B188" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18007,17 +18047,17 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -18025,19 +18065,19 @@
       <c r="A190" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B190" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
@@ -18050,9 +18090,9 @@
       <c r="A191" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B191" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B191" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -18062,12 +18102,12 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18075,24 +18115,24 @@
       <c r="A192" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B192" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B192" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -18100,9 +18140,9 @@
       <c r="A193" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B193" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B193" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -18112,12 +18152,12 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18125,9 +18165,9 @@
       <c r="A194" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B194" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B194" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -18137,12 +18177,12 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -18150,24 +18190,24 @@
       <c r="A195" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B195" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B195" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18175,24 +18215,24 @@
       <c r="A196" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B196" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -18205,15 +18245,19 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C197" s="4" t="inlineStr"/>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18221,15 +18265,15 @@
       <c r="A198" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B198" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B198" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr"/>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
@@ -18242,20 +18286,20 @@
       <c r="A199" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B199" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B199" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr"/>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -18268,19 +18312,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C200" s="4" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="C200" s="4" t="inlineStr"/>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -18295,12 +18335,12 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
@@ -18320,12 +18360,12 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
@@ -18345,12 +18385,12 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
@@ -18370,12 +18410,12 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
@@ -18395,17 +18435,17 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18413,24 +18453,24 @@
       <c r="A206" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B206" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B206" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
@@ -18438,18 +18478,43 @@
       <c r="A207" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B207" s="23" t="inlineStr">
+      <c r="B207" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B208" s="23" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C207" s="4" t="inlineStr"/>
-      <c r="D207" s="4" t="inlineStr">
+      <c r="C208" s="4" t="inlineStr"/>
+      <c r="D208" s="4" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E207" s="4" t="inlineStr">
+      <c r="E208" s="4" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -23192,7 +23257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23236,7 +23301,7 @@
         <v>46307</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>5</v>
@@ -23250,7 +23315,7 @@
         <v>46308</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>7</v>
@@ -23264,7 +23329,7 @@
         <v>46309</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>8</v>
@@ -23278,7 +23343,7 @@
         <v>46310</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>12</v>
@@ -23292,7 +23357,7 @@
         <v>46311</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>20</v>
@@ -23306,7 +23371,7 @@
         <v>46312</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>28</v>
@@ -23320,7 +23385,7 @@
         <v>46313</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>28</v>
@@ -23334,7 +23399,7 @@
         <v>46314</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>32</v>
@@ -23348,13 +23413,13 @@
         <v>46315</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -23362,10 +23427,10 @@
         <v>46316</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" s="5" t="n"/>
     </row>
@@ -23374,10 +23439,10 @@
         <v>46317</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" s="5" t="n"/>
     </row>
@@ -23386,10 +23451,10 @@
         <v>46318</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" s="5" t="n"/>
     </row>
@@ -23398,10 +23463,10 @@
         <v>46319</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" s="5" t="n"/>
     </row>
@@ -25601,6 +25666,44 @@
       <c r="H81" s="4" t="inlineStr">
         <is>
           <t>dr1v90 a53a88a (0 违例; eram 70%; bin 55a2679b; 面 B 引脚沿用 V1 假设)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>D49</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F82" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>zynq_pov 254e998 (categories.csv; 达成率前后逐日一致)</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-20.xlsx
+++ b/docs/progress/显性目的进度_2026-10-20.xlsx
@@ -8580,7 +8580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/18</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -12450,29 +12450,37 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>KR8.1</t>
+          <t>D47</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>上电到 0° 片亮起 (停转) (最新 12.4 s)</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr"/>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>系统从 QSPI 加载 (去 TF/eMMC 准备; 03 板试)</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 加分</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H110" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I110" s="4" t="inlineStr"/>
+        <v>46315</v>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>T2 板 QSPI 选 64MiB / 厂商驱动提速</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12492,22 +12500,22 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>KR8.4</t>
+          <t>KR8.1</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>上电到转稳全亮 (最新 26 s)</t>
+          <t>上电到 0° 片亮起 (停转) (最新 12.4 s)</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>V0— V1— V2—</t>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H111" s="12" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="I111" s="4" t="inlineStr"/>
     </row>
@@ -12519,32 +12527,28 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>联网/找板/自愈</t>
+          <t>开机即用</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>KR8.4</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>开机自连 WiFi</t>
-        </is>
-      </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>上电到转稳全亮 (最新 26 s)</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>V0— V1— V2—</t>
         </is>
       </c>
       <c r="H112" s="12" t="n">
@@ -12570,12 +12574,12 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS)</t>
+          <t>开机自连 WiFi</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
@@ -12589,7 +12593,7 @@
         </is>
       </c>
       <c r="H113" s="12" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="I113" s="4" t="inlineStr"/>
     </row>
@@ -12611,12 +12615,12 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 (服务监护/看门狗/兜底热点/povnetd 1.2)</t>
+          <t>按名字找板 (mDNS)</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -12630,7 +12634,7 @@
         </is>
       </c>
       <c r="H114" s="12" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="I114" s="4" t="inlineStr"/>
     </row>
@@ -12652,12 +12656,12 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复 ≤30 s (03 长跑断 155 s)</t>
+          <t>不插串口永远连得上 (服务监护/看门狗/兜底热点/povnetd 1.2)</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
@@ -12671,7 +12675,7 @@
         </is>
       </c>
       <c r="H115" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I115" s="4" t="inlineStr"/>
     </row>
@@ -12693,12 +12697,12 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>D43</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>povnetd 1.3 网络自愈回归修复</t>
+          <t>WiFi 断线恢复 ≤30 s (03 长跑断 155 s)</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -12729,27 +12733,31 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>KR8.2</t>
+          <t>D43</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>按名字找到板子 (最新 19.8 s)</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr"/>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>povnetd 1.3 网络自愈回归修复</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 必须</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H117" s="12" t="n">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="I117" s="4" t="inlineStr"/>
     </row>
@@ -12761,32 +12769,28 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>远程运维/升级 (含 JTAG 灌桥)</t>
+          <t>联网/找板/自愈</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR8.2</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>转子运维 (netguard-lite / 遥测 / 远程升级)</t>
-        </is>
-      </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G118" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>按名字找到板子 (最新 19.8 s)</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H118" s="12" t="n">
@@ -12812,17 +12816,17 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>主控经 JTAG 给桥灌位流 (V1 远程升级软件)</t>
+          <t>转子运维 (netguard-lite / 遥测 / 远程升级)</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
@@ -12831,7 +12835,7 @@
         </is>
       </c>
       <c r="H119" s="12" t="n">
-        <v>46314</v>
+        <v>46309</v>
       </c>
       <c r="I119" s="4" t="inlineStr"/>
     </row>
@@ -12853,17 +12857,17 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>D42</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>03 板软件跟进主线</t>
+          <t>主控经 JTAG 给桥灌位流 (V1 远程升级软件)</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>V0 · 加分</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
@@ -12889,27 +12893,31 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>KR8.3</t>
+          <t>D42</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>需要串口 (1=需要) (最新 0 是/否)</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr"/>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>03 板软件跟进主线</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H121" s="12" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="I121" s="4" t="inlineStr"/>
     </row>
@@ -12931,12 +12939,12 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>KR8.3</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用) (最新 1 是/否)</t>
+          <t>需要串口 (1=需要) (最新 0 是/否)</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr"/>
@@ -12946,7 +12954,7 @@
         </is>
       </c>
       <c r="H122" s="12" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="I122" s="4" t="inlineStr"/>
     </row>
@@ -12968,12 +12976,12 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>KR9.2</t>
+          <t>KR9.1</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>远程升级失败自动回滚 (1=有) (最新 1 是/否)</t>
+          <t>转子遥测可用 (1=可用) (最新 1 是/否)</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr"/>
@@ -12995,40 +13003,34 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>主控↔桥通信</t>
+          <t>远程运维/升级 (含 JTAG 灌桥)</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>KR9.2</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>C1 台架彩排 + 1.2G 误码测试</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>V1准备 · 加分</t>
-        </is>
-      </c>
-      <c r="G124" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H124" s="12" t="n"/>
-      <c r="I124" s="4" t="inlineStr">
-        <is>
-          <t>不做 (用户 10-19 定), 由 D39 到板 comm_check 代替</t>
-        </is>
-      </c>
+          <t>远程升级失败自动回滚 (1=有) (最新 1 是/否)</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -13048,28 +13050,30 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信全功能 (配置/状态/错误恢复/升级)</t>
+          <t>C1 台架彩排 + 1.2G 误码测试</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
-        </is>
-      </c>
-      <c r="G125" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H125" s="12" t="n">
-        <v>46312</v>
-      </c>
-      <c r="I125" s="4" t="inlineStr"/>
+          <t>V1准备 · 加分</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="n"/>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>不做 (用户 10-19 定), 由 D39 到板 comm_check 代替</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -13089,12 +13093,12 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 + PRBS 位流</t>
+          <t>SoC↔桥通信全功能 (配置/状态/错误恢复/升级)</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -13108,7 +13112,7 @@
         </is>
       </c>
       <c r="H126" s="12" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="I126" s="4" t="inlineStr"/>
     </row>
@@ -13120,7 +13124,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>可靠性验证 (冷启动/长跑)</t>
+          <t>主控↔桥通信</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
@@ -13130,17 +13134,17 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>V0A</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>V0 重启验收 (不插串口: 找回/守护/开机默认/WiFi/推流/稳定 6 项)</t>
+          <t>SoC↔桥通信专项验证包 + PRBS 位流</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>V0 · 必须</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
@@ -13149,7 +13153,7 @@
         </is>
       </c>
       <c r="H127" s="12" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="I127" s="4" t="inlineStr"/>
     </row>
@@ -13171,12 +13175,12 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>V0A</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>冷启动认不到 TF 卡 (03 停在 u-boot)</t>
+          <t>V0 重启验收 (不插串口: 找回/守护/开机默认/WiFi/推流/稳定 6 项)</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
@@ -13190,7 +13194,7 @@
         </is>
       </c>
       <c r="H128" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I128" s="4" t="inlineStr"/>
     </row>
@@ -13212,17 +13216,17 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>D49</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+          <t>冷启动认不到 TF 卡 (03 停在 u-boot)</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>V0 · 加分</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
@@ -13231,7 +13235,7 @@
         </is>
       </c>
       <c r="H129" s="12" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I129" s="4" t="inlineStr"/>
     </row>
@@ -13248,27 +13252,31 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D49</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr"/>
-      <c r="G130" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H130" s="12" t="n">
-        <v>46312</v>
+        <v>46315</v>
       </c>
       <c r="I130" s="4" t="inlineStr"/>
     </row>
@@ -13290,12 +13298,12 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
+          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr"/>
@@ -13305,7 +13313,7 @@
         </is>
       </c>
       <c r="H131" s="12" t="n">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="I131" s="4" t="inlineStr"/>
     </row>
@@ -13322,33 +13330,29 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
+          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr"/>
-      <c r="G132" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H132" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I132" s="4" t="inlineStr">
-        <is>
-          <t>T2 板留 eMMC、打胶</t>
-        </is>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="I132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -13358,7 +13362,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>开发环境</t>
+          <t>可靠性验证 (冷启动/长跑)</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
@@ -13368,24 +13372,65 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>D 盘 EIO（IP-guard 驱动）</t>
+          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr"/>
-      <c r="G133" s="8" t="inlineStr">
-        <is>
-          <t>监控</t>
+      <c r="G133" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H133" s="12" t="n">
         <v>46308</v>
       </c>
       <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>T2 板留 eMMC、打胶</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>④ 运维保障</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>开发环境</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>风险</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>D 盘 EIO（IP-guard 驱动）</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr"/>
+      <c r="G134" s="8" t="inlineStr">
+        <is>
+          <t>监控</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
         <is>
           <t>看门狗自动重挂 + 构建放 WSL 本地盘</t>
         </is>
@@ -13405,7 +13450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J208"/>
+  <dimension ref="A1:J209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -14688,26 +14733,26 @@
     </row>
     <row r="55">
       <c r="A55" s="12" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46315</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>D47</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
+          <t>03 从 QSPI 加载系统 5/5 + 坏镜像/空片回退 TF 通过; 单份 29/32 MiB 够, A/B 要 64 MiB; QSPI 读仅 2.3 MB/s 开机慢 7.6 s; Linux 驱动写 QSPI 静默失效 (待查/找厂商); 03 已回 TF 原路径</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d22_reach/README.md</t>
+          <t>dr1v90 f3f384c</t>
         </is>
       </c>
     </row>
@@ -14715,24 +14760,24 @@
       <c r="A56" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>D32</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
+          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>dr1v90</t>
+          <t>dr1v90 d22_reach/README.md</t>
         </is>
       </c>
     </row>
@@ -14740,9 +14785,9 @@
       <c r="A57" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -14752,12 +14797,12 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
+          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/acc32_*.log</t>
+          <t>dr1v90</t>
         </is>
       </c>
     </row>
@@ -14765,24 +14810,24 @@
       <c r="A58" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B58" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
+          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>progress/v0_accept/acc32_*.log</t>
         </is>
       </c>
     </row>
@@ -14790,24 +14835,24 @@
       <c r="A59" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>补录</t>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>KR4.2</t>
+          <t>用户</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
+          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -14817,22 +14862,22 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>补录</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
+          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -14842,22 +14887,22 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
+          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 card03</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -14867,22 +14912,22 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
+          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2b111f0</t>
+          <t>dr1v90 card03</t>
         </is>
       </c>
     </row>
@@ -14892,22 +14937,22 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
+          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
+          <t>dr1v90 2b111f0</t>
         </is>
       </c>
     </row>
@@ -14915,24 +14960,24 @@
       <c r="A64" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B64" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
+          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
         </is>
       </c>
     </row>
@@ -14940,24 +14985,24 @@
       <c r="A65" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
+          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 97a10cf</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -14967,22 +15012,22 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
+          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 7253608</t>
+          <t>dr1v90 97a10cf</t>
         </is>
       </c>
     </row>
@@ -14990,24 +15035,24 @@
       <c r="A67" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B67" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D34</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
+          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 7253608</t>
         </is>
       </c>
     </row>
@@ -15015,24 +15060,24 @@
       <c r="A68" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
+          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 23474c7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15047,17 +15092,17 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
+          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 f2584d9</t>
+          <t>dr1v90 23474c7</t>
         </is>
       </c>
     </row>
@@ -15072,17 +15117,17 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>D38</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
+          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ad201f9</t>
+          <t>dr1v90 f2584d9</t>
         </is>
       </c>
     </row>
@@ -15092,22 +15137,22 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>V1主控</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
+          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>本机构建</t>
+          <t>dr1v90 ad201f9</t>
         </is>
       </c>
     </row>
@@ -15122,17 +15167,17 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V1主控</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
+          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d39-comm b69f6d8</t>
+          <t>本机构建</t>
         </is>
       </c>
     </row>
@@ -15142,22 +15187,22 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>V2-7</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
+          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ff1846a</t>
+          <t>dr1v90 task/d39-comm b69f6d8</t>
         </is>
       </c>
     </row>
@@ -15172,17 +15217,17 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V2-7</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
+          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3ef6b06</t>
+          <t>dr1v90 ff1846a</t>
         </is>
       </c>
     </row>
@@ -15192,22 +15237,22 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
+          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>progress/d29_coldboot</t>
+          <t>dr1v90 3ef6b06</t>
         </is>
       </c>
     </row>
@@ -15215,24 +15260,24 @@
       <c r="A76" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B76" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>D11;D39</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
+          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>用户 10-19</t>
+          <t>progress/d29_coldboot</t>
         </is>
       </c>
     </row>
@@ -15240,24 +15285,24 @@
       <c r="A77" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B77" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D11;D39</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
+          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6333eb5</t>
+          <t>用户 10-19</t>
         </is>
       </c>
     </row>
@@ -15272,67 +15317,67 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>D42;D43</t>
+          <t>D41</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
+          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 8689db2 / 6e6d47b</t>
+          <t>dr1v90 6333eb5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D42;D43</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
+          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1017_03_24h</t>
+          <t>dr1v90 8689db2 / 6e6d47b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46313</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
+          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/SPEC.md</t>
+          <t>progress/soak_v0/1017_03_24h</t>
         </is>
       </c>
     </row>
@@ -15340,24 +15385,24 @@
       <c r="A81" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>V2-5</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
+          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_fmt/README.md</t>
+          <t>dr1v90 d27_link/SPEC.md</t>
         </is>
       </c>
     </row>
@@ -15372,17 +15417,17 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>D28b</t>
+          <t>V2-5</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
+          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/回板当天.md</t>
+          <t>dr1v90 v2_fmt/README.md</t>
         </is>
       </c>
     </row>
@@ -15390,24 +15435,24 @@
       <c r="A83" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>进展</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>D27b</t>
+          <t>D28b</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
+          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/README.md</t>
+          <t>dr1v90 v1_bringup/回板当天.md</t>
         </is>
       </c>
     </row>
@@ -15415,24 +15460,24 @@
       <c r="A84" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>V2-6</t>
+          <t>D27b</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
+          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 gw5a_bridge/p2/README.md</t>
+          <t>dr1v90 d27_link/README.md</t>
         </is>
       </c>
     </row>
@@ -15442,22 +15487,22 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>全套</t>
+          <t>V2-6</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
+          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ~/full_*.log</t>
+          <t>dr1v90 gw5a_bridge/p2/README.md</t>
         </is>
       </c>
     </row>
@@ -15467,22 +15512,22 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>修复</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>全套</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
+          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 slice/SPEC.md §13.2</t>
+          <t>dr1v90 ~/full_*.log</t>
         </is>
       </c>
     </row>
@@ -15492,22 +15537,22 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
+          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1016_wkend_24h</t>
+          <t>dr1v90 slice/SPEC.md §13.2</t>
         </is>
       </c>
     </row>
@@ -15517,7 +15562,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -15527,37 +15572,37 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
+          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1017_*.log</t>
+          <t>progress/soak_v0/1016_wkend_24h</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>部署</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
+          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22c.board.log</t>
+          <t>progress/v0_accept/accept_1017_*.log</t>
         </is>
       </c>
     </row>
@@ -15565,9 +15610,9 @@
       <c r="A90" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -15577,12 +15622,12 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
+          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d22c.board.log</t>
         </is>
       </c>
     </row>
@@ -15590,24 +15635,24 @@
       <c r="A91" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
+          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board5.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15615,9 +15660,9 @@
       <c r="A92" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -15627,12 +15672,12 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
+          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d21.board5.log</t>
         </is>
       </c>
     </row>
@@ -15647,12 +15692,12 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
+          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -15665,9 +15710,9 @@
       <c r="A94" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -15677,12 +15722,12 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
+          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_A fps_B</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15690,9 +15735,9 @@
       <c r="A95" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -15702,12 +15747,12 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
+          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_C</t>
+          <t>soak_runs/fps_A fps_B</t>
         </is>
       </c>
     </row>
@@ -15715,24 +15760,24 @@
       <c r="A96" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
+          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20d-ackrps db4ec93</t>
+          <t>soak_runs/fps_C</t>
         </is>
       </c>
     </row>
@@ -15747,17 +15792,17 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
+          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
+          <t>dr1v90 task/d20d-ackrps db4ec93</t>
         </is>
       </c>
     </row>
@@ -15767,22 +15812,22 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
+          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_D</t>
+          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
         </is>
       </c>
     </row>
@@ -15790,9 +15835,9 @@
       <c r="A99" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -15802,12 +15847,12 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
+          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>soak_runs/fps_D</t>
         </is>
       </c>
     </row>
@@ -15815,24 +15860,24 @@
       <c r="A100" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
+          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>~/rv_deploy.board.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15840,24 +15885,24 @@
       <c r="A101" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
+          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_deploy.board.log</t>
         </is>
       </c>
     </row>
@@ -15865,24 +15910,24 @@
       <c r="A102" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>验收</t>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
+          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15892,22 +15937,22 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>开工</t>
+          <t>验收</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>D20e/D23</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
+          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
+          <t>progress/v0_accept/</t>
         </is>
       </c>
     </row>
@@ -15915,24 +15960,24 @@
       <c r="A104" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B104" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>开工</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D20e/D23</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
+          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
         </is>
       </c>
     </row>
@@ -15940,24 +15985,24 @@
       <c r="A105" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
+          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15972,12 +16017,12 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
+          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -15990,24 +16035,24 @@
       <c r="A107" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
+          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1016_d20e.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16015,24 +16060,24 @@
       <c r="A108" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>KR7.3/D24</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
+          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>progress/v0_accept/accept_1016_d20e.log</t>
         </is>
       </c>
     </row>
@@ -16040,24 +16085,24 @@
       <c r="A109" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>KR7.3/D24</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
+          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>D:\card03</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16065,24 +16110,24 @@
       <c r="A110" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>D25</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
+          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>D:\card03</t>
         </is>
       </c>
     </row>
@@ -16090,24 +16135,24 @@
       <c r="A111" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D25</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
+          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\cap_COM29.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16122,17 +16167,17 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
+          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20d_ackrps d20c_fps</t>
+          <t>D:\card03\cap_COM29.log</t>
         </is>
       </c>
     </row>
@@ -16140,24 +16185,24 @@
       <c r="A113" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
+          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d12_latency/RESULTS.md</t>
+          <t>dr1v90 d20d_ackrps d20c_fps</t>
         </is>
       </c>
     </row>
@@ -16172,17 +16217,17 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
+          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d9_e2e/</t>
+          <t>dr1v90 d12_latency/RESULTS.md</t>
         </is>
       </c>
     </row>
@@ -16190,24 +16235,24 @@
       <c r="A115" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
+          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\boot03.log</t>
+          <t>dr1v90 d9_e2e/</t>
         </is>
       </c>
     </row>
@@ -16215,24 +16260,24 @@
       <c r="A116" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
+          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
+          <t>D:\card03\boot03.log</t>
         </is>
       </c>
     </row>
@@ -16240,24 +16285,24 @@
       <c r="A117" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>开工</t>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
+          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
+          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
         </is>
       </c>
     </row>
@@ -16267,22 +16312,22 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>方案</t>
+          <t>开工</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
+          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d29_sdboot/PLAN.md</t>
+          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
         </is>
       </c>
     </row>
@@ -16290,24 +16335,24 @@
       <c r="A119" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>方案</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
+          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/</t>
+          <t>dr1v90 d29_sdboot/PLAN.md</t>
         </is>
       </c>
     </row>
@@ -16315,24 +16360,24 @@
       <c r="A120" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>修复</t>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
+          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
+          <t>dr1v90 v1_bringup/</t>
         </is>
       </c>
     </row>
@@ -16342,22 +16387,22 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>进展</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>V2-3</t>
+          <t>D30</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
+          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_map/DESIGN.md</t>
+          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
         </is>
       </c>
     </row>
@@ -16367,47 +16412,47 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>评估</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>V2-3</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
+          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d31_v1odd/REPORT.md</t>
+          <t>dr1v90 v2_map/DESIGN.md</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="12" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B123" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46311</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>评估</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D31</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
+          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/report.md</t>
+          <t>dr1v90 d31_v1odd/REPORT.md</t>
         </is>
       </c>
     </row>
@@ -16415,24 +16460,24 @@
       <c r="A124" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>QoS</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
+          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>~/qos_runs</t>
+          <t>progress/soak_v0/report.md</t>
         </is>
       </c>
     </row>
@@ -16447,17 +16492,17 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>D16b</t>
+          <t>QoS</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
+          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16b-tile 7936b7e</t>
+          <t>~/qos_runs</t>
         </is>
       </c>
     </row>
@@ -16465,24 +16510,24 @@
       <c r="A126" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B126" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D16b</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
+          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>dr1v90 task/d16b-tile 7936b7e</t>
         </is>
       </c>
     </row>
@@ -16497,12 +16542,12 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
+          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -16515,24 +16560,24 @@
       <c r="A128" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B128" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>V1/V2</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
+          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>budget/rpm_range_2026-10-15.md</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -16540,24 +16585,24 @@
       <c r="A129" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B129" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>V1/V2</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
+          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>progress/realspin_v0/</t>
+          <t>budget/rpm_range_2026-10-15.md</t>
         </is>
       </c>
     </row>
@@ -16565,19 +16610,19 @@
       <c r="A130" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B130" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
+          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -16590,24 +16635,24 @@
       <c r="A131" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
+          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20-smooth 83a5fd7</t>
+          <t>progress/realspin_v0/</t>
         </is>
       </c>
     </row>
@@ -16615,24 +16660,24 @@
       <c r="A132" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
+          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 e215176</t>
+          <t>dr1v90 task/d20-smooth 83a5fd7</t>
         </is>
       </c>
     </row>
@@ -16640,24 +16685,24 @@
       <c r="A133" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
+          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d19-halfrev 1beafa6</t>
+          <t>dr1v90 e215176</t>
         </is>
       </c>
     </row>
@@ -16672,17 +16717,17 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>D20b</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
+          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20b-sim 9081f62</t>
+          <t>dr1v90 task/d19-halfrev 1beafa6</t>
         </is>
       </c>
     </row>
@@ -16692,22 +16737,22 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D20b</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
+          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/merge-d19-d20 106364e</t>
+          <t>dr1v90 task/d20b-sim 9081f62</t>
         </is>
       </c>
     </row>
@@ -16715,24 +16760,24 @@
       <c r="A136" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B136" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>D19/D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
+          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/merge-d19-d20 106364e</t>
         </is>
       </c>
     </row>
@@ -16740,24 +16785,24 @@
       <c r="A137" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D19/D20</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
+          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband adeba44</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16767,22 +16812,22 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>D20/D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
+          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>~/realspin/tcp</t>
+          <t>dr1v90 task/d21-nband adeba44</t>
         </is>
       </c>
     </row>
@@ -16790,24 +16835,24 @@
       <c r="A139" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B139" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D20/D22</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
+          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>~/realspin/tcp</t>
         </is>
       </c>
     </row>
@@ -16815,9 +16860,9 @@
       <c r="A140" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B140" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -16827,12 +16872,12 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
+          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach ee4a55c</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -16847,17 +16892,17 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
+          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20c-fps 338eaaf</t>
+          <t>dr1v90 task/d22-reach ee4a55c</t>
         </is>
       </c>
     </row>
@@ -16867,7 +16912,7 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>复验</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -16877,12 +16922,12 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
+          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d20c.v.log</t>
+          <t>dr1v90 task/d20c-fps 338eaaf</t>
         </is>
       </c>
     </row>
@@ -16892,22 +16937,22 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>复验</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
+          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d8-cosim 85dfe51</t>
+          <t>~/rv_d20c.v.log</t>
         </is>
       </c>
     </row>
@@ -16915,9 +16960,9 @@
       <c r="A144" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B144" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -16927,12 +16972,12 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
+          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/d8-cosim 85dfe51</t>
         </is>
       </c>
     </row>
@@ -16940,24 +16985,24 @@
       <c r="A145" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B145" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>D22/D20</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
+          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/netdiag_1015_1814</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16965,24 +17010,24 @@
       <c r="A146" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B146" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22/D20</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
+          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board.log</t>
+          <t>soak_runs/netdiag_1015_1814</t>
         </is>
       </c>
     </row>
@@ -16997,17 +17042,17 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
+          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach</t>
+          <t>~/rv_d21.board.log</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17072,7 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
+          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
@@ -17040,9 +17085,9 @@
       <c r="A149" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B149" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -17052,12 +17097,12 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
+          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22.board2.log</t>
+          <t>dr1v90 task/d22-reach</t>
         </is>
       </c>
     </row>
@@ -17067,22 +17112,22 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
+          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>~/d21b_forensic.log</t>
+          <t>~/rv_d22.board2.log</t>
         </is>
       </c>
     </row>
@@ -17097,17 +17142,17 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
+          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach 0d1da09</t>
+          <t>~/d21b_forensic.log</t>
         </is>
       </c>
     </row>
@@ -17117,7 +17162,7 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -17127,12 +17172,12 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
+          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22b.board.log</t>
+          <t>dr1v90 task/d22-reach 0d1da09</t>
         </is>
       </c>
     </row>
@@ -17142,7 +17187,7 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -17152,12 +17197,12 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
+          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach e438a12</t>
+          <t>~/rv_d22b.board.log</t>
         </is>
       </c>
     </row>
@@ -17167,47 +17212,47 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
+          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband 084bba3</t>
+          <t>dr1v90 task/d22-reach e438a12</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B155" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>dr1v90 task/d21-nband 084bba3</t>
         </is>
       </c>
     </row>
@@ -17215,24 +17260,24 @@
       <c r="A156" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B156" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -17240,24 +17285,24 @@
       <c r="A157" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B157" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B157" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -17277,7 +17322,7 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -17290,24 +17335,24 @@
       <c r="A159" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B159" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B159" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -17315,24 +17360,24 @@
       <c r="A160" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B160" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B160" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -17340,9 +17385,9 @@
       <c r="A161" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B161" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B161" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -17352,12 +17397,12 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -17365,9 +17410,9 @@
       <c r="A162" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B162" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B162" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -17377,12 +17422,12 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -17390,24 +17435,24 @@
       <c r="A163" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B163" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17415,24 +17460,24 @@
       <c r="A164" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B164" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -17440,24 +17485,24 @@
       <c r="A165" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B165" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B165" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -17465,24 +17510,24 @@
       <c r="A166" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B166" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B166" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17490,9 +17535,9 @@
       <c r="A167" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B167" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -17502,12 +17547,12 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -17515,24 +17560,24 @@
       <c r="A168" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B168" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B168" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -17540,9 +17585,9 @@
       <c r="A169" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B169" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B169" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -17552,12 +17597,12 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -17565,24 +17610,24 @@
       <c r="A170" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B170" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -17590,24 +17635,24 @@
       <c r="A171" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B171" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B171" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -17615,24 +17660,24 @@
       <c r="A172" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B172" s="5" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
@@ -17640,24 +17685,24 @@
       <c r="A173" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B173" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
@@ -17665,24 +17710,24 @@
       <c r="A174" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B174" s="5" t="inlineStr">
-        <is>
-          <t>开始</t>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -17690,24 +17735,24 @@
       <c r="A175" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B175" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
@@ -17715,49 +17760,49 @@
       <c r="A176" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B176" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B176" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B177" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B177" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -17772,17 +17817,17 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -17797,17 +17842,17 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -17815,9 +17860,9 @@
       <c r="A180" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B180" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
@@ -17827,12 +17872,12 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -17840,9 +17885,9 @@
       <c r="A181" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B181" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -17852,12 +17897,12 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -17865,24 +17910,24 @@
       <c r="A182" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B182" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -17890,9 +17935,9 @@
       <c r="A183" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B183" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B183" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -17902,12 +17947,12 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -17922,17 +17967,17 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -17940,9 +17985,9 @@
       <c r="A185" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B185" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -17952,12 +17997,12 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -17977,7 +18022,7 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
@@ -17990,24 +18035,24 @@
       <c r="A187" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B187" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18015,24 +18060,24 @@
       <c r="A188" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B188" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -18040,24 +18085,24 @@
       <c r="A189" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B189" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B189" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18072,17 +18117,17 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -18090,19 +18135,19 @@
       <c r="A191" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B191" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
@@ -18115,9 +18160,9 @@
       <c r="A192" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B192" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B192" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
@@ -18127,12 +18172,12 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18140,24 +18185,24 @@
       <c r="A193" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B193" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B193" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -18165,9 +18210,9 @@
       <c r="A194" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B194" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B194" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -18177,12 +18222,12 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18190,9 +18235,9 @@
       <c r="A195" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B195" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B195" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -18202,12 +18247,12 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -18215,24 +18260,24 @@
       <c r="A196" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B196" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B196" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18240,24 +18285,24 @@
       <c r="A197" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B197" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -18270,15 +18315,19 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C198" s="4" t="inlineStr"/>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18286,15 +18335,15 @@
       <c r="A199" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B199" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B199" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr"/>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
@@ -18307,20 +18356,20 @@
       <c r="A200" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B200" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B200" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr"/>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -18333,19 +18382,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C201" s="4" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="C201" s="4" t="inlineStr"/>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -18360,12 +18405,12 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
@@ -18385,12 +18430,12 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
@@ -18410,12 +18455,12 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
@@ -18435,12 +18480,12 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
@@ -18460,17 +18505,17 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18478,24 +18523,24 @@
       <c r="A207" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B207" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B207" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
@@ -18503,18 +18548,43 @@
       <c r="A208" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B208" s="23" t="inlineStr">
+      <c r="B208" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B209" s="23" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C208" s="4" t="inlineStr"/>
-      <c r="D208" s="4" t="inlineStr">
+      <c r="C209" s="4" t="inlineStr"/>
+      <c r="D209" s="4" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E208" s="4" t="inlineStr">
+      <c r="E209" s="4" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -23257,7 +23327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23301,7 +23371,7 @@
         <v>46307</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>5</v>
@@ -23315,7 +23385,7 @@
         <v>46308</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>7</v>
@@ -23329,7 +23399,7 @@
         <v>46309</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>8</v>
@@ -23343,7 +23413,7 @@
         <v>46310</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>12</v>
@@ -23357,7 +23427,7 @@
         <v>46311</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>20</v>
@@ -23371,7 +23441,7 @@
         <v>46312</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>28</v>
@@ -23385,7 +23455,7 @@
         <v>46313</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>28</v>
@@ -23399,7 +23469,7 @@
         <v>46314</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>32</v>
@@ -23413,13 +23483,13 @@
         <v>46315</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -23427,10 +23497,10 @@
         <v>46316</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" s="5" t="n"/>
     </row>
@@ -23439,10 +23509,10 @@
         <v>46317</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" s="5" t="n"/>
     </row>
@@ -23451,10 +23521,10 @@
         <v>46318</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="5" t="n"/>
     </row>
@@ -23463,10 +23533,10 @@
         <v>46319</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" s="5" t="n"/>
     </row>
@@ -25704,6 +25774,44 @@
       <c r="H82" s="4" t="inlineStr">
         <is>
           <t>zynq_pov 254e998 (categories.csv; 达成率前后逐日一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>D47</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>系统从 QSPI 加载 (去 TF/eMMC 准备; 03 板试)</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>dr1v90 f3f384c (5/5 QSPI 启动 + 坏镜像回退 TF; 慢 7.6 s; Linux 写 QSPI 失效走 u-boot; 03 已回 TF)</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-20.xlsx
+++ b/docs/progress/显性目的进度_2026-10-20.xlsx
@@ -8580,7 +8580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:I135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8752,16 +8752,16 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
+          <t>20/23</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
           <t>19/22</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>18/21</t>
-        </is>
-      </c>
       <c r="E6" s="9" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -9374,12 +9374,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 整机</t>
+          <t>V2 192×216 · 面板映射/后端</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>V2-4</t>
+          <t>D48</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>2 期 30 Hz 整机上转子</t>
+          <t>V2 双面全链路系统仿真 (PC→主控→桥→2260 模型)</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -12097,17 +12097,15 @@
           <t>V2 · 必须</t>
         </is>
       </c>
-      <c r="G101" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H101" s="12" t="n"/>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t>等 T2 板 (V2-1) + 1.2G 上行 (V2-2)</t>
-        </is>
-      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="I101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -12117,36 +12115,38 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>画面指标 (各期)</t>
+          <t>V2 192×216 · 整机</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>KR1.6</t>
+          <t>V2-4</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>内容刷新率 (实转上屏) (最新 10.8 fps)</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr"/>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1⬜ V2⬜</t>
-        </is>
-      </c>
-      <c r="H102" s="12" t="n">
-        <v>46307</v>
-      </c>
+          <t>2 期 30 Hz 整机上转子</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 必须</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="n"/>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>等 V1 整机 720 RPM 实转 (验证板 11-10 回板)</t>
+          <t>等 T2 板 (V2-1) + 1.2G 上行 (V2-2)</t>
         </is>
       </c>
     </row>
@@ -12168,18 +12168,18 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>KR2.1</t>
+          <t>KR1.6</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>体帧率 (最新 21.7 Hz)</t>
+          <t>内容刷新率 (实转上屏) (最新 10.8 fps)</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1🔵 V2⬜</t>
+          <t>V0✅ V1⬜ V2⬜</t>
         </is>
       </c>
       <c r="H103" s="12" t="n">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>等 V1 回板实转 720 RPM×358 片</t>
+          <t>等 V1 整机 720 RPM 实转 (验证板 11-10 回板)</t>
         </is>
       </c>
     </row>
@@ -12209,18 +12209,18 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>KR3.1</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>每面像素数 (最新 28800 px)</t>
+          <t>体帧率 (最新 21.7 Hz)</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr"/>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1✅ V2⬜</t>
+          <t>V0✅ V1🔵 V2⬜</t>
         </is>
       </c>
       <c r="H104" s="12" t="n">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>等 2 期 192×216 屏</t>
+          <t>等 V1 回板实转 720 RPM×358 片</t>
         </is>
       </c>
     </row>
@@ -12250,18 +12250,18 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>KR3.2</t>
+          <t>KR3.1</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>每圈片数 (最新 142 片)</t>
+          <t>每面像素数 (最新 28800 px)</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr"/>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1🔵 V2⬜</t>
+          <t>V0✅ V1✅ V2⬜</t>
         </is>
       </c>
       <c r="H105" s="12" t="n">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>等 V1 回板实测</t>
+          <t>等 2 期 192×216 屏</t>
         </is>
       </c>
     </row>
@@ -12291,18 +12291,18 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>KR4.1</t>
+          <t>KR3.2</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>色深 (最新 3 bit/通道)</t>
+          <t>每圈片数 (最新 142 片)</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr"/>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1🔵 V2🔵</t>
+          <t>V0✅ V1🔵 V2⬜</t>
         </is>
       </c>
       <c r="H106" s="12" t="n">
@@ -12310,50 +12310,50 @@
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>等 V1 2260 回板上屏</t>
+          <t>等 V1 回板实测</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>④ 运维保障</t>
+          <t>③ 显示 (按期换后端)</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>开机即用</t>
+          <t>画面指标 (各期)</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>KR4.1</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>开机自动演示 + 转速门控</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>色深 (最新 3 bit/通道)</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1🔵 V2🔵</t>
         </is>
       </c>
       <c r="H107" s="12" t="n">
         <v>46307</v>
       </c>
-      <c r="I107" s="4" t="inlineStr"/>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>等 V1 2260 回板上屏</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>启动提速 + 启动屏显 (含原 backlog B1)</t>
+          <t>开机自动演示 + 转速门控</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="H108" s="12" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="I108" s="4" t="inlineStr"/>
     </row>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>开机默认动画 = 立方体动图 (用户 10-16 提)</t>
+          <t>启动提速 + 启动屏显 (含原 backlog B1)</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
@@ -12433,7 +12433,7 @@
         </is>
       </c>
       <c r="H109" s="12" t="n">
-        <v>46311</v>
+        <v>46309</v>
       </c>
       <c r="I109" s="4" t="inlineStr"/>
     </row>
@@ -12455,17 +12455,17 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>D47</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>系统从 QSPI 加载 (去 TF/eMMC 准备; 03 板试)</t>
+          <t>开机默认动画 = 立方体动图 (用户 10-16 提)</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>V2 · 加分</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
@@ -12474,13 +12474,9 @@
         </is>
       </c>
       <c r="H110" s="12" t="n">
-        <v>46315</v>
-      </c>
-      <c r="I110" s="4" t="inlineStr">
-        <is>
-          <t>T2 板 QSPI 选 64MiB / 厂商驱动提速</t>
-        </is>
-      </c>
+        <v>46311</v>
+      </c>
+      <c r="I110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12495,29 +12491,37 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>KR8.1</t>
+          <t>D47</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>上电到 0° 片亮起 (停转) (最新 12.4 s)</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr"/>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>系统从 QSPI 加载 (去 TF/eMMC 准备; 03 板试)</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 加分</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H111" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I111" s="4" t="inlineStr"/>
+        <v>46315</v>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>T2 板 QSPI 选 64MiB / 厂商驱动提速</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12537,22 +12541,22 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>KR8.4</t>
+          <t>KR8.1</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>上电到转稳全亮 (最新 26 s)</t>
+          <t>上电到 0° 片亮起 (停转) (最新 12.4 s)</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>V0— V1— V2—</t>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H112" s="12" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="I112" s="4" t="inlineStr"/>
     </row>
@@ -12564,32 +12568,28 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>联网/找板/自愈</t>
+          <t>开机即用</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>KR8.4</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>开机自连 WiFi</t>
-        </is>
-      </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G113" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>上电到转稳全亮 (最新 26 s)</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>V0— V1— V2—</t>
         </is>
       </c>
       <c r="H113" s="12" t="n">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS)</t>
+          <t>开机自连 WiFi</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="H114" s="12" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="I114" s="4" t="inlineStr"/>
     </row>
@@ -12656,12 +12656,12 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 (服务监护/看门狗/兜底热点/povnetd 1.2)</t>
+          <t>按名字找板 (mDNS)</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
@@ -12675,7 +12675,7 @@
         </is>
       </c>
       <c r="H115" s="12" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="I115" s="4" t="inlineStr"/>
     </row>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复 ≤30 s (03 长跑断 155 s)</t>
+          <t>不插串口永远连得上 (服务监护/看门狗/兜底热点/povnetd 1.2)</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="H116" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I116" s="4" t="inlineStr"/>
     </row>
@@ -12738,12 +12738,12 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>D43</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>povnetd 1.3 网络自愈回归修复</t>
+          <t>WiFi 断线恢复 ≤30 s (03 长跑断 155 s)</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
@@ -12774,27 +12774,31 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>KR8.2</t>
+          <t>D43</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>按名字找到板子 (最新 19.8 s)</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr"/>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>povnetd 1.3 网络自愈回归修复</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 必须</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H118" s="12" t="n">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="I118" s="4" t="inlineStr"/>
     </row>
@@ -12806,32 +12810,28 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>远程运维/升级 (含 JTAG 灌桥)</t>
+          <t>联网/找板/自愈</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR8.2</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>转子运维 (netguard-lite / 遥测 / 远程升级)</t>
-        </is>
-      </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G119" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>按名字找到板子 (最新 19.8 s)</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr"/>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H119" s="12" t="n">
@@ -12857,17 +12857,17 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>主控经 JTAG 给桥灌位流 (V1 远程升级软件)</t>
+          <t>转子运维 (netguard-lite / 遥测 / 远程升级)</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
@@ -12876,7 +12876,7 @@
         </is>
       </c>
       <c r="H120" s="12" t="n">
-        <v>46314</v>
+        <v>46309</v>
       </c>
       <c r="I120" s="4" t="inlineStr"/>
     </row>
@@ -12898,17 +12898,17 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>D42</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>03 板软件跟进主线</t>
+          <t>主控经 JTAG 给桥灌位流 (V1 远程升级软件)</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>V0 · 加分</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
@@ -12934,27 +12934,31 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>KR8.3</t>
+          <t>D42</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>需要串口 (1=需要) (最新 0 是/否)</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr"/>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>03 板软件跟进主线</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H122" s="12" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="I122" s="4" t="inlineStr"/>
     </row>
@@ -12976,12 +12980,12 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>KR8.3</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用) (最新 1 是/否)</t>
+          <t>需要串口 (1=需要) (最新 0 是/否)</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr"/>
@@ -12991,7 +12995,7 @@
         </is>
       </c>
       <c r="H123" s="12" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="I123" s="4" t="inlineStr"/>
     </row>
@@ -13013,12 +13017,12 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>KR9.2</t>
+          <t>KR9.1</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>远程升级失败自动回滚 (1=有) (最新 1 是/否)</t>
+          <t>转子遥测可用 (1=可用) (最新 1 是/否)</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr"/>
@@ -13040,40 +13044,34 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>主控↔桥通信</t>
+          <t>远程运维/升级 (含 JTAG 灌桥)</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>KR9.2</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>C1 台架彩排 + 1.2G 误码测试</t>
-        </is>
-      </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>V1准备 · 加分</t>
-        </is>
-      </c>
-      <c r="G125" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H125" s="12" t="n"/>
-      <c r="I125" s="4" t="inlineStr">
-        <is>
-          <t>不做 (用户 10-19 定), 由 D39 到板 comm_check 代替</t>
-        </is>
-      </c>
+          <t>远程升级失败自动回滚 (1=有) (最新 1 是/否)</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -13093,28 +13091,30 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信全功能 (配置/状态/错误恢复/升级)</t>
+          <t>C1 台架彩排 + 1.2G 误码测试</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H126" s="12" t="n">
-        <v>46312</v>
-      </c>
-      <c r="I126" s="4" t="inlineStr"/>
+          <t>V1准备 · 加分</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="n"/>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>不做 (用户 10-19 定), 由 D39 到板 comm_check 代替</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 + PRBS 位流</t>
+          <t>SoC↔桥通信全功能 (配置/状态/错误恢复/升级)</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="H127" s="12" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="I127" s="4" t="inlineStr"/>
     </row>
@@ -13165,7 +13165,7 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>可靠性验证 (冷启动/长跑)</t>
+          <t>主控↔桥通信</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
@@ -13175,17 +13175,17 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>V0A</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>V0 重启验收 (不插串口: 找回/守护/开机默认/WiFi/推流/稳定 6 项)</t>
+          <t>SoC↔桥通信专项验证包 + PRBS 位流</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>V0 · 必须</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
@@ -13194,7 +13194,7 @@
         </is>
       </c>
       <c r="H128" s="12" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="I128" s="4" t="inlineStr"/>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>V0A</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>冷启动认不到 TF 卡 (03 停在 u-boot)</t>
+          <t>V0 重启验收 (不插串口: 找回/守护/开机默认/WiFi/推流/稳定 6 项)</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
@@ -13235,7 +13235,7 @@
         </is>
       </c>
       <c r="H129" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I129" s="4" t="inlineStr"/>
     </row>
@@ -13257,17 +13257,17 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>D49</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+          <t>冷启动认不到 TF 卡 (03 停在 u-boot)</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>V0 · 加分</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
@@ -13276,7 +13276,7 @@
         </is>
       </c>
       <c r="H130" s="12" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I130" s="4" t="inlineStr"/>
     </row>
@@ -13293,27 +13293,31 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D49</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr"/>
-      <c r="G131" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H131" s="12" t="n">
-        <v>46312</v>
+        <v>46315</v>
       </c>
       <c r="I131" s="4" t="inlineStr"/>
     </row>
@@ -13335,12 +13339,12 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
+          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr"/>
@@ -13350,7 +13354,7 @@
         </is>
       </c>
       <c r="H132" s="12" t="n">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="I132" s="4" t="inlineStr"/>
     </row>
@@ -13367,33 +13371,29 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
+          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr"/>
-      <c r="G133" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H133" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I133" s="4" t="inlineStr">
-        <is>
-          <t>T2 板留 eMMC、打胶</t>
-        </is>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="I133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>开发环境</t>
+          <t>可靠性验证 (冷启动/长跑)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -13413,24 +13413,65 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>D 盘 EIO（IP-guard 驱动）</t>
+          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr"/>
-      <c r="G134" s="8" t="inlineStr">
-        <is>
-          <t>监控</t>
+      <c r="G134" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H134" s="12" t="n">
         <v>46308</v>
       </c>
       <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>T2 板留 eMMC、打胶</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>④ 运维保障</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>开发环境</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>风险</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>D 盘 EIO（IP-guard 驱动）</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr"/>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>监控</t>
+        </is>
+      </c>
+      <c r="H135" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
         <is>
           <t>看门狗自动重挂 + 构建放 WSL 本地盘</t>
         </is>
@@ -13450,7 +13491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J209"/>
+  <dimension ref="A1:J210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13585,16 +13626,16 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>65/75</t>
+          <t>66/76</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>KR 17/24 + 交付 48/51 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 17/24 + 交付 49/52 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="17" t="n">
@@ -13731,7 +13772,7 @@
         <v>0.9118000000000001</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>0.8667</v>
+        <v>0.8683999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -14758,26 +14799,26 @@
     </row>
     <row r="56">
       <c r="A56" s="12" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46315</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>D48</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
+          <t>V2 双面全链路系统仿真 PASS: 605/513/461 三档, 两面像素 2,488,320 + 上行 528,768 组 0 错, 反例 8 个全 FAIL, 无 RTL bug; 主会话复跑 quick 7/0</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d22_reach/README.md</t>
+          <t>dr1v90 fca9830</t>
         </is>
       </c>
     </row>
@@ -14785,24 +14826,24 @@
       <c r="A57" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>D32</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
+          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>dr1v90</t>
+          <t>dr1v90 d22_reach/README.md</t>
         </is>
       </c>
     </row>
@@ -14810,9 +14851,9 @@
       <c r="A58" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -14822,12 +14863,12 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
+          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/acc32_*.log</t>
+          <t>dr1v90</t>
         </is>
       </c>
     </row>
@@ -14835,24 +14876,24 @@
       <c r="A59" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B59" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
+          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>progress/v0_accept/acc32_*.log</t>
         </is>
       </c>
     </row>
@@ -14860,24 +14901,24 @@
       <c r="A60" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>补录</t>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>KR4.2</t>
+          <t>用户</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
+          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -14887,22 +14928,22 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>补录</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
+          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -14912,22 +14953,22 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
+          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 card03</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -14937,22 +14978,22 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
+          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2b111f0</t>
+          <t>dr1v90 card03</t>
         </is>
       </c>
     </row>
@@ -14962,22 +15003,22 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
+          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
+          <t>dr1v90 2b111f0</t>
         </is>
       </c>
     </row>
@@ -14985,24 +15026,24 @@
       <c r="A65" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B65" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
+          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
         </is>
       </c>
     </row>
@@ -15010,24 +15051,24 @@
       <c r="A66" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
+          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 97a10cf</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15037,22 +15078,22 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
+          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 7253608</t>
+          <t>dr1v90 97a10cf</t>
         </is>
       </c>
     </row>
@@ -15060,24 +15101,24 @@
       <c r="A68" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B68" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D34</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
+          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 7253608</t>
         </is>
       </c>
     </row>
@@ -15085,24 +15126,24 @@
       <c r="A69" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
+          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 23474c7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15117,17 +15158,17 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
+          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 f2584d9</t>
+          <t>dr1v90 23474c7</t>
         </is>
       </c>
     </row>
@@ -15142,17 +15183,17 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>D38</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
+          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ad201f9</t>
+          <t>dr1v90 f2584d9</t>
         </is>
       </c>
     </row>
@@ -15162,22 +15203,22 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>V1主控</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
+          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>本机构建</t>
+          <t>dr1v90 ad201f9</t>
         </is>
       </c>
     </row>
@@ -15192,17 +15233,17 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V1主控</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
+          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d39-comm b69f6d8</t>
+          <t>本机构建</t>
         </is>
       </c>
     </row>
@@ -15212,22 +15253,22 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>V2-7</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
+          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ff1846a</t>
+          <t>dr1v90 task/d39-comm b69f6d8</t>
         </is>
       </c>
     </row>
@@ -15242,17 +15283,17 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V2-7</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
+          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3ef6b06</t>
+          <t>dr1v90 ff1846a</t>
         </is>
       </c>
     </row>
@@ -15262,22 +15303,22 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
+          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>progress/d29_coldboot</t>
+          <t>dr1v90 3ef6b06</t>
         </is>
       </c>
     </row>
@@ -15285,24 +15326,24 @@
       <c r="A77" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B77" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>D11;D39</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
+          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>用户 10-19</t>
+          <t>progress/d29_coldboot</t>
         </is>
       </c>
     </row>
@@ -15310,24 +15351,24 @@
       <c r="A78" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D11;D39</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
+          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6333eb5</t>
+          <t>用户 10-19</t>
         </is>
       </c>
     </row>
@@ -15342,67 +15383,67 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>D42;D43</t>
+          <t>D41</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
+          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 8689db2 / 6e6d47b</t>
+          <t>dr1v90 6333eb5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D42;D43</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
+          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1017_03_24h</t>
+          <t>dr1v90 8689db2 / 6e6d47b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46313</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
+          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/SPEC.md</t>
+          <t>progress/soak_v0/1017_03_24h</t>
         </is>
       </c>
     </row>
@@ -15410,24 +15451,24 @@
       <c r="A82" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>V2-5</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
+          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_fmt/README.md</t>
+          <t>dr1v90 d27_link/SPEC.md</t>
         </is>
       </c>
     </row>
@@ -15442,17 +15483,17 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>D28b</t>
+          <t>V2-5</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
+          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/回板当天.md</t>
+          <t>dr1v90 v2_fmt/README.md</t>
         </is>
       </c>
     </row>
@@ -15460,24 +15501,24 @@
       <c r="A84" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>进展</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>D27b</t>
+          <t>D28b</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
+          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/README.md</t>
+          <t>dr1v90 v1_bringup/回板当天.md</t>
         </is>
       </c>
     </row>
@@ -15485,24 +15526,24 @@
       <c r="A85" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>V2-6</t>
+          <t>D27b</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
+          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 gw5a_bridge/p2/README.md</t>
+          <t>dr1v90 d27_link/README.md</t>
         </is>
       </c>
     </row>
@@ -15512,22 +15553,22 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>全套</t>
+          <t>V2-6</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
+          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ~/full_*.log</t>
+          <t>dr1v90 gw5a_bridge/p2/README.md</t>
         </is>
       </c>
     </row>
@@ -15537,22 +15578,22 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>修复</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>全套</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
+          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 slice/SPEC.md §13.2</t>
+          <t>dr1v90 ~/full_*.log</t>
         </is>
       </c>
     </row>
@@ -15562,22 +15603,22 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
+          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1016_wkend_24h</t>
+          <t>dr1v90 slice/SPEC.md §13.2</t>
         </is>
       </c>
     </row>
@@ -15587,7 +15628,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -15597,37 +15638,37 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
+          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1017_*.log</t>
+          <t>progress/soak_v0/1016_wkend_24h</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>部署</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
+          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22c.board.log</t>
+          <t>progress/v0_accept/accept_1017_*.log</t>
         </is>
       </c>
     </row>
@@ -15635,9 +15676,9 @@
       <c r="A91" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -15647,12 +15688,12 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
+          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d22c.board.log</t>
         </is>
       </c>
     </row>
@@ -15660,24 +15701,24 @@
       <c r="A92" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
+          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board5.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15685,9 +15726,9 @@
       <c r="A93" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -15697,12 +15738,12 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
+          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d21.board5.log</t>
         </is>
       </c>
     </row>
@@ -15717,12 +15758,12 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
+          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -15735,9 +15776,9 @@
       <c r="A95" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -15747,12 +15788,12 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
+          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_A fps_B</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15760,9 +15801,9 @@
       <c r="A96" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -15772,12 +15813,12 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
+          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_C</t>
+          <t>soak_runs/fps_A fps_B</t>
         </is>
       </c>
     </row>
@@ -15785,24 +15826,24 @@
       <c r="A97" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
+          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20d-ackrps db4ec93</t>
+          <t>soak_runs/fps_C</t>
         </is>
       </c>
     </row>
@@ -15817,17 +15858,17 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
+          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
+          <t>dr1v90 task/d20d-ackrps db4ec93</t>
         </is>
       </c>
     </row>
@@ -15837,22 +15878,22 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
+          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_D</t>
+          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
         </is>
       </c>
     </row>
@@ -15860,9 +15901,9 @@
       <c r="A100" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -15872,12 +15913,12 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
+          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>soak_runs/fps_D</t>
         </is>
       </c>
     </row>
@@ -15885,24 +15926,24 @@
       <c r="A101" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
+          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>~/rv_deploy.board.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15910,24 +15951,24 @@
       <c r="A102" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
+          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_deploy.board.log</t>
         </is>
       </c>
     </row>
@@ -15935,24 +15976,24 @@
       <c r="A103" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>验收</t>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
+          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15962,22 +16003,22 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>开工</t>
+          <t>验收</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>D20e/D23</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
+          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
+          <t>progress/v0_accept/</t>
         </is>
       </c>
     </row>
@@ -15985,24 +16026,24 @@
       <c r="A105" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B105" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>开工</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D20e/D23</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
+          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
         </is>
       </c>
     </row>
@@ -16010,24 +16051,24 @@
       <c r="A106" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B106" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
+          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -16042,12 +16083,12 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
+          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -16060,24 +16101,24 @@
       <c r="A108" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
+          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1016_d20e.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16085,24 +16126,24 @@
       <c r="A109" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>KR7.3/D24</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
+          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>progress/v0_accept/accept_1016_d20e.log</t>
         </is>
       </c>
     </row>
@@ -16110,24 +16151,24 @@
       <c r="A110" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>KR7.3/D24</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
+          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>D:\card03</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16135,24 +16176,24 @@
       <c r="A111" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>D25</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
+          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>D:\card03</t>
         </is>
       </c>
     </row>
@@ -16160,24 +16201,24 @@
       <c r="A112" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D25</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
+          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\cap_COM29.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16192,17 +16233,17 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
+          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20d_ackrps d20c_fps</t>
+          <t>D:\card03\cap_COM29.log</t>
         </is>
       </c>
     </row>
@@ -16210,24 +16251,24 @@
       <c r="A114" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
+          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d12_latency/RESULTS.md</t>
+          <t>dr1v90 d20d_ackrps d20c_fps</t>
         </is>
       </c>
     </row>
@@ -16242,17 +16283,17 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
+          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d9_e2e/</t>
+          <t>dr1v90 d12_latency/RESULTS.md</t>
         </is>
       </c>
     </row>
@@ -16260,24 +16301,24 @@
       <c r="A116" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
+          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\boot03.log</t>
+          <t>dr1v90 d9_e2e/</t>
         </is>
       </c>
     </row>
@@ -16285,24 +16326,24 @@
       <c r="A117" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
+          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
+          <t>D:\card03\boot03.log</t>
         </is>
       </c>
     </row>
@@ -16310,24 +16351,24 @@
       <c r="A118" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>开工</t>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
+          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
+          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
         </is>
       </c>
     </row>
@@ -16337,22 +16378,22 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>方案</t>
+          <t>开工</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
+          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d29_sdboot/PLAN.md</t>
+          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
         </is>
       </c>
     </row>
@@ -16360,24 +16401,24 @@
       <c r="A120" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>方案</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
+          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/</t>
+          <t>dr1v90 d29_sdboot/PLAN.md</t>
         </is>
       </c>
     </row>
@@ -16385,24 +16426,24 @@
       <c r="A121" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>修复</t>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
+          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
+          <t>dr1v90 v1_bringup/</t>
         </is>
       </c>
     </row>
@@ -16412,22 +16453,22 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>进展</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>V2-3</t>
+          <t>D30</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
+          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_map/DESIGN.md</t>
+          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
         </is>
       </c>
     </row>
@@ -16437,47 +16478,47 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>评估</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>V2-3</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
+          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d31_v1odd/REPORT.md</t>
+          <t>dr1v90 v2_map/DESIGN.md</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="12" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B124" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46311</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>评估</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D31</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
+          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/report.md</t>
+          <t>dr1v90 d31_v1odd/REPORT.md</t>
         </is>
       </c>
     </row>
@@ -16485,24 +16526,24 @@
       <c r="A125" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>QoS</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
+          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>~/qos_runs</t>
+          <t>progress/soak_v0/report.md</t>
         </is>
       </c>
     </row>
@@ -16517,17 +16558,17 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>D16b</t>
+          <t>QoS</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
+          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16b-tile 7936b7e</t>
+          <t>~/qos_runs</t>
         </is>
       </c>
     </row>
@@ -16535,24 +16576,24 @@
       <c r="A127" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B127" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D16b</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
+          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>dr1v90 task/d16b-tile 7936b7e</t>
         </is>
       </c>
     </row>
@@ -16567,12 +16608,12 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
+          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -16585,24 +16626,24 @@
       <c r="A129" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B129" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>V1/V2</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
+          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>budget/rpm_range_2026-10-15.md</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -16610,24 +16651,24 @@
       <c r="A130" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>V1/V2</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
+          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>progress/realspin_v0/</t>
+          <t>budget/rpm_range_2026-10-15.md</t>
         </is>
       </c>
     </row>
@@ -16635,19 +16676,19 @@
       <c r="A131" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B131" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
+          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -16660,24 +16701,24 @@
       <c r="A132" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
+          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20-smooth 83a5fd7</t>
+          <t>progress/realspin_v0/</t>
         </is>
       </c>
     </row>
@@ -16685,24 +16726,24 @@
       <c r="A133" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
+          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 e215176</t>
+          <t>dr1v90 task/d20-smooth 83a5fd7</t>
         </is>
       </c>
     </row>
@@ -16710,24 +16751,24 @@
       <c r="A134" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
+          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d19-halfrev 1beafa6</t>
+          <t>dr1v90 e215176</t>
         </is>
       </c>
     </row>
@@ -16742,17 +16783,17 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>D20b</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
+          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20b-sim 9081f62</t>
+          <t>dr1v90 task/d19-halfrev 1beafa6</t>
         </is>
       </c>
     </row>
@@ -16762,22 +16803,22 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D20b</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
+          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/merge-d19-d20 106364e</t>
+          <t>dr1v90 task/d20b-sim 9081f62</t>
         </is>
       </c>
     </row>
@@ -16785,24 +16826,24 @@
       <c r="A137" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B137" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>D19/D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
+          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/merge-d19-d20 106364e</t>
         </is>
       </c>
     </row>
@@ -16810,24 +16851,24 @@
       <c r="A138" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D19/D20</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
+          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband adeba44</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16837,22 +16878,22 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>D20/D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
+          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>~/realspin/tcp</t>
+          <t>dr1v90 task/d21-nband adeba44</t>
         </is>
       </c>
     </row>
@@ -16860,24 +16901,24 @@
       <c r="A140" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B140" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D20/D22</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
+          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>~/realspin/tcp</t>
         </is>
       </c>
     </row>
@@ -16885,9 +16926,9 @@
       <c r="A141" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B141" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -16897,12 +16938,12 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
+          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach ee4a55c</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -16917,17 +16958,17 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
+          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20c-fps 338eaaf</t>
+          <t>dr1v90 task/d22-reach ee4a55c</t>
         </is>
       </c>
     </row>
@@ -16937,7 +16978,7 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>复验</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -16947,12 +16988,12 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
+          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d20c.v.log</t>
+          <t>dr1v90 task/d20c-fps 338eaaf</t>
         </is>
       </c>
     </row>
@@ -16962,22 +17003,22 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>复验</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
+          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d8-cosim 85dfe51</t>
+          <t>~/rv_d20c.v.log</t>
         </is>
       </c>
     </row>
@@ -16985,9 +17026,9 @@
       <c r="A145" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B145" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -16997,12 +17038,12 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
+          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/d8-cosim 85dfe51</t>
         </is>
       </c>
     </row>
@@ -17010,24 +17051,24 @@
       <c r="A146" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B146" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>D22/D20</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
+          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/netdiag_1015_1814</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -17035,24 +17076,24 @@
       <c r="A147" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B147" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22/D20</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
+          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board.log</t>
+          <t>soak_runs/netdiag_1015_1814</t>
         </is>
       </c>
     </row>
@@ -17067,17 +17108,17 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
+          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach</t>
+          <t>~/rv_d21.board.log</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17138,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
+          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -17110,9 +17151,9 @@
       <c r="A150" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B150" s="5" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -17122,12 +17163,12 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
+          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22.board2.log</t>
+          <t>dr1v90 task/d22-reach</t>
         </is>
       </c>
     </row>
@@ -17137,22 +17178,22 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
+          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>~/d21b_forensic.log</t>
+          <t>~/rv_d22.board2.log</t>
         </is>
       </c>
     </row>
@@ -17167,17 +17208,17 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
+          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach 0d1da09</t>
+          <t>~/d21b_forensic.log</t>
         </is>
       </c>
     </row>
@@ -17187,7 +17228,7 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -17197,12 +17238,12 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
+          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22b.board.log</t>
+          <t>dr1v90 task/d22-reach 0d1da09</t>
         </is>
       </c>
     </row>
@@ -17212,7 +17253,7 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -17222,12 +17263,12 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
+          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach e438a12</t>
+          <t>~/rv_d22b.board.log</t>
         </is>
       </c>
     </row>
@@ -17237,47 +17278,47 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
+          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband 084bba3</t>
+          <t>dr1v90 task/d22-reach e438a12</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B156" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>dr1v90 task/d21-nband 084bba3</t>
         </is>
       </c>
     </row>
@@ -17285,24 +17326,24 @@
       <c r="A157" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B157" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -17310,24 +17351,24 @@
       <c r="A158" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B158" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B158" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17388,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -17360,24 +17401,24 @@
       <c r="A160" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B160" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -17385,24 +17426,24 @@
       <c r="A161" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B161" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B161" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -17410,9 +17451,9 @@
       <c r="A162" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B162" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -17422,12 +17463,12 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -17435,9 +17476,9 @@
       <c r="A163" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B163" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B163" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -17447,12 +17488,12 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -17460,24 +17501,24 @@
       <c r="A164" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B164" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B164" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17485,24 +17526,24 @@
       <c r="A165" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B165" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -17510,24 +17551,24 @@
       <c r="A166" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B166" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B166" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -17535,24 +17576,24 @@
       <c r="A167" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B167" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B167" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17560,9 +17601,9 @@
       <c r="A168" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B168" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -17572,12 +17613,12 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -17585,24 +17626,24 @@
       <c r="A169" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B169" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B169" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -17610,9 +17651,9 @@
       <c r="A170" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B170" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B170" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
@@ -17622,12 +17663,12 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -17635,24 +17676,24 @@
       <c r="A171" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B171" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -17660,24 +17701,24 @@
       <c r="A172" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B172" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B172" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -17685,24 +17726,24 @@
       <c r="A173" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B173" s="5" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
@@ -17710,24 +17751,24 @@
       <c r="A174" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
@@ -17735,24 +17776,24 @@
       <c r="A175" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B175" s="5" t="inlineStr">
-        <is>
-          <t>开始</t>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -17760,24 +17801,24 @@
       <c r="A176" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B176" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
@@ -17785,49 +17826,49 @@
       <c r="A177" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B177" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B177" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B178" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B178" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -17842,17 +17883,17 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -17867,17 +17908,17 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -17885,9 +17926,9 @@
       <c r="A181" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B181" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -17897,12 +17938,12 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -17910,9 +17951,9 @@
       <c r="A182" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B182" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B182" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -17922,12 +17963,12 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -17935,24 +17976,24 @@
       <c r="A183" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B183" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -17960,9 +18001,9 @@
       <c r="A184" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B184" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B184" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -17972,12 +18013,12 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -17992,17 +18033,17 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -18010,9 +18051,9 @@
       <c r="A186" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B186" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
@@ -18022,12 +18063,12 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -18047,7 +18088,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
@@ -18060,24 +18101,24 @@
       <c r="A188" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B188" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B188" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18085,24 +18126,24 @@
       <c r="A189" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B189" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -18110,24 +18151,24 @@
       <c r="A190" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B190" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B190" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18142,17 +18183,17 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -18160,19 +18201,19 @@
       <c r="A192" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B192" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
@@ -18185,9 +18226,9 @@
       <c r="A193" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B193" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B193" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -18197,12 +18238,12 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18210,24 +18251,24 @@
       <c r="A194" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B194" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B194" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -18235,9 +18276,9 @@
       <c r="A195" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B195" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B195" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -18247,12 +18288,12 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18260,9 +18301,9 @@
       <c r="A196" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B196" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B196" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -18272,12 +18313,12 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -18285,24 +18326,24 @@
       <c r="A197" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B197" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B197" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18310,24 +18351,24 @@
       <c r="A198" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B198" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -18340,15 +18381,19 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C199" s="4" t="inlineStr"/>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18356,15 +18401,15 @@
       <c r="A200" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B200" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B200" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr"/>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
@@ -18377,20 +18422,20 @@
       <c r="A201" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B201" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B201" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr"/>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -18403,19 +18448,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C202" s="4" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="C202" s="4" t="inlineStr"/>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -18430,12 +18471,12 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
@@ -18455,12 +18496,12 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
@@ -18480,12 +18521,12 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
@@ -18505,12 +18546,12 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
@@ -18530,17 +18571,17 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18548,24 +18589,24 @@
       <c r="A208" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B208" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B208" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
@@ -18573,18 +18614,43 @@
       <c r="A209" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B209" s="23" t="inlineStr">
+      <c r="B209" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B210" s="23" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C209" s="4" t="inlineStr"/>
-      <c r="D209" s="4" t="inlineStr">
+      <c r="C210" s="4" t="inlineStr"/>
+      <c r="D210" s="4" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E209" s="4" t="inlineStr">
+      <c r="E210" s="4" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -23327,7 +23393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23371,7 +23437,7 @@
         <v>46307</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>5</v>
@@ -23385,7 +23451,7 @@
         <v>46308</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>7</v>
@@ -23399,7 +23465,7 @@
         <v>46309</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>8</v>
@@ -23413,7 +23479,7 @@
         <v>46310</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>12</v>
@@ -23427,7 +23493,7 @@
         <v>46311</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>20</v>
@@ -23441,7 +23507,7 @@
         <v>46312</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>28</v>
@@ -23455,7 +23521,7 @@
         <v>46313</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>28</v>
@@ -23469,7 +23535,7 @@
         <v>46314</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>32</v>
@@ -23483,13 +23549,13 @@
         <v>46315</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
@@ -23497,10 +23563,10 @@
         <v>46316</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="5" t="n"/>
     </row>
@@ -23509,10 +23575,10 @@
         <v>46317</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" s="5" t="n"/>
     </row>
@@ -23521,10 +23587,10 @@
         <v>46318</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="5" t="n"/>
     </row>
@@ -23533,10 +23599,10 @@
         <v>46319</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="5" t="n"/>
     </row>
@@ -25812,6 +25878,44 @@
       <c r="H83" s="4" t="inlineStr">
         <is>
           <t>dr1v90 f3f384c (5/5 QSPI 启动 + 坏镜像回退 TF; 慢 7.6 s; Linux 写 QSPI 失效走 u-boot; 03 已回 TF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>D48</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>V2 双面全链路系统仿真 (PC→主控→桥→2260 模型)</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>2;3</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>2期</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>dr1v90 fca9830 (三档 3 内容 两面像素 249 万 / 上行 53 万组 0 错; 反例全抓)</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-20.xlsx
+++ b/docs/progress/显性目的进度_2026-10-20.xlsx
@@ -8580,7 +8580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I135"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8752,16 +8752,16 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
+          <t>21/24</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
           <t>20/23</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>19/22</t>
-        </is>
-      </c>
       <c r="E6" s="9" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -9318,16 +9318,16 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
@@ -11874,31 +11874,35 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>D46</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>1.2G 可能过不了</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr"/>
-      <c r="G96" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+          <t>V2 桥补齐 面 B + 1.2G PRBS 误码档 (comm_check --phase v2)</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 必须</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H96" s="12" t="n">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
+          <t>V2 桥板引脚 + V2 主控 PRBS 位流</t>
         </is>
       </c>
     </row>
@@ -11910,38 +11914,38 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 主控位流</t>
+          <t>V2 192×216 · T2 板/1.2G 上行</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>风险</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>V2 主控位流跟上主线 (p2_ul1200_b12_v3)</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>V2 · 必须</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>1.2G 可能过不了</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr"/>
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H97" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I97" s="4" t="inlineStr"/>
+        <v>46308</v>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -11961,12 +11965,12 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>D44</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>V2 双面主控位流 (片上 RAM/时序评估)</t>
+          <t>V2 主控位流跟上主线 (p2_ul1200_b12_v3)</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -11980,7 +11984,7 @@
         </is>
       </c>
       <c r="H98" s="12" t="n">
-        <v>46315</v>
+        <v>46311</v>
       </c>
       <c r="I98" s="4" t="inlineStr"/>
     </row>
@@ -11992,7 +11996,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 面板映射/后端</t>
+          <t>V2 192×216 · 主控位流</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -12002,12 +12006,12 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>V2-3</t>
+          <t>D44</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>2 期 192×216 面板映射</t>
+          <t>V2 双面主控位流 (片上 RAM/时序评估)</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -12021,7 +12025,7 @@
         </is>
       </c>
       <c r="H99" s="12" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I99" s="4" t="inlineStr"/>
     </row>
@@ -12043,12 +12047,12 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>V2-7</t>
+          <t>V2-3</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>板端 voxslice --disp p2 (2 期后端)</t>
+          <t>2 期 192×216 面板映射</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -12084,12 +12088,12 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>D48</t>
+          <t>V2-7</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>V2 双面全链路系统仿真 (PC→主控→桥→2260 模型)</t>
+          <t>板端 voxslice --disp p2 (2 期后端)</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -12103,7 +12107,7 @@
         </is>
       </c>
       <c r="H101" s="12" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I101" s="4" t="inlineStr"/>
     </row>
@@ -12115,7 +12119,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 整机</t>
+          <t>V2 192×216 · 面板映射/后端</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -12125,12 +12129,12 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>V2-4</t>
+          <t>D48</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>2 期 30 Hz 整机上转子</t>
+          <t>V2 双面全链路系统仿真 (PC→主控→桥→2260 模型)</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -12138,17 +12142,15 @@
           <t>V2 · 必须</t>
         </is>
       </c>
-      <c r="G102" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H102" s="12" t="n"/>
-      <c r="I102" s="4" t="inlineStr">
-        <is>
-          <t>等 T2 板 (V2-1) + 1.2G 上行 (V2-2)</t>
-        </is>
-      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="I102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -12158,36 +12160,38 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>画面指标 (各期)</t>
+          <t>V2 192×216 · 整机</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>KR1.6</t>
+          <t>V2-4</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>内容刷新率 (实转上屏) (最新 10.8 fps)</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr"/>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1⬜ V2⬜</t>
-        </is>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>46307</v>
-      </c>
+          <t>2 期 30 Hz 整机上转子</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 必须</t>
+        </is>
+      </c>
+      <c r="G103" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="n"/>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>等 V1 整机 720 RPM 实转 (验证板 11-10 回板)</t>
+          <t>等 T2 板 (V2-1) + 1.2G 上行 (V2-2)</t>
         </is>
       </c>
     </row>
@@ -12209,18 +12213,18 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>KR2.1</t>
+          <t>KR1.6</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>体帧率 (最新 21.7 Hz)</t>
+          <t>内容刷新率 (实转上屏) (最新 10.8 fps)</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr"/>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1🔵 V2⬜</t>
+          <t>V0✅ V1⬜ V2⬜</t>
         </is>
       </c>
       <c r="H104" s="12" t="n">
@@ -12228,7 +12232,7 @@
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>等 V1 回板实转 720 RPM×358 片</t>
+          <t>等 V1 整机 720 RPM 实转 (验证板 11-10 回板)</t>
         </is>
       </c>
     </row>
@@ -12250,18 +12254,18 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>KR3.1</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>每面像素数 (最新 28800 px)</t>
+          <t>体帧率 (最新 21.7 Hz)</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr"/>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1✅ V2⬜</t>
+          <t>V0✅ V1🔵 V2⬜</t>
         </is>
       </c>
       <c r="H105" s="12" t="n">
@@ -12269,7 +12273,7 @@
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>等 2 期 192×216 屏</t>
+          <t>等 V1 回板实转 720 RPM×358 片</t>
         </is>
       </c>
     </row>
@@ -12291,18 +12295,18 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>KR3.2</t>
+          <t>KR3.1</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>每圈片数 (最新 142 片)</t>
+          <t>每面像素数 (最新 28800 px)</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr"/>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1🔵 V2⬜</t>
+          <t>V0✅ V1✅ V2⬜</t>
         </is>
       </c>
       <c r="H106" s="12" t="n">
@@ -12310,7 +12314,7 @@
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>等 V1 回板实测</t>
+          <t>等 2 期 192×216 屏</t>
         </is>
       </c>
     </row>
@@ -12332,18 +12336,18 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>KR4.1</t>
+          <t>KR3.2</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>色深 (最新 3 bit/通道)</t>
+          <t>每圈片数 (最新 142 片)</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1🔵 V2🔵</t>
+          <t>V0✅ V1🔵 V2⬜</t>
         </is>
       </c>
       <c r="H107" s="12" t="n">
@@ -12351,50 +12355,50 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>等 V1 2260 回板上屏</t>
+          <t>等 V1 回板实测</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>④ 运维保障</t>
+          <t>③ 显示 (按期换后端)</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>开机即用</t>
+          <t>画面指标 (各期)</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>KR4.1</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>开机自动演示 + 转速门控</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>色深 (最新 3 bit/通道)</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr"/>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1🔵 V2🔵</t>
         </is>
       </c>
       <c r="H108" s="12" t="n">
         <v>46307</v>
       </c>
-      <c r="I108" s="4" t="inlineStr"/>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>等 V1 2260 回板上屏</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -12414,12 +12418,12 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>启动提速 + 启动屏显 (含原 backlog B1)</t>
+          <t>开机自动演示 + 转速门控</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
@@ -12433,7 +12437,7 @@
         </is>
       </c>
       <c r="H109" s="12" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="I109" s="4" t="inlineStr"/>
     </row>
@@ -12455,12 +12459,12 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>开机默认动画 = 立方体动图 (用户 10-16 提)</t>
+          <t>启动提速 + 启动屏显 (含原 backlog B1)</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -12474,7 +12478,7 @@
         </is>
       </c>
       <c r="H110" s="12" t="n">
-        <v>46311</v>
+        <v>46309</v>
       </c>
       <c r="I110" s="4" t="inlineStr"/>
     </row>
@@ -12496,17 +12500,17 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>D47</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>系统从 QSPI 加载 (去 TF/eMMC 准备; 03 板试)</t>
+          <t>开机默认动画 = 立方体动图 (用户 10-16 提)</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>V2 · 加分</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
@@ -12515,13 +12519,9 @@
         </is>
       </c>
       <c r="H111" s="12" t="n">
-        <v>46315</v>
-      </c>
-      <c r="I111" s="4" t="inlineStr">
-        <is>
-          <t>T2 板 QSPI 选 64MiB / 厂商驱动提速</t>
-        </is>
-      </c>
+        <v>46311</v>
+      </c>
+      <c r="I111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12536,29 +12536,37 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>KR8.1</t>
+          <t>D47</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>上电到 0° 片亮起 (停转) (最新 12.4 s)</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr"/>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>系统从 QSPI 加载 (去 TF/eMMC 准备; 03 板试)</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 加分</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H112" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I112" s="4" t="inlineStr"/>
+        <v>46315</v>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>T2 板 QSPI 选 64MiB / 厂商驱动提速</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12578,22 +12586,22 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>KR8.4</t>
+          <t>KR8.1</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>上电到转稳全亮 (最新 26 s)</t>
+          <t>上电到 0° 片亮起 (停转) (最新 12.4 s)</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>V0— V1— V2—</t>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H113" s="12" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="I113" s="4" t="inlineStr"/>
     </row>
@@ -12605,32 +12613,28 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>联网/找板/自愈</t>
+          <t>开机即用</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>KR8.4</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>开机自连 WiFi</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>上电到转稳全亮 (最新 26 s)</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>V0— V1— V2—</t>
         </is>
       </c>
       <c r="H114" s="12" t="n">
@@ -12656,12 +12660,12 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS)</t>
+          <t>开机自连 WiFi</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
@@ -12675,7 +12679,7 @@
         </is>
       </c>
       <c r="H115" s="12" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="I115" s="4" t="inlineStr"/>
     </row>
@@ -12697,12 +12701,12 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 (服务监护/看门狗/兜底热点/povnetd 1.2)</t>
+          <t>按名字找板 (mDNS)</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -12716,7 +12720,7 @@
         </is>
       </c>
       <c r="H116" s="12" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="I116" s="4" t="inlineStr"/>
     </row>
@@ -12738,12 +12742,12 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复 ≤30 s (03 长跑断 155 s)</t>
+          <t>不插串口永远连得上 (服务监护/看门狗/兜底热点/povnetd 1.2)</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
@@ -12757,7 +12761,7 @@
         </is>
       </c>
       <c r="H117" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I117" s="4" t="inlineStr"/>
     </row>
@@ -12779,12 +12783,12 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>D43</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>povnetd 1.3 网络自愈回归修复</t>
+          <t>WiFi 断线恢复 ≤30 s (03 长跑断 155 s)</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -12815,27 +12819,31 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>KR8.2</t>
+          <t>D43</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>按名字找到板子 (最新 19.8 s)</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr"/>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>povnetd 1.3 网络自愈回归修复</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 必须</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H119" s="12" t="n">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="I119" s="4" t="inlineStr"/>
     </row>
@@ -12847,32 +12855,28 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>远程运维/升级 (含 JTAG 灌桥)</t>
+          <t>联网/找板/自愈</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR8.2</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>转子运维 (netguard-lite / 遥测 / 远程升级)</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G120" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>按名字找到板子 (最新 19.8 s)</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr"/>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H120" s="12" t="n">
@@ -12898,17 +12902,17 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>主控经 JTAG 给桥灌位流 (V1 远程升级软件)</t>
+          <t>转子运维 (netguard-lite / 遥测 / 远程升级)</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
@@ -12917,7 +12921,7 @@
         </is>
       </c>
       <c r="H121" s="12" t="n">
-        <v>46314</v>
+        <v>46309</v>
       </c>
       <c r="I121" s="4" t="inlineStr"/>
     </row>
@@ -12939,17 +12943,17 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>D42</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>03 板软件跟进主线</t>
+          <t>主控经 JTAG 给桥灌位流 (V1 远程升级软件)</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>V0 · 加分</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
@@ -12975,27 +12979,31 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>KR8.3</t>
+          <t>D42</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>需要串口 (1=需要) (最新 0 是/否)</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr"/>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>03 板软件跟进主线</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H123" s="12" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="I123" s="4" t="inlineStr"/>
     </row>
@@ -13017,12 +13025,12 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>KR8.3</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用) (最新 1 是/否)</t>
+          <t>需要串口 (1=需要) (最新 0 是/否)</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr"/>
@@ -13032,7 +13040,7 @@
         </is>
       </c>
       <c r="H124" s="12" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="I124" s="4" t="inlineStr"/>
     </row>
@@ -13054,12 +13062,12 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>KR9.2</t>
+          <t>KR9.1</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>远程升级失败自动回滚 (1=有) (最新 1 是/否)</t>
+          <t>转子遥测可用 (1=可用) (最新 1 是/否)</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr"/>
@@ -13081,40 +13089,34 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>主控↔桥通信</t>
+          <t>远程运维/升级 (含 JTAG 灌桥)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>KR9.2</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>C1 台架彩排 + 1.2G 误码测试</t>
-        </is>
-      </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>V1准备 · 加分</t>
-        </is>
-      </c>
-      <c r="G126" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H126" s="12" t="n"/>
-      <c r="I126" s="4" t="inlineStr">
-        <is>
-          <t>不做 (用户 10-19 定), 由 D39 到板 comm_check 代替</t>
-        </is>
-      </c>
+          <t>远程升级失败自动回滚 (1=有) (最新 1 是/否)</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr"/>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -13134,28 +13136,30 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信全功能 (配置/状态/错误恢复/升级)</t>
+          <t>C1 台架彩排 + 1.2G 误码测试</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H127" s="12" t="n">
-        <v>46312</v>
-      </c>
-      <c r="I127" s="4" t="inlineStr"/>
+          <t>V1准备 · 加分</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="n"/>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t>不做 (用户 10-19 定), 由 D39 到板 comm_check 代替</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -13175,12 +13179,12 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 + PRBS 位流</t>
+          <t>SoC↔桥通信全功能 (配置/状态/错误恢复/升级)</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
@@ -13194,7 +13198,7 @@
         </is>
       </c>
       <c r="H128" s="12" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="I128" s="4" t="inlineStr"/>
     </row>
@@ -13206,7 +13210,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>可靠性验证 (冷启动/长跑)</t>
+          <t>主控↔桥通信</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
@@ -13216,17 +13220,17 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>V0A</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>V0 重启验收 (不插串口: 找回/守护/开机默认/WiFi/推流/稳定 6 项)</t>
+          <t>SoC↔桥通信专项验证包 + PRBS 位流</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>V0 · 必须</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
@@ -13235,7 +13239,7 @@
         </is>
       </c>
       <c r="H129" s="12" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="I129" s="4" t="inlineStr"/>
     </row>
@@ -13257,12 +13261,12 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>V0A</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>冷启动认不到 TF 卡 (03 停在 u-boot)</t>
+          <t>V0 重启验收 (不插串口: 找回/守护/开机默认/WiFi/推流/稳定 6 项)</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -13276,7 +13280,7 @@
         </is>
       </c>
       <c r="H130" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I130" s="4" t="inlineStr"/>
     </row>
@@ -13298,17 +13302,17 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>D49</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+          <t>冷启动认不到 TF 卡 (03 停在 u-boot)</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>V0 · 加分</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
@@ -13317,7 +13321,7 @@
         </is>
       </c>
       <c r="H131" s="12" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I131" s="4" t="inlineStr"/>
     </row>
@@ -13334,27 +13338,31 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D49</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr"/>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H132" s="12" t="n">
-        <v>46312</v>
+        <v>46315</v>
       </c>
       <c r="I132" s="4" t="inlineStr"/>
     </row>
@@ -13376,12 +13384,12 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
+          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr"/>
@@ -13391,7 +13399,7 @@
         </is>
       </c>
       <c r="H133" s="12" t="n">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="I133" s="4" t="inlineStr"/>
     </row>
@@ -13408,33 +13416,29 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
+          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr"/>
-      <c r="G134" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H134" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I134" s="4" t="inlineStr">
-        <is>
-          <t>T2 板留 eMMC、打胶</t>
-        </is>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="I134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -13444,7 +13448,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>开发环境</t>
+          <t>可靠性验证 (冷启动/长跑)</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
@@ -13454,24 +13458,65 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>D 盘 EIO（IP-guard 驱动）</t>
+          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr"/>
-      <c r="G135" s="8" t="inlineStr">
-        <is>
-          <t>监控</t>
+      <c r="G135" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H135" s="12" t="n">
         <v>46308</v>
       </c>
       <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>T2 板留 eMMC、打胶</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>④ 运维保障</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>开发环境</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>风险</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>D 盘 EIO（IP-guard 驱动）</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr"/>
+      <c r="G136" s="8" t="inlineStr">
+        <is>
+          <t>监控</t>
+        </is>
+      </c>
+      <c r="H136" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
         <is>
           <t>看门狗自动重挂 + 构建放 WSL 本地盘</t>
         </is>
@@ -13491,7 +13536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J210"/>
+  <dimension ref="A1:J211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13626,16 +13671,16 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>0.868421052631579</v>
+        <v>0.8701298701298701</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>66/76</t>
+          <t>67/77</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>KR 17/24 + 交付 49/52 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 17/24 + 交付 50/53 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="17" t="n">
@@ -13772,7 +13817,7 @@
         <v>0.9118000000000001</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8701</v>
       </c>
     </row>
     <row r="13">
@@ -14824,26 +14869,26 @@
     </row>
     <row r="57">
       <c r="A57" s="12" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46315</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>D46</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
+          <t>V2 桥 p2b (面 B) + p2p (1.2G PRBS) 三档 0 违例, comm_check 支持 --phase v2 (离线演练 85/0); sbd 兼容规则补 V2 36 像素/行; 主会话复跑 16/0; 待 V2 主控 PRBS 位流 + 桥引脚</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d22_reach/README.md</t>
+          <t>dr1v90</t>
         </is>
       </c>
     </row>
@@ -14851,24 +14896,24 @@
       <c r="A58" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>D32</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
+          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>dr1v90</t>
+          <t>dr1v90 d22_reach/README.md</t>
         </is>
       </c>
     </row>
@@ -14876,9 +14921,9 @@
       <c r="A59" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -14888,12 +14933,12 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
+          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/acc32_*.log</t>
+          <t>dr1v90</t>
         </is>
       </c>
     </row>
@@ -14901,24 +14946,24 @@
       <c r="A60" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B60" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
+          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>progress/v0_accept/acc32_*.log</t>
         </is>
       </c>
     </row>
@@ -14926,24 +14971,24 @@
       <c r="A61" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>补录</t>
+      <c r="B61" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>KR4.2</t>
+          <t>用户</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
+          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -14953,22 +14998,22 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>补录</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
+          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -14978,22 +15023,22 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
+          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 card03</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15003,22 +15048,22 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
+          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2b111f0</t>
+          <t>dr1v90 card03</t>
         </is>
       </c>
     </row>
@@ -15028,22 +15073,22 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
+          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
+          <t>dr1v90 2b111f0</t>
         </is>
       </c>
     </row>
@@ -15051,24 +15096,24 @@
       <c r="A66" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B66" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
+          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
         </is>
       </c>
     </row>
@@ -15076,24 +15121,24 @@
       <c r="A67" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
+          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 97a10cf</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15103,22 +15148,22 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
+          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 7253608</t>
+          <t>dr1v90 97a10cf</t>
         </is>
       </c>
     </row>
@@ -15126,24 +15171,24 @@
       <c r="A69" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D34</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
+          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 7253608</t>
         </is>
       </c>
     </row>
@@ -15151,24 +15196,24 @@
       <c r="A70" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B70" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
+          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 23474c7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15183,17 +15228,17 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
+          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 f2584d9</t>
+          <t>dr1v90 23474c7</t>
         </is>
       </c>
     </row>
@@ -15208,17 +15253,17 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>D38</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
+          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ad201f9</t>
+          <t>dr1v90 f2584d9</t>
         </is>
       </c>
     </row>
@@ -15228,22 +15273,22 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>V1主控</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
+          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>本机构建</t>
+          <t>dr1v90 ad201f9</t>
         </is>
       </c>
     </row>
@@ -15258,17 +15303,17 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V1主控</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
+          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d39-comm b69f6d8</t>
+          <t>本机构建</t>
         </is>
       </c>
     </row>
@@ -15278,22 +15323,22 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>V2-7</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
+          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ff1846a</t>
+          <t>dr1v90 task/d39-comm b69f6d8</t>
         </is>
       </c>
     </row>
@@ -15308,17 +15353,17 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V2-7</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
+          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3ef6b06</t>
+          <t>dr1v90 ff1846a</t>
         </is>
       </c>
     </row>
@@ -15328,22 +15373,22 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
+          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>progress/d29_coldboot</t>
+          <t>dr1v90 3ef6b06</t>
         </is>
       </c>
     </row>
@@ -15351,24 +15396,24 @@
       <c r="A78" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B78" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>D11;D39</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
+          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>用户 10-19</t>
+          <t>progress/d29_coldboot</t>
         </is>
       </c>
     </row>
@@ -15376,24 +15421,24 @@
       <c r="A79" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B79" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D11;D39</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
+          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6333eb5</t>
+          <t>用户 10-19</t>
         </is>
       </c>
     </row>
@@ -15408,67 +15453,67 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>D42;D43</t>
+          <t>D41</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
+          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 8689db2 / 6e6d47b</t>
+          <t>dr1v90 6333eb5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D42;D43</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
+          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1017_03_24h</t>
+          <t>dr1v90 8689db2 / 6e6d47b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46313</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
+          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/SPEC.md</t>
+          <t>progress/soak_v0/1017_03_24h</t>
         </is>
       </c>
     </row>
@@ -15476,24 +15521,24 @@
       <c r="A83" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>V2-5</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
+          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_fmt/README.md</t>
+          <t>dr1v90 d27_link/SPEC.md</t>
         </is>
       </c>
     </row>
@@ -15508,17 +15553,17 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>D28b</t>
+          <t>V2-5</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
+          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/回板当天.md</t>
+          <t>dr1v90 v2_fmt/README.md</t>
         </is>
       </c>
     </row>
@@ -15526,24 +15571,24 @@
       <c r="A85" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>进展</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>D27b</t>
+          <t>D28b</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
+          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/README.md</t>
+          <t>dr1v90 v1_bringup/回板当天.md</t>
         </is>
       </c>
     </row>
@@ -15551,24 +15596,24 @@
       <c r="A86" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>V2-6</t>
+          <t>D27b</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
+          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 gw5a_bridge/p2/README.md</t>
+          <t>dr1v90 d27_link/README.md</t>
         </is>
       </c>
     </row>
@@ -15578,22 +15623,22 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>全套</t>
+          <t>V2-6</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
+          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ~/full_*.log</t>
+          <t>dr1v90 gw5a_bridge/p2/README.md</t>
         </is>
       </c>
     </row>
@@ -15603,22 +15648,22 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>修复</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>全套</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
+          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 slice/SPEC.md §13.2</t>
+          <t>dr1v90 ~/full_*.log</t>
         </is>
       </c>
     </row>
@@ -15628,22 +15673,22 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
+          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1016_wkend_24h</t>
+          <t>dr1v90 slice/SPEC.md §13.2</t>
         </is>
       </c>
     </row>
@@ -15653,7 +15698,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -15663,37 +15708,37 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
+          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1017_*.log</t>
+          <t>progress/soak_v0/1016_wkend_24h</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>部署</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
+          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22c.board.log</t>
+          <t>progress/v0_accept/accept_1017_*.log</t>
         </is>
       </c>
     </row>
@@ -15701,9 +15746,9 @@
       <c r="A92" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -15713,12 +15758,12 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
+          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d22c.board.log</t>
         </is>
       </c>
     </row>
@@ -15726,24 +15771,24 @@
       <c r="A93" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
+          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board5.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15751,9 +15796,9 @@
       <c r="A94" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -15763,12 +15808,12 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
+          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d21.board5.log</t>
         </is>
       </c>
     </row>
@@ -15783,12 +15828,12 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
+          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -15801,9 +15846,9 @@
       <c r="A96" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -15813,12 +15858,12 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
+          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_A fps_B</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15826,9 +15871,9 @@
       <c r="A97" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -15838,12 +15883,12 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
+          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_C</t>
+          <t>soak_runs/fps_A fps_B</t>
         </is>
       </c>
     </row>
@@ -15851,24 +15896,24 @@
       <c r="A98" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
+          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20d-ackrps db4ec93</t>
+          <t>soak_runs/fps_C</t>
         </is>
       </c>
     </row>
@@ -15883,17 +15928,17 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
+          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
+          <t>dr1v90 task/d20d-ackrps db4ec93</t>
         </is>
       </c>
     </row>
@@ -15903,22 +15948,22 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
+          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_D</t>
+          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
         </is>
       </c>
     </row>
@@ -15926,9 +15971,9 @@
       <c r="A101" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -15938,12 +15983,12 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
+          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>soak_runs/fps_D</t>
         </is>
       </c>
     </row>
@@ -15951,24 +15996,24 @@
       <c r="A102" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
+          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>~/rv_deploy.board.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15976,24 +16021,24 @@
       <c r="A103" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
+          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_deploy.board.log</t>
         </is>
       </c>
     </row>
@@ -16001,24 +16046,24 @@
       <c r="A104" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>验收</t>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
+          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16028,22 +16073,22 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>开工</t>
+          <t>验收</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>D20e/D23</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
+          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
+          <t>progress/v0_accept/</t>
         </is>
       </c>
     </row>
@@ -16051,24 +16096,24 @@
       <c r="A106" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B106" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>开工</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D20e/D23</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
+          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
         </is>
       </c>
     </row>
@@ -16076,24 +16121,24 @@
       <c r="A107" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B107" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
+          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -16108,12 +16153,12 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
+          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -16126,24 +16171,24 @@
       <c r="A109" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
+          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1016_d20e.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16151,24 +16196,24 @@
       <c r="A110" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>KR7.3/D24</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
+          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>progress/v0_accept/accept_1016_d20e.log</t>
         </is>
       </c>
     </row>
@@ -16176,24 +16221,24 @@
       <c r="A111" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>KR7.3/D24</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
+          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>D:\card03</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16201,24 +16246,24 @@
       <c r="A112" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>D25</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
+          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>D:\card03</t>
         </is>
       </c>
     </row>
@@ -16226,24 +16271,24 @@
       <c r="A113" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D25</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
+          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\cap_COM29.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16258,17 +16303,17 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
+          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20d_ackrps d20c_fps</t>
+          <t>D:\card03\cap_COM29.log</t>
         </is>
       </c>
     </row>
@@ -16276,24 +16321,24 @@
       <c r="A115" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
+          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d12_latency/RESULTS.md</t>
+          <t>dr1v90 d20d_ackrps d20c_fps</t>
         </is>
       </c>
     </row>
@@ -16308,17 +16353,17 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
+          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d9_e2e/</t>
+          <t>dr1v90 d12_latency/RESULTS.md</t>
         </is>
       </c>
     </row>
@@ -16326,24 +16371,24 @@
       <c r="A117" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
+          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\boot03.log</t>
+          <t>dr1v90 d9_e2e/</t>
         </is>
       </c>
     </row>
@@ -16351,24 +16396,24 @@
       <c r="A118" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
+          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
+          <t>D:\card03\boot03.log</t>
         </is>
       </c>
     </row>
@@ -16376,24 +16421,24 @@
       <c r="A119" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>开工</t>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
+          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
+          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
         </is>
       </c>
     </row>
@@ -16403,22 +16448,22 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>方案</t>
+          <t>开工</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
+          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d29_sdboot/PLAN.md</t>
+          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
         </is>
       </c>
     </row>
@@ -16426,24 +16471,24 @@
       <c r="A121" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B121" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>方案</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
+          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/</t>
+          <t>dr1v90 d29_sdboot/PLAN.md</t>
         </is>
       </c>
     </row>
@@ -16451,24 +16496,24 @@
       <c r="A122" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>修复</t>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
+          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
+          <t>dr1v90 v1_bringup/</t>
         </is>
       </c>
     </row>
@@ -16478,22 +16523,22 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>进展</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>V2-3</t>
+          <t>D30</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
+          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_map/DESIGN.md</t>
+          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
         </is>
       </c>
     </row>
@@ -16503,47 +16548,47 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>评估</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>V2-3</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
+          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d31_v1odd/REPORT.md</t>
+          <t>dr1v90 v2_map/DESIGN.md</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="12" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B125" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46311</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>评估</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D31</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
+          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/report.md</t>
+          <t>dr1v90 d31_v1odd/REPORT.md</t>
         </is>
       </c>
     </row>
@@ -16551,24 +16596,24 @@
       <c r="A126" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>QoS</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
+          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>~/qos_runs</t>
+          <t>progress/soak_v0/report.md</t>
         </is>
       </c>
     </row>
@@ -16583,17 +16628,17 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>D16b</t>
+          <t>QoS</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
+          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16b-tile 7936b7e</t>
+          <t>~/qos_runs</t>
         </is>
       </c>
     </row>
@@ -16601,24 +16646,24 @@
       <c r="A128" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B128" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D16b</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
+          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>dr1v90 task/d16b-tile 7936b7e</t>
         </is>
       </c>
     </row>
@@ -16633,12 +16678,12 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
+          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -16651,24 +16696,24 @@
       <c r="A130" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B130" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>V1/V2</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
+          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>budget/rpm_range_2026-10-15.md</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -16676,24 +16721,24 @@
       <c r="A131" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>V1/V2</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
+          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>progress/realspin_v0/</t>
+          <t>budget/rpm_range_2026-10-15.md</t>
         </is>
       </c>
     </row>
@@ -16701,19 +16746,19 @@
       <c r="A132" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
+          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -16726,24 +16771,24 @@
       <c r="A133" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
+          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20-smooth 83a5fd7</t>
+          <t>progress/realspin_v0/</t>
         </is>
       </c>
     </row>
@@ -16751,24 +16796,24 @@
       <c r="A134" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
+          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 e215176</t>
+          <t>dr1v90 task/d20-smooth 83a5fd7</t>
         </is>
       </c>
     </row>
@@ -16776,24 +16821,24 @@
       <c r="A135" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
+          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d19-halfrev 1beafa6</t>
+          <t>dr1v90 e215176</t>
         </is>
       </c>
     </row>
@@ -16808,17 +16853,17 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>D20b</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
+          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20b-sim 9081f62</t>
+          <t>dr1v90 task/d19-halfrev 1beafa6</t>
         </is>
       </c>
     </row>
@@ -16828,22 +16873,22 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D20b</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
+          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/merge-d19-d20 106364e</t>
+          <t>dr1v90 task/d20b-sim 9081f62</t>
         </is>
       </c>
     </row>
@@ -16851,24 +16896,24 @@
       <c r="A138" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B138" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>D19/D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
+          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/merge-d19-d20 106364e</t>
         </is>
       </c>
     </row>
@@ -16876,24 +16921,24 @@
       <c r="A139" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D19/D20</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
+          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband adeba44</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16903,22 +16948,22 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>D20/D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
+          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>~/realspin/tcp</t>
+          <t>dr1v90 task/d21-nband adeba44</t>
         </is>
       </c>
     </row>
@@ -16926,24 +16971,24 @@
       <c r="A141" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B141" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D20/D22</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
+          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>~/realspin/tcp</t>
         </is>
       </c>
     </row>
@@ -16951,9 +16996,9 @@
       <c r="A142" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B142" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -16963,12 +17008,12 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
+          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach ee4a55c</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -16983,17 +17028,17 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
+          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20c-fps 338eaaf</t>
+          <t>dr1v90 task/d22-reach ee4a55c</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17048,7 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>复验</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -17013,12 +17058,12 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
+          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d20c.v.log</t>
+          <t>dr1v90 task/d20c-fps 338eaaf</t>
         </is>
       </c>
     </row>
@@ -17028,22 +17073,22 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>复验</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
+          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d8-cosim 85dfe51</t>
+          <t>~/rv_d20c.v.log</t>
         </is>
       </c>
     </row>
@@ -17051,9 +17096,9 @@
       <c r="A146" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B146" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -17063,12 +17108,12 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
+          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/d8-cosim 85dfe51</t>
         </is>
       </c>
     </row>
@@ -17076,24 +17121,24 @@
       <c r="A147" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B147" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>D22/D20</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
+          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/netdiag_1015_1814</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -17101,24 +17146,24 @@
       <c r="A148" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B148" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22/D20</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
+          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board.log</t>
+          <t>soak_runs/netdiag_1015_1814</t>
         </is>
       </c>
     </row>
@@ -17133,17 +17178,17 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
+          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach</t>
+          <t>~/rv_d21.board.log</t>
         </is>
       </c>
     </row>
@@ -17163,7 +17208,7 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
+          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -17176,9 +17221,9 @@
       <c r="A151" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B151" s="5" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B151" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -17188,12 +17233,12 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
+          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22.board2.log</t>
+          <t>dr1v90 task/d22-reach</t>
         </is>
       </c>
     </row>
@@ -17203,22 +17248,22 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
+          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>~/d21b_forensic.log</t>
+          <t>~/rv_d22.board2.log</t>
         </is>
       </c>
     </row>
@@ -17233,17 +17278,17 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
+          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach 0d1da09</t>
+          <t>~/d21b_forensic.log</t>
         </is>
       </c>
     </row>
@@ -17253,7 +17298,7 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -17263,12 +17308,12 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
+          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22b.board.log</t>
+          <t>dr1v90 task/d22-reach 0d1da09</t>
         </is>
       </c>
     </row>
@@ -17278,7 +17323,7 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -17288,12 +17333,12 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
+          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach e438a12</t>
+          <t>~/rv_d22b.board.log</t>
         </is>
       </c>
     </row>
@@ -17303,47 +17348,47 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
+          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband 084bba3</t>
+          <t>dr1v90 task/d22-reach e438a12</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B157" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>dr1v90 task/d21-nband 084bba3</t>
         </is>
       </c>
     </row>
@@ -17351,24 +17396,24 @@
       <c r="A158" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B158" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -17376,24 +17421,24 @@
       <c r="A159" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B159" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B159" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -17413,7 +17458,7 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
@@ -17426,24 +17471,24 @@
       <c r="A161" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B161" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B161" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -17451,24 +17496,24 @@
       <c r="A162" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B162" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B162" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -17476,9 +17521,9 @@
       <c r="A163" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B163" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B163" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -17488,12 +17533,12 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -17501,9 +17546,9 @@
       <c r="A164" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B164" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B164" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -17513,12 +17558,12 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -17526,24 +17571,24 @@
       <c r="A165" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B165" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17551,24 +17596,24 @@
       <c r="A166" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B166" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -17576,24 +17621,24 @@
       <c r="A167" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B167" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B167" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -17601,24 +17646,24 @@
       <c r="A168" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B168" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B168" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17626,9 +17671,9 @@
       <c r="A169" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B169" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -17638,12 +17683,12 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -17651,24 +17696,24 @@
       <c r="A170" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B170" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B170" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -17676,9 +17721,9 @@
       <c r="A171" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B171" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B171" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -17688,12 +17733,12 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -17701,24 +17746,24 @@
       <c r="A172" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B172" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -17726,24 +17771,24 @@
       <c r="A173" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B173" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B173" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -17751,24 +17796,24 @@
       <c r="A174" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B174" s="5" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
@@ -17776,24 +17821,24 @@
       <c r="A175" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B175" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
@@ -17801,24 +17846,24 @@
       <c r="A176" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B176" s="5" t="inlineStr">
-        <is>
-          <t>开始</t>
+      <c r="B176" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -17826,24 +17871,24 @@
       <c r="A177" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B177" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
@@ -17851,49 +17896,49 @@
       <c r="A178" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B178" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B178" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B179" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -17908,17 +17953,17 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -17933,17 +17978,17 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -17951,9 +17996,9 @@
       <c r="A182" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B182" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -17963,12 +18008,12 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -17976,9 +18021,9 @@
       <c r="A183" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B183" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B183" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -17988,12 +18033,12 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -18001,24 +18046,24 @@
       <c r="A184" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B184" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -18026,9 +18071,9 @@
       <c r="A185" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B185" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B185" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -18038,12 +18083,12 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18058,17 +18103,17 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -18076,9 +18121,9 @@
       <c r="A187" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B187" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -18088,12 +18133,12 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -18113,7 +18158,7 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
@@ -18126,24 +18171,24 @@
       <c r="A189" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B189" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B189" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18151,24 +18196,24 @@
       <c r="A190" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B190" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -18176,24 +18221,24 @@
       <c r="A191" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B191" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B191" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18208,17 +18253,17 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -18226,19 +18271,19 @@
       <c r="A193" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B193" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
@@ -18251,9 +18296,9 @@
       <c r="A194" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B194" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B194" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -18263,12 +18308,12 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18276,24 +18321,24 @@
       <c r="A195" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B195" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B195" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -18301,9 +18346,9 @@
       <c r="A196" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B196" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B196" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -18313,12 +18358,12 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18326,9 +18371,9 @@
       <c r="A197" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B197" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B197" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -18338,12 +18383,12 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -18351,24 +18396,24 @@
       <c r="A198" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B198" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B198" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18376,24 +18421,24 @@
       <c r="A199" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B199" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -18406,15 +18451,19 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C200" s="4" t="inlineStr"/>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18422,15 +18471,15 @@
       <c r="A201" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B201" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B201" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr"/>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
@@ -18443,20 +18492,20 @@
       <c r="A202" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B202" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B202" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr"/>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -18469,19 +18518,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C203" s="4" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="C203" s="4" t="inlineStr"/>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -18496,12 +18541,12 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
@@ -18521,12 +18566,12 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
@@ -18546,12 +18591,12 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
@@ -18571,12 +18616,12 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
@@ -18596,17 +18641,17 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18614,24 +18659,24 @@
       <c r="A209" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B209" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B209" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
@@ -18639,18 +18684,43 @@
       <c r="A210" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B210" s="23" t="inlineStr">
+      <c r="B210" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B211" s="23" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C210" s="4" t="inlineStr"/>
-      <c r="D210" s="4" t="inlineStr">
+      <c r="C211" s="4" t="inlineStr"/>
+      <c r="D211" s="4" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E210" s="4" t="inlineStr">
+      <c r="E211" s="4" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -23393,7 +23463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23437,7 +23507,7 @@
         <v>46307</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>5</v>
@@ -23451,7 +23521,7 @@
         <v>46308</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>7</v>
@@ -23465,7 +23535,7 @@
         <v>46309</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>8</v>
@@ -23479,7 +23549,7 @@
         <v>46310</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>12</v>
@@ -23493,7 +23563,7 @@
         <v>46311</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>20</v>
@@ -23507,7 +23577,7 @@
         <v>46312</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>28</v>
@@ -23521,7 +23591,7 @@
         <v>46313</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>28</v>
@@ -23535,7 +23605,7 @@
         <v>46314</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>32</v>
@@ -23549,13 +23619,13 @@
         <v>46315</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -23563,10 +23633,10 @@
         <v>46316</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="5" t="n"/>
     </row>
@@ -23575,10 +23645,10 @@
         <v>46317</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="5" t="n"/>
     </row>
@@ -23587,10 +23657,10 @@
         <v>46318</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="5" t="n"/>
     </row>
@@ -23599,10 +23669,10 @@
         <v>46319</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="5" t="n"/>
     </row>
@@ -25916,6 +25986,44 @@
       <c r="H84" s="4" t="inlineStr">
         <is>
           <t>dr1v90 fca9830 (三档 3 内容 两面像素 249 万 / 上行 53 万组 0 错; 反例全抓)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>D46</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>V2 桥补齐 面 B + 1.2G PRBS 误码档 (comm_check --phase v2)</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>2;4;7</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>2期</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>dr1v90 合并 (p2b/p2p 0 违例; d46 verify 16/0; 桥引脚占位)</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-20.xlsx
+++ b/docs/progress/显性目的进度_2026-10-20.xlsx
@@ -8580,7 +8580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I136"/>
+  <dimension ref="A1:I137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>12/12</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
           <t>11/11</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>10/10</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
@@ -10414,29 +10414,37 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>KR1.5</t>
+          <t>D45</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>板上切片耗时 (每帧) (最新 17.3 ms)</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1— V2—</t>
+          <t>前端统一 V2 网格 (V1/V2 共用收包→散写→切片; V1 回板即实测 V2 前端)</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>V1准备 · 必须</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H60" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I60" s="4" t="inlineStr"/>
+        <v>46315</v>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>V1 回板实测 (先看 GEOM_G2 0xC0D8A0B4)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -10446,36 +10454,32 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>转速同步/换档/半圈换帧</t>
+          <t>板上切片 (CPU→PL)</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>KR1.5</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>停转低亮 0° 片</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>板上切片耗时 (每帧) (最新 17.3 ms)</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1— V2—</t>
         </is>
       </c>
       <c r="H61" s="12" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I61" s="4" t="inlineStr"/>
     </row>
@@ -10497,12 +10501,12 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧 (换帧上限 2×转速, 300-1200 rpm)</t>
+          <t>停转低亮 0° 片</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -10516,7 +10520,7 @@
         </is>
       </c>
       <c r="H62" s="12" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="I62" s="4" t="inlineStr"/>
     </row>
@@ -10538,17 +10542,17 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm)</t>
+          <t>半圈换帧 (换帧上限 2×转速, 300-1200 rpm)</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
@@ -10557,7 +10561,7 @@
         </is>
       </c>
       <c r="H63" s="12" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="I63" s="4" t="inlineStr"/>
     </row>
@@ -10579,12 +10583,12 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>D25</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>V1 每圈片数换档 358/286/210 (300-1200 rpm)</t>
+          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -10620,12 +10624,12 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D25</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>V1 奇数档 357/285/209 + 24 Hz 满档 (用户 B1/B2)</t>
+          <t>V1 每圈片数换档 358/286/210 (300-1200 rpm)</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -10639,7 +10643,7 @@
         </is>
       </c>
       <c r="H65" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I65" s="4" t="inlineStr"/>
     </row>
@@ -10656,27 +10660,31 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>KR6.1</t>
+          <t>D34</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>停转自动低亮 (1=有) (最新 1 是/否)</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>V1 奇数档 357/285/209 + 24 Hz 满档 (用户 B1/B2)</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>V1准备 · 必须</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H66" s="12" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="I66" s="4" t="inlineStr"/>
     </row>
@@ -10688,36 +10696,32 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>几何 LUT/校准</t>
+          <t>转速同步/换档/半圈换帧</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>KR6.1</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>几何 LUT + 转起来校准</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>V1准备 · 必须</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>停转自动低亮 (1=有) (最新 1 是/否)</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H67" s="12" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="I67" s="4" t="inlineStr"/>
     </row>
@@ -10734,23 +10738,27 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>KR5.1</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>几何 LUT 复现正确 (1=逐字节复现) (最新 1 是/否)</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>几何 LUT + 转起来校准</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>V1准备 · 必须</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H68" s="12" t="n">
@@ -10776,12 +10784,12 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>KR5.1</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>左右镜像已核实 (1=已核) (最新 1 是/否)</t>
+          <t>几何 LUT 复现正确 (1=逐字节复现) (最新 1 是/否)</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr"/>
@@ -10803,36 +10811,32 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>DDR 带宽</t>
+          <t>几何 LUT/校准</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>16 bit DDR 做到极限 (A 线: 慢读定位/分端口/预取缓冲/兜底)</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 加分</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>左右镜像已核实 (1=已核) (最新 1 是/否)</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H70" s="12" t="n">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="I70" s="4" t="inlineStr"/>
     </row>
@@ -10849,33 +10853,33 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2 期 DDR 带宽：16 bit 余量约 11%，32 bit 像素超限</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+          <t>16 bit DDR 做到极限 (A 线: 慢读定位/分端口/预取缓冲/兜底)</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H71" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>B 线 T2 板 32 bit DDR + PL 读口 ≥200 MHz/分端口</t>
-        </is>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="I71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -10895,18 +10899,18 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>偶发慢读 133 µs &gt; 30 Hz 片窗 110 µs</t>
+          <t>2 期 DDR 带宽：16 bit 余量约 11%，32 bit 像素超限</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr"/>
-      <c r="G72" s="8" t="inlineStr">
-        <is>
-          <t>监控</t>
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H72" s="12" t="n">
@@ -10914,7 +10918,7 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>D16 预取缓冲 + 降争用</t>
+          <t>B 线 T2 板 32 bit DDR + PL 读口 ≥200 MHz/分端口</t>
         </is>
       </c>
     </row>
@@ -10926,38 +10930,38 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>流畅度</t>
+          <t>DDR 带宽</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>风险</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>流畅度检测 + 画面模拟器 (流畅为一等要求)</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>偶发慢读 133 µs &gt; 30 Hz 片窗 110 µs</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>监控</t>
         </is>
       </c>
       <c r="H73" s="12" t="n">
-        <v>46310</v>
-      </c>
-      <c r="I73" s="4" t="inlineStr"/>
+        <v>46308</v>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>D16 预取缓冲 + 降争用</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -10972,23 +10976,27 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>丢帧/迟到率 (最新 0.0012 %)</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr"/>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>流畅度检测 + 画面模拟器 (流畅为一等要求)</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 必须</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H74" s="12" t="n">
@@ -10999,41 +11007,37 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>③ 显示 (按期换后端)</t>
+          <t>② 数据处理</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>V0 2047 · 上屏</t>
+          <t>流畅度</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>3-bit 屏 CPU 板上切片上屏</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>丢帧/迟到率 (最新 0.0012 %)</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H75" s="12" t="n">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="I75" s="4" t="inlineStr"/>
     </row>
@@ -11045,7 +11049,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 上行/桥</t>
+          <t>V0 2047 · 上屏</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -11055,17 +11059,17 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>上行出口 12-bit (2 期加 1.2G)</t>
+          <t>3-bit 屏 CPU 板上切片上屏</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
@@ -11074,7 +11078,7 @@
         </is>
       </c>
       <c r="H76" s="12" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="I76" s="4" t="inlineStr"/>
     </row>
@@ -11096,12 +11100,12 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>桥侧接收核对 12-bit</t>
+          <t>上行出口 12-bit (2 期加 1.2G)</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -11115,7 +11119,7 @@
         </is>
       </c>
       <c r="H77" s="12" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I77" s="4" t="inlineStr"/>
     </row>
@@ -11137,12 +11141,12 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit</t>
+          <t>桥侧接收核对 12-bit</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -11178,12 +11182,12 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>主控↔桥联合仿真</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -11197,7 +11201,7 @@
         </is>
       </c>
       <c r="H79" s="12" t="n">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="I79" s="4" t="inlineStr"/>
     </row>
@@ -11214,33 +11218,33 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>1 期 4,296 片/s 桥链路余量仅 0.40%</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="8" t="inlineStr">
-        <is>
-          <t>监控</t>
+          <t>主控↔桥联合仿真</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>V1准备 · 必须</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H80" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>退路降到 22 Hz（用户定保持 24 Hz）</t>
-        </is>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="I80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -11260,18 +11264,18 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2260 从未收到合法 ACK（疑物理通路）</t>
+          <t>1 期 4,296 片/s 桥链路余量仅 0.40%</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr"/>
-      <c r="G81" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>监控</t>
         </is>
       </c>
       <c r="H81" s="12" t="n">
@@ -11279,7 +11283,7 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>验证板一颗一组针对此问题，回板验证</t>
+          <t>退路降到 22 Hz（用户定保持 24 Hz）</t>
         </is>
       </c>
     </row>
@@ -11291,38 +11295,38 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 主控位流</t>
+          <t>V1 2260 · 上行/桥</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>风险</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>1 期主控整合位流</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>V1准备 · 必须</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>2260 从未收到合法 ACK（疑物理通路）</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr"/>
+      <c r="G82" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H82" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I82" s="4" t="inlineStr"/>
+        <v>46308</v>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>验证板一颗一组针对此问题，回板验证</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -11342,12 +11346,12 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>V1-B1</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>V1 主控/桥位流按投板版出齐 (单面 io25 / PRBS / 面 B 桥)</t>
+          <t>1 期主控整合位流</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -11361,7 +11365,7 @@
         </is>
       </c>
       <c r="H83" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I83" s="4" t="inlineStr"/>
     </row>
@@ -11373,7 +11377,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 双面</t>
+          <t>V1 2260 · 主控位流</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -11383,12 +11387,12 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>V1-B1</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>核实 V1 能否双面 (W6 光电冲突)</t>
+          <t>V1 主控/桥位流按投板版出齐 (单面 io25 / PRBS / 面 B 桥)</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -11424,12 +11428,12 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>D38</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>V1 面 B 软件就绪 (IO 电压开关/面B RTL/桥B/JTAG 两器件/--faces AB)</t>
+          <t>核实 V1 能否双面 (W6 光电冲突)</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -11465,17 +11469,17 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>D40</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>双面主控位流编译通过 (TD hold 修复崩溃)</t>
+          <t>V1 面 B 软件就绪 (IO 电压开关/面B RTL/桥B/JTAG 两器件/--faces AB)</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 可选</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
@@ -11484,7 +11488,7 @@
         </is>
       </c>
       <c r="H86" s="12" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I86" s="4" t="inlineStr"/>
     </row>
@@ -11496,7 +11500,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 全链路/板端后端</t>
+          <t>V1 2260 · 双面</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -11506,17 +11510,17 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D40</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>全链路系统仿真 (主机→2260 模型)</t>
+          <t>双面主控位流编译通过 (TD hold 修复崩溃)</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
+          <t>V1准备 · 可选</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
@@ -11525,7 +11529,7 @@
         </is>
       </c>
       <c r="H87" s="12" t="n">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="I87" s="4" t="inlineStr"/>
     </row>
@@ -11547,12 +11551,12 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>V1 真内容板端通路 (voxslice 加 2260 后端)</t>
+          <t>全链路系统仿真 (主机→2260 模型)</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -11578,7 +11582,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 投板对齐/回板</t>
+          <t>V1 2260 · 全链路/板端后端</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -11588,12 +11592,12 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>V1 回板当天一键 bring-up 脚本</t>
+          <t>V1 真内容板端通路 (voxslice 加 2260 后端)</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -11629,12 +11633,12 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>软件引脚/硬件假设对齐 10-15/16 投板版</t>
+          <t>V1 回板当天一键 bring-up 脚本</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -11648,7 +11652,7 @@
         </is>
       </c>
       <c r="H90" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I90" s="4" t="inlineStr"/>
     </row>
@@ -11670,12 +11674,12 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>主控 IO 1.8V 可行性 (用户定最终 2.5V)</t>
+          <t>软件引脚/硬件假设对齐 10-15/16 投板版</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -11706,33 +11710,33 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>灯板 SDO→SDI 0Ω 在 09-18 图上悬空</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr"/>
-      <c r="G92" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+          <t>主控 IO 1.8V 可行性 (用户定最终 2.5V)</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>V1准备 · 必须</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H92" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>硬件确认并补 0Ω</t>
-        </is>
-      </c>
+        <v>46314</v>
+      </c>
+      <c r="I92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -11752,12 +11756,12 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>1 期面板映射缺 4 项信息</t>
+          <t>灯板 SDO→SDI 0Ω 在 09-18 图上悬空</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr"/>
@@ -11771,7 +11775,7 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>问硬件同事</t>
+          <t>硬件确认并补 0Ω</t>
         </is>
       </c>
     </row>
@@ -11783,38 +11787,36 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · T2 板/1.2G 上行</t>
+          <t>V1 2260 · 投板对齐/回板</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>风险</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>V2-1</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>T2 自研 SoC 板 (32 bit DDR + PL 读带宽)</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>V2 · 必须</t>
-        </is>
-      </c>
-      <c r="G94" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H94" s="12" t="n"/>
+          <t>1 期面板映射缺 4 项信息</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="n">
+        <v>46308</v>
+      </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>等硬件线 T2 自研板 (32 bit DDR) 投板/回板</t>
+          <t>问硬件同事</t>
         </is>
       </c>
     </row>
@@ -11836,12 +11838,12 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>V2-2</t>
+          <t>V2-1</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>2 期上行 1.2G 实测</t>
+          <t>T2 自研 SoC 板 (32 bit DDR + PL 读带宽)</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -11857,7 +11859,7 @@
       <c r="H95" s="12" t="n"/>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>等 V1 回板 PRBS 实测, 定 1.2G 还是退 1.0G (R1)</t>
+          <t>等硬件线 T2 自研板 (32 bit DDR) 投板/回板</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11881,12 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>D46</t>
+          <t>V2-2</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>V2 桥补齐 面 B + 1.2G PRBS 误码档 (comm_check --phase v2)</t>
+          <t>2 期上行 1.2G 实测</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -11892,17 +11894,15 @@
           <t>V2 · 必须</t>
         </is>
       </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H96" s="12" t="n">
-        <v>46315</v>
-      </c>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="n"/>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>V2 桥板引脚 + V2 主控 PRBS 位流</t>
+          <t>等 V1 回板 PRBS 实测, 定 1.2G 还是退 1.0G (R1)</t>
         </is>
       </c>
     </row>
@@ -11919,31 +11919,35 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>D46</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>1.2G 可能过不了</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr"/>
-      <c r="G97" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+          <t>V2 桥补齐 面 B + 1.2G PRBS 误码档 (comm_check --phase v2)</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 必须</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H97" s="12" t="n">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
+          <t>V2 桥板引脚 + V2 主控 PRBS 位流</t>
         </is>
       </c>
     </row>
@@ -11955,38 +11959,38 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 主控位流</t>
+          <t>V2 192×216 · T2 板/1.2G 上行</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>风险</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>V2 主控位流跟上主线 (p2_ul1200_b12_v3)</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>V2 · 必须</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>1.2G 可能过不了</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr"/>
+      <c r="G98" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H98" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I98" s="4" t="inlineStr"/>
+        <v>46308</v>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -12006,12 +12010,12 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>D44</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>V2 双面主控位流 (片上 RAM/时序评估)</t>
+          <t>V2 主控位流跟上主线 (p2_ul1200_b12_v3)</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -12025,7 +12029,7 @@
         </is>
       </c>
       <c r="H99" s="12" t="n">
-        <v>46315</v>
+        <v>46311</v>
       </c>
       <c r="I99" s="4" t="inlineStr"/>
     </row>
@@ -12037,7 +12041,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 面板映射/后端</t>
+          <t>V2 192×216 · 主控位流</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -12047,12 +12051,12 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>V2-3</t>
+          <t>D44</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>2 期 192×216 面板映射</t>
+          <t>V2 双面主控位流 (片上 RAM/时序评估)</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -12066,7 +12070,7 @@
         </is>
       </c>
       <c r="H100" s="12" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I100" s="4" t="inlineStr"/>
     </row>
@@ -12088,12 +12092,12 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>V2-7</t>
+          <t>V2-3</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>板端 voxslice --disp p2 (2 期后端)</t>
+          <t>2 期 192×216 面板映射</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -12129,12 +12133,12 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>D48</t>
+          <t>V2-7</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>V2 双面全链路系统仿真 (PC→主控→桥→2260 模型)</t>
+          <t>板端 voxslice --disp p2 (2 期后端)</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -12148,7 +12152,7 @@
         </is>
       </c>
       <c r="H102" s="12" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I102" s="4" t="inlineStr"/>
     </row>
@@ -12160,7 +12164,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 整机</t>
+          <t>V2 192×216 · 面板映射/后端</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
@@ -12170,12 +12174,12 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>V2-4</t>
+          <t>D48</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>2 期 30 Hz 整机上转子</t>
+          <t>V2 双面全链路系统仿真 (PC→主控→桥→2260 模型)</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -12183,17 +12187,15 @@
           <t>V2 · 必须</t>
         </is>
       </c>
-      <c r="G103" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H103" s="12" t="n"/>
-      <c r="I103" s="4" t="inlineStr">
-        <is>
-          <t>等 T2 板 (V2-1) + 1.2G 上行 (V2-2)</t>
-        </is>
-      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="I103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -12203,36 +12205,38 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>画面指标 (各期)</t>
+          <t>V2 192×216 · 整机</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>KR1.6</t>
+          <t>V2-4</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>内容刷新率 (实转上屏) (最新 10.8 fps)</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr"/>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1⬜ V2⬜</t>
-        </is>
-      </c>
-      <c r="H104" s="12" t="n">
-        <v>46307</v>
-      </c>
+          <t>2 期 30 Hz 整机上转子</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 必须</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H104" s="12" t="n"/>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>等 V1 整机 720 RPM 实转 (验证板 11-10 回板)</t>
+          <t>等 T2 板 (V2-1) + 1.2G 上行 (V2-2)</t>
         </is>
       </c>
     </row>
@@ -12254,18 +12258,18 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>KR2.1</t>
+          <t>KR1.6</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>体帧率 (最新 21.7 Hz)</t>
+          <t>内容刷新率 (实转上屏) (最新 10.8 fps)</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr"/>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1🔵 V2⬜</t>
+          <t>V0✅ V1⬜ V2⬜</t>
         </is>
       </c>
       <c r="H105" s="12" t="n">
@@ -12273,7 +12277,7 @@
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>等 V1 回板实转 720 RPM×358 片</t>
+          <t>等 V1 整机 720 RPM 实转 (验证板 11-10 回板)</t>
         </is>
       </c>
     </row>
@@ -12295,18 +12299,18 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>KR3.1</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>每面像素数 (最新 28800 px)</t>
+          <t>体帧率 (最新 21.7 Hz)</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr"/>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1✅ V2⬜</t>
+          <t>V0✅ V1🔵 V2⬜</t>
         </is>
       </c>
       <c r="H106" s="12" t="n">
@@ -12314,7 +12318,7 @@
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>等 2 期 192×216 屏</t>
+          <t>等 V1 回板实转 720 RPM×358 片</t>
         </is>
       </c>
     </row>
@@ -12336,18 +12340,18 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>KR3.2</t>
+          <t>KR3.1</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>每圈片数 (最新 142 片)</t>
+          <t>每面像素数 (最新 28800 px)</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1🔵 V2⬜</t>
+          <t>V0✅ V1✅ V2⬜</t>
         </is>
       </c>
       <c r="H107" s="12" t="n">
@@ -12355,7 +12359,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>等 V1 回板实测</t>
+          <t>等 2 期 192×216 屏</t>
         </is>
       </c>
     </row>
@@ -12377,18 +12381,18 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>KR4.1</t>
+          <t>KR3.2</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>色深 (最新 3 bit/通道)</t>
+          <t>每圈片数 (最新 142 片)</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr"/>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1🔵 V2🔵</t>
+          <t>V0✅ V1🔵 V2⬜</t>
         </is>
       </c>
       <c r="H108" s="12" t="n">
@@ -12396,50 +12400,50 @@
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>等 V1 2260 回板上屏</t>
+          <t>等 V1 回板实测</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>④ 运维保障</t>
+          <t>③ 显示 (按期换后端)</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>开机即用</t>
+          <t>画面指标 (各期)</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>KR4.1</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>开机自动演示 + 转速门控</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>色深 (最新 3 bit/通道)</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr"/>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1🔵 V2🔵</t>
         </is>
       </c>
       <c r="H109" s="12" t="n">
         <v>46307</v>
       </c>
-      <c r="I109" s="4" t="inlineStr"/>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>等 V1 2260 回板上屏</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -12459,12 +12463,12 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>启动提速 + 启动屏显 (含原 backlog B1)</t>
+          <t>开机自动演示 + 转速门控</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -12478,7 +12482,7 @@
         </is>
       </c>
       <c r="H110" s="12" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="I110" s="4" t="inlineStr"/>
     </row>
@@ -12500,12 +12504,12 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>开机默认动画 = 立方体动图 (用户 10-16 提)</t>
+          <t>启动提速 + 启动屏显 (含原 backlog B1)</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -12519,7 +12523,7 @@
         </is>
       </c>
       <c r="H111" s="12" t="n">
-        <v>46311</v>
+        <v>46309</v>
       </c>
       <c r="I111" s="4" t="inlineStr"/>
     </row>
@@ -12541,17 +12545,17 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>D47</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>系统从 QSPI 加载 (去 TF/eMMC 准备; 03 板试)</t>
+          <t>开机默认动画 = 立方体动图 (用户 10-16 提)</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>V2 · 加分</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
@@ -12560,13 +12564,9 @@
         </is>
       </c>
       <c r="H112" s="12" t="n">
-        <v>46315</v>
-      </c>
-      <c r="I112" s="4" t="inlineStr">
-        <is>
-          <t>T2 板 QSPI 选 64MiB / 厂商驱动提速</t>
-        </is>
-      </c>
+        <v>46311</v>
+      </c>
+      <c r="I112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12581,29 +12581,37 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>KR8.1</t>
+          <t>D47</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>上电到 0° 片亮起 (停转) (最新 12.4 s)</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr"/>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>系统从 QSPI 加载 (去 TF/eMMC 准备; 03 板试)</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 加分</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H113" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I113" s="4" t="inlineStr"/>
+        <v>46315</v>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>T2 板 QSPI 选 64MiB / 厂商驱动提速</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -12623,22 +12631,22 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>KR8.4</t>
+          <t>KR8.1</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>上电到转稳全亮 (最新 26 s)</t>
+          <t>上电到 0° 片亮起 (停转) (最新 12.4 s)</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>V0— V1— V2—</t>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H114" s="12" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="I114" s="4" t="inlineStr"/>
     </row>
@@ -12650,32 +12658,28 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>联网/找板/自愈</t>
+          <t>开机即用</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>KR8.4</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>开机自连 WiFi</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G115" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>上电到转稳全亮 (最新 26 s)</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>V0— V1— V2—</t>
         </is>
       </c>
       <c r="H115" s="12" t="n">
@@ -12701,12 +12705,12 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS)</t>
+          <t>开机自连 WiFi</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -12720,7 +12724,7 @@
         </is>
       </c>
       <c r="H116" s="12" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="I116" s="4" t="inlineStr"/>
     </row>
@@ -12742,12 +12746,12 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 (服务监护/看门狗/兜底热点/povnetd 1.2)</t>
+          <t>按名字找板 (mDNS)</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
@@ -12761,7 +12765,7 @@
         </is>
       </c>
       <c r="H117" s="12" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="I117" s="4" t="inlineStr"/>
     </row>
@@ -12783,12 +12787,12 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复 ≤30 s (03 长跑断 155 s)</t>
+          <t>不插串口永远连得上 (服务监护/看门狗/兜底热点/povnetd 1.2)</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -12802,7 +12806,7 @@
         </is>
       </c>
       <c r="H118" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I118" s="4" t="inlineStr"/>
     </row>
@@ -12824,12 +12828,12 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>D43</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>povnetd 1.3 网络自愈回归修复</t>
+          <t>WiFi 断线恢复 ≤30 s (03 长跑断 155 s)</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -12860,27 +12864,31 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>KR8.2</t>
+          <t>D43</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>按名字找到板子 (最新 19.8 s)</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr"/>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>povnetd 1.3 网络自愈回归修复</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 必须</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H120" s="12" t="n">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="I120" s="4" t="inlineStr"/>
     </row>
@@ -12892,32 +12900,28 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>远程运维/升级 (含 JTAG 灌桥)</t>
+          <t>联网/找板/自愈</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR8.2</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>转子运维 (netguard-lite / 遥测 / 远程升级)</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G121" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>按名字找到板子 (最新 19.8 s)</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr"/>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H121" s="12" t="n">
@@ -12943,17 +12947,17 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>主控经 JTAG 给桥灌位流 (V1 远程升级软件)</t>
+          <t>转子运维 (netguard-lite / 遥测 / 远程升级)</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
@@ -12962,7 +12966,7 @@
         </is>
       </c>
       <c r="H122" s="12" t="n">
-        <v>46314</v>
+        <v>46309</v>
       </c>
       <c r="I122" s="4" t="inlineStr"/>
     </row>
@@ -12984,17 +12988,17 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>D42</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>03 板软件跟进主线</t>
+          <t>主控经 JTAG 给桥灌位流 (V1 远程升级软件)</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>V0 · 加分</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
@@ -13020,27 +13024,31 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>KR8.3</t>
+          <t>D42</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>需要串口 (1=需要) (最新 0 是/否)</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr"/>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>03 板软件跟进主线</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H124" s="12" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="I124" s="4" t="inlineStr"/>
     </row>
@@ -13062,12 +13070,12 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>KR8.3</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用) (最新 1 是/否)</t>
+          <t>需要串口 (1=需要) (最新 0 是/否)</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr"/>
@@ -13077,7 +13085,7 @@
         </is>
       </c>
       <c r="H125" s="12" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="I125" s="4" t="inlineStr"/>
     </row>
@@ -13099,12 +13107,12 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>KR9.2</t>
+          <t>KR9.1</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>远程升级失败自动回滚 (1=有) (最新 1 是/否)</t>
+          <t>转子遥测可用 (1=可用) (最新 1 是/否)</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr"/>
@@ -13126,40 +13134,34 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>主控↔桥通信</t>
+          <t>远程运维/升级 (含 JTAG 灌桥)</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>KR9.2</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>C1 台架彩排 + 1.2G 误码测试</t>
-        </is>
-      </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>V1准备 · 加分</t>
-        </is>
-      </c>
-      <c r="G127" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H127" s="12" t="n"/>
-      <c r="I127" s="4" t="inlineStr">
-        <is>
-          <t>不做 (用户 10-19 定), 由 D39 到板 comm_check 代替</t>
-        </is>
-      </c>
+          <t>远程升级失败自动回滚 (1=有) (最新 1 是/否)</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr"/>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -13179,28 +13181,30 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信全功能 (配置/状态/错误恢复/升级)</t>
+          <t>C1 台架彩排 + 1.2G 误码测试</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
-        </is>
-      </c>
-      <c r="G128" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H128" s="12" t="n">
-        <v>46312</v>
-      </c>
-      <c r="I128" s="4" t="inlineStr"/>
+          <t>V1准备 · 加分</t>
+        </is>
+      </c>
+      <c r="G128" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="n"/>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t>不做 (用户 10-19 定), 由 D39 到板 comm_check 代替</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -13220,12 +13224,12 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 + PRBS 位流</t>
+          <t>SoC↔桥通信全功能 (配置/状态/错误恢复/升级)</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
@@ -13239,7 +13243,7 @@
         </is>
       </c>
       <c r="H129" s="12" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="I129" s="4" t="inlineStr"/>
     </row>
@@ -13251,7 +13255,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>可靠性验证 (冷启动/长跑)</t>
+          <t>主控↔桥通信</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
@@ -13261,17 +13265,17 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>V0A</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>V0 重启验收 (不插串口: 找回/守护/开机默认/WiFi/推流/稳定 6 项)</t>
+          <t>SoC↔桥通信专项验证包 + PRBS 位流</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>V0 · 必须</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
@@ -13280,7 +13284,7 @@
         </is>
       </c>
       <c r="H130" s="12" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="I130" s="4" t="inlineStr"/>
     </row>
@@ -13302,12 +13306,12 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>V0A</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>冷启动认不到 TF 卡 (03 停在 u-boot)</t>
+          <t>V0 重启验收 (不插串口: 找回/守护/开机默认/WiFi/推流/稳定 6 项)</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
@@ -13321,7 +13325,7 @@
         </is>
       </c>
       <c r="H131" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I131" s="4" t="inlineStr"/>
     </row>
@@ -13343,17 +13347,17 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>D49</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+          <t>冷启动认不到 TF 卡 (03 停在 u-boot)</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>V0 · 加分</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
@@ -13362,7 +13366,7 @@
         </is>
       </c>
       <c r="H132" s="12" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I132" s="4" t="inlineStr"/>
     </row>
@@ -13379,27 +13383,31 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D49</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr"/>
-      <c r="G133" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H133" s="12" t="n">
-        <v>46312</v>
+        <v>46315</v>
       </c>
       <c r="I133" s="4" t="inlineStr"/>
     </row>
@@ -13421,12 +13429,12 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
+          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr"/>
@@ -13436,7 +13444,7 @@
         </is>
       </c>
       <c r="H134" s="12" t="n">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="I134" s="4" t="inlineStr"/>
     </row>
@@ -13453,33 +13461,29 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
+          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr"/>
-      <c r="G135" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H135" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I135" s="4" t="inlineStr">
-        <is>
-          <t>T2 板留 eMMC、打胶</t>
-        </is>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="I135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -13489,7 +13493,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>开发环境</t>
+          <t>可靠性验证 (冷启动/长跑)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
@@ -13499,24 +13503,65 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>D 盘 EIO（IP-guard 驱动）</t>
+          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr"/>
-      <c r="G136" s="8" t="inlineStr">
-        <is>
-          <t>监控</t>
+      <c r="G136" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H136" s="12" t="n">
         <v>46308</v>
       </c>
       <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>T2 板留 eMMC、打胶</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>④ 运维保障</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>开发环境</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>风险</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>D 盘 EIO（IP-guard 驱动）</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr"/>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>监控</t>
+        </is>
+      </c>
+      <c r="H137" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
         <is>
           <t>看门狗自动重挂 + 构建放 WSL 本地盘</t>
         </is>
@@ -13536,7 +13581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J211"/>
+  <dimension ref="A1:J212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13639,16 +13684,16 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>0.9117647058823529</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>62/68</t>
+          <t>63/69</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>KR 18/24 + 交付 44/44 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
+          <t>KR 18/24 + 交付 45/45 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
         </is>
       </c>
       <c r="G5" s="17" t="n">
@@ -13671,16 +13716,16 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>0.8701298701298701</v>
+        <v>0.8717948717948718</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>67/77</t>
+          <t>68/78</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>KR 17/24 + 交付 50/53 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 17/24 + 交付 51/54 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="17" t="n">
@@ -13814,10 +13859,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.913</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>0.8701</v>
+        <v>0.8718</v>
       </c>
     </row>
     <row r="13">
@@ -14894,26 +14939,26 @@
     </row>
     <row r="58">
       <c r="A58" s="12" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46315</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>D45</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
+          <t>前端统一 V2 网格: V1 位流切片器读 192×216 (取样在入环前, ERAM 174/250 不变, 两档 0 违例) + voxslice 1.0 运行时网格/PC 默认 192; V0 行为不变 (VOX_GRID=160); 联合复验 4 套全过</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d22_reach/README.md</t>
+          <t>dr1v90 771abc4</t>
         </is>
       </c>
     </row>
@@ -14921,24 +14966,24 @@
       <c r="A59" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>D32</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
+          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>dr1v90</t>
+          <t>dr1v90 d22_reach/README.md</t>
         </is>
       </c>
     </row>
@@ -14946,9 +14991,9 @@
       <c r="A60" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -14958,12 +15003,12 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
+          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/acc32_*.log</t>
+          <t>dr1v90</t>
         </is>
       </c>
     </row>
@@ -14971,24 +15016,24 @@
       <c r="A61" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B61" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
+          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>progress/v0_accept/acc32_*.log</t>
         </is>
       </c>
     </row>
@@ -14996,24 +15041,24 @@
       <c r="A62" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>补录</t>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>KR4.2</t>
+          <t>用户</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
+          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15023,22 +15068,22 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>补录</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
+          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -15048,22 +15093,22 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
+          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 card03</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15073,22 +15118,22 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
+          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2b111f0</t>
+          <t>dr1v90 card03</t>
         </is>
       </c>
     </row>
@@ -15098,22 +15143,22 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
+          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
+          <t>dr1v90 2b111f0</t>
         </is>
       </c>
     </row>
@@ -15121,24 +15166,24 @@
       <c r="A67" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B67" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
+          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
         </is>
       </c>
     </row>
@@ -15146,24 +15191,24 @@
       <c r="A68" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
+          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 97a10cf</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15173,22 +15218,22 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
+          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 7253608</t>
+          <t>dr1v90 97a10cf</t>
         </is>
       </c>
     </row>
@@ -15196,24 +15241,24 @@
       <c r="A70" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B70" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D34</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
+          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 7253608</t>
         </is>
       </c>
     </row>
@@ -15221,24 +15266,24 @@
       <c r="A71" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
+          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 23474c7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15253,17 +15298,17 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
+          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 f2584d9</t>
+          <t>dr1v90 23474c7</t>
         </is>
       </c>
     </row>
@@ -15278,17 +15323,17 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>D38</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
+          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ad201f9</t>
+          <t>dr1v90 f2584d9</t>
         </is>
       </c>
     </row>
@@ -15298,22 +15343,22 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>V1主控</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
+          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>本机构建</t>
+          <t>dr1v90 ad201f9</t>
         </is>
       </c>
     </row>
@@ -15328,17 +15373,17 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V1主控</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
+          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d39-comm b69f6d8</t>
+          <t>本机构建</t>
         </is>
       </c>
     </row>
@@ -15348,22 +15393,22 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>V2-7</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
+          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ff1846a</t>
+          <t>dr1v90 task/d39-comm b69f6d8</t>
         </is>
       </c>
     </row>
@@ -15378,17 +15423,17 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V2-7</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
+          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3ef6b06</t>
+          <t>dr1v90 ff1846a</t>
         </is>
       </c>
     </row>
@@ -15398,22 +15443,22 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
+          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>progress/d29_coldboot</t>
+          <t>dr1v90 3ef6b06</t>
         </is>
       </c>
     </row>
@@ -15421,24 +15466,24 @@
       <c r="A79" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B79" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>D11;D39</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
+          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>用户 10-19</t>
+          <t>progress/d29_coldboot</t>
         </is>
       </c>
     </row>
@@ -15446,24 +15491,24 @@
       <c r="A80" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D11;D39</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
+          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6333eb5</t>
+          <t>用户 10-19</t>
         </is>
       </c>
     </row>
@@ -15478,67 +15523,67 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>D42;D43</t>
+          <t>D41</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
+          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 8689db2 / 6e6d47b</t>
+          <t>dr1v90 6333eb5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D42;D43</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
+          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1017_03_24h</t>
+          <t>dr1v90 8689db2 / 6e6d47b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46313</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
+          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/SPEC.md</t>
+          <t>progress/soak_v0/1017_03_24h</t>
         </is>
       </c>
     </row>
@@ -15546,24 +15591,24 @@
       <c r="A84" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>V2-5</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
+          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_fmt/README.md</t>
+          <t>dr1v90 d27_link/SPEC.md</t>
         </is>
       </c>
     </row>
@@ -15578,17 +15623,17 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>D28b</t>
+          <t>V2-5</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
+          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/回板当天.md</t>
+          <t>dr1v90 v2_fmt/README.md</t>
         </is>
       </c>
     </row>
@@ -15596,24 +15641,24 @@
       <c r="A86" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>进展</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>D27b</t>
+          <t>D28b</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
+          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/README.md</t>
+          <t>dr1v90 v1_bringup/回板当天.md</t>
         </is>
       </c>
     </row>
@@ -15621,24 +15666,24 @@
       <c r="A87" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>V2-6</t>
+          <t>D27b</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
+          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 gw5a_bridge/p2/README.md</t>
+          <t>dr1v90 d27_link/README.md</t>
         </is>
       </c>
     </row>
@@ -15648,22 +15693,22 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>全套</t>
+          <t>V2-6</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
+          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ~/full_*.log</t>
+          <t>dr1v90 gw5a_bridge/p2/README.md</t>
         </is>
       </c>
     </row>
@@ -15673,22 +15718,22 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>修复</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>全套</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
+          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 slice/SPEC.md §13.2</t>
+          <t>dr1v90 ~/full_*.log</t>
         </is>
       </c>
     </row>
@@ -15698,22 +15743,22 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
+          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1016_wkend_24h</t>
+          <t>dr1v90 slice/SPEC.md §13.2</t>
         </is>
       </c>
     </row>
@@ -15723,7 +15768,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -15733,37 +15778,37 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
+          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1017_*.log</t>
+          <t>progress/soak_v0/1016_wkend_24h</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>部署</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
+          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22c.board.log</t>
+          <t>progress/v0_accept/accept_1017_*.log</t>
         </is>
       </c>
     </row>
@@ -15771,9 +15816,9 @@
       <c r="A93" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -15783,12 +15828,12 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
+          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d22c.board.log</t>
         </is>
       </c>
     </row>
@@ -15796,24 +15841,24 @@
       <c r="A94" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
+          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board5.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15821,9 +15866,9 @@
       <c r="A95" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -15833,12 +15878,12 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
+          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d21.board5.log</t>
         </is>
       </c>
     </row>
@@ -15853,12 +15898,12 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
+          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -15871,9 +15916,9 @@
       <c r="A97" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -15883,12 +15928,12 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
+          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_A fps_B</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15896,9 +15941,9 @@
       <c r="A98" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -15908,12 +15953,12 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
+          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_C</t>
+          <t>soak_runs/fps_A fps_B</t>
         </is>
       </c>
     </row>
@@ -15921,24 +15966,24 @@
       <c r="A99" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
+          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20d-ackrps db4ec93</t>
+          <t>soak_runs/fps_C</t>
         </is>
       </c>
     </row>
@@ -15953,17 +15998,17 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
+          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
+          <t>dr1v90 task/d20d-ackrps db4ec93</t>
         </is>
       </c>
     </row>
@@ -15973,22 +16018,22 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
+          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_D</t>
+          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
         </is>
       </c>
     </row>
@@ -15996,9 +16041,9 @@
       <c r="A102" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -16008,12 +16053,12 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
+          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>soak_runs/fps_D</t>
         </is>
       </c>
     </row>
@@ -16021,24 +16066,24 @@
       <c r="A103" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
+          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>~/rv_deploy.board.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16046,24 +16091,24 @@
       <c r="A104" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
+          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_deploy.board.log</t>
         </is>
       </c>
     </row>
@@ -16071,24 +16116,24 @@
       <c r="A105" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B105" s="5" t="inlineStr">
-        <is>
-          <t>验收</t>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
+          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16098,22 +16143,22 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>开工</t>
+          <t>验收</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>D20e/D23</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
+          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
+          <t>progress/v0_accept/</t>
         </is>
       </c>
     </row>
@@ -16121,24 +16166,24 @@
       <c r="A107" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B107" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>开工</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D20e/D23</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
+          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
         </is>
       </c>
     </row>
@@ -16146,24 +16191,24 @@
       <c r="A108" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B108" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
+          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -16178,12 +16223,12 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
+          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -16196,24 +16241,24 @@
       <c r="A110" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
+          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1016_d20e.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16221,24 +16266,24 @@
       <c r="A111" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>KR7.3/D24</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
+          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>progress/v0_accept/accept_1016_d20e.log</t>
         </is>
       </c>
     </row>
@@ -16246,24 +16291,24 @@
       <c r="A112" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>KR7.3/D24</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
+          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>D:\card03</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16271,24 +16316,24 @@
       <c r="A113" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>D25</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
+          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>D:\card03</t>
         </is>
       </c>
     </row>
@@ -16296,24 +16341,24 @@
       <c r="A114" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D25</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
+          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\cap_COM29.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16328,17 +16373,17 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
+          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20d_ackrps d20c_fps</t>
+          <t>D:\card03\cap_COM29.log</t>
         </is>
       </c>
     </row>
@@ -16346,24 +16391,24 @@
       <c r="A116" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
+          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d12_latency/RESULTS.md</t>
+          <t>dr1v90 d20d_ackrps d20c_fps</t>
         </is>
       </c>
     </row>
@@ -16378,17 +16423,17 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
+          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d9_e2e/</t>
+          <t>dr1v90 d12_latency/RESULTS.md</t>
         </is>
       </c>
     </row>
@@ -16396,24 +16441,24 @@
       <c r="A118" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
+          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\boot03.log</t>
+          <t>dr1v90 d9_e2e/</t>
         </is>
       </c>
     </row>
@@ -16421,24 +16466,24 @@
       <c r="A119" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
+          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
+          <t>D:\card03\boot03.log</t>
         </is>
       </c>
     </row>
@@ -16446,24 +16491,24 @@
       <c r="A120" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>开工</t>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
+          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
+          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
         </is>
       </c>
     </row>
@@ -16473,22 +16518,22 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>方案</t>
+          <t>开工</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
+          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d29_sdboot/PLAN.md</t>
+          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
         </is>
       </c>
     </row>
@@ -16496,24 +16541,24 @@
       <c r="A122" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B122" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>方案</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
+          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/</t>
+          <t>dr1v90 d29_sdboot/PLAN.md</t>
         </is>
       </c>
     </row>
@@ -16521,24 +16566,24 @@
       <c r="A123" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>修复</t>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
+          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
+          <t>dr1v90 v1_bringup/</t>
         </is>
       </c>
     </row>
@@ -16548,22 +16593,22 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>进展</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>V2-3</t>
+          <t>D30</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
+          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_map/DESIGN.md</t>
+          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
         </is>
       </c>
     </row>
@@ -16573,47 +16618,47 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>评估</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>V2-3</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
+          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d31_v1odd/REPORT.md</t>
+          <t>dr1v90 v2_map/DESIGN.md</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="12" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46311</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>评估</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D31</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
+          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/report.md</t>
+          <t>dr1v90 d31_v1odd/REPORT.md</t>
         </is>
       </c>
     </row>
@@ -16621,24 +16666,24 @@
       <c r="A127" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>QoS</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
+          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>~/qos_runs</t>
+          <t>progress/soak_v0/report.md</t>
         </is>
       </c>
     </row>
@@ -16653,17 +16698,17 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>D16b</t>
+          <t>QoS</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
+          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16b-tile 7936b7e</t>
+          <t>~/qos_runs</t>
         </is>
       </c>
     </row>
@@ -16671,24 +16716,24 @@
       <c r="A129" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B129" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D16b</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
+          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>dr1v90 task/d16b-tile 7936b7e</t>
         </is>
       </c>
     </row>
@@ -16703,12 +16748,12 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
+          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -16721,24 +16766,24 @@
       <c r="A131" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B131" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>V1/V2</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
+          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>budget/rpm_range_2026-10-15.md</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -16746,24 +16791,24 @@
       <c r="A132" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>V1/V2</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
+          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>progress/realspin_v0/</t>
+          <t>budget/rpm_range_2026-10-15.md</t>
         </is>
       </c>
     </row>
@@ -16771,19 +16816,19 @@
       <c r="A133" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B133" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
+          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -16796,24 +16841,24 @@
       <c r="A134" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
+          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20-smooth 83a5fd7</t>
+          <t>progress/realspin_v0/</t>
         </is>
       </c>
     </row>
@@ -16821,24 +16866,24 @@
       <c r="A135" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B135" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
+          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 e215176</t>
+          <t>dr1v90 task/d20-smooth 83a5fd7</t>
         </is>
       </c>
     </row>
@@ -16846,24 +16891,24 @@
       <c r="A136" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
+          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d19-halfrev 1beafa6</t>
+          <t>dr1v90 e215176</t>
         </is>
       </c>
     </row>
@@ -16878,17 +16923,17 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>D20b</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
+          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20b-sim 9081f62</t>
+          <t>dr1v90 task/d19-halfrev 1beafa6</t>
         </is>
       </c>
     </row>
@@ -16898,22 +16943,22 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D20b</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
+          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/merge-d19-d20 106364e</t>
+          <t>dr1v90 task/d20b-sim 9081f62</t>
         </is>
       </c>
     </row>
@@ -16921,24 +16966,24 @@
       <c r="A139" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B139" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>D19/D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
+          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/merge-d19-d20 106364e</t>
         </is>
       </c>
     </row>
@@ -16946,24 +16991,24 @@
       <c r="A140" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D19/D20</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
+          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband adeba44</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16973,22 +17018,22 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>D20/D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
+          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>~/realspin/tcp</t>
+          <t>dr1v90 task/d21-nband adeba44</t>
         </is>
       </c>
     </row>
@@ -16996,24 +17041,24 @@
       <c r="A142" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B142" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D20/D22</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
+          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>~/realspin/tcp</t>
         </is>
       </c>
     </row>
@@ -17021,9 +17066,9 @@
       <c r="A143" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B143" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -17033,12 +17078,12 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
+          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach ee4a55c</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -17053,17 +17098,17 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
+          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20c-fps 338eaaf</t>
+          <t>dr1v90 task/d22-reach ee4a55c</t>
         </is>
       </c>
     </row>
@@ -17073,7 +17118,7 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>复验</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -17083,12 +17128,12 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
+          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d20c.v.log</t>
+          <t>dr1v90 task/d20c-fps 338eaaf</t>
         </is>
       </c>
     </row>
@@ -17098,22 +17143,22 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>复验</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
+          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d8-cosim 85dfe51</t>
+          <t>~/rv_d20c.v.log</t>
         </is>
       </c>
     </row>
@@ -17121,9 +17166,9 @@
       <c r="A147" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B147" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -17133,12 +17178,12 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
+          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/d8-cosim 85dfe51</t>
         </is>
       </c>
     </row>
@@ -17146,24 +17191,24 @@
       <c r="A148" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B148" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>D22/D20</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
+          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/netdiag_1015_1814</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -17171,24 +17216,24 @@
       <c r="A149" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B149" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22/D20</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
+          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board.log</t>
+          <t>soak_runs/netdiag_1015_1814</t>
         </is>
       </c>
     </row>
@@ -17203,17 +17248,17 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
+          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach</t>
+          <t>~/rv_d21.board.log</t>
         </is>
       </c>
     </row>
@@ -17233,7 +17278,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
+          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -17246,9 +17291,9 @@
       <c r="A152" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B152" s="5" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B152" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -17258,12 +17303,12 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
+          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22.board2.log</t>
+          <t>dr1v90 task/d22-reach</t>
         </is>
       </c>
     </row>
@@ -17273,22 +17318,22 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
+          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>~/d21b_forensic.log</t>
+          <t>~/rv_d22.board2.log</t>
         </is>
       </c>
     </row>
@@ -17303,17 +17348,17 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
+          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach 0d1da09</t>
+          <t>~/d21b_forensic.log</t>
         </is>
       </c>
     </row>
@@ -17323,7 +17368,7 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -17333,12 +17378,12 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
+          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22b.board.log</t>
+          <t>dr1v90 task/d22-reach 0d1da09</t>
         </is>
       </c>
     </row>
@@ -17348,7 +17393,7 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -17358,12 +17403,12 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
+          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach e438a12</t>
+          <t>~/rv_d22b.board.log</t>
         </is>
       </c>
     </row>
@@ -17373,47 +17418,47 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
+          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband 084bba3</t>
+          <t>dr1v90 task/d22-reach e438a12</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B158" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>dr1v90 task/d21-nband 084bba3</t>
         </is>
       </c>
     </row>
@@ -17421,24 +17466,24 @@
       <c r="A159" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B159" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -17446,24 +17491,24 @@
       <c r="A160" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B160" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B160" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -17483,7 +17528,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -17496,24 +17541,24 @@
       <c r="A162" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B162" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -17521,24 +17566,24 @@
       <c r="A163" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B163" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B163" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -17546,9 +17591,9 @@
       <c r="A164" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B164" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -17558,12 +17603,12 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -17571,9 +17616,9 @@
       <c r="A165" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B165" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B165" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -17583,12 +17628,12 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -17596,24 +17641,24 @@
       <c r="A166" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B166" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17621,24 +17666,24 @@
       <c r="A167" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B167" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -17646,24 +17691,24 @@
       <c r="A168" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B168" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B168" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -17671,24 +17716,24 @@
       <c r="A169" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B169" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B169" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17696,9 +17741,9 @@
       <c r="A170" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B170" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
@@ -17708,12 +17753,12 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -17721,24 +17766,24 @@
       <c r="A171" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B171" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B171" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -17746,9 +17791,9 @@
       <c r="A172" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B172" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B172" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -17758,12 +17803,12 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -17771,24 +17816,24 @@
       <c r="A173" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B173" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -17796,24 +17841,24 @@
       <c r="A174" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B174" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -17821,24 +17866,24 @@
       <c r="A175" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B175" s="5" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
@@ -17846,24 +17891,24 @@
       <c r="A176" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B176" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
@@ -17871,24 +17916,24 @@
       <c r="A177" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B177" s="5" t="inlineStr">
-        <is>
-          <t>开始</t>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -17896,24 +17941,24 @@
       <c r="A178" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B178" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
@@ -17921,49 +17966,49 @@
       <c r="A179" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B179" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B179" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B180" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -17978,17 +18023,17 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -18003,17 +18048,17 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -18021,9 +18066,9 @@
       <c r="A183" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B183" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -18033,12 +18078,12 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -18046,9 +18091,9 @@
       <c r="A184" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B184" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B184" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -18058,12 +18103,12 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -18071,24 +18116,24 @@
       <c r="A185" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B185" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -18096,9 +18141,9 @@
       <c r="A186" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B186" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B186" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
@@ -18108,12 +18153,12 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18128,17 +18173,17 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -18146,9 +18191,9 @@
       <c r="A188" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B188" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
@@ -18158,12 +18203,12 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -18183,7 +18228,7 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
@@ -18196,24 +18241,24 @@
       <c r="A190" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B190" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B190" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18221,24 +18266,24 @@
       <c r="A191" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B191" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -18246,24 +18291,24 @@
       <c r="A192" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B192" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B192" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18278,17 +18323,17 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -18296,19 +18341,19 @@
       <c r="A194" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B194" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
@@ -18321,9 +18366,9 @@
       <c r="A195" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B195" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B195" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -18333,12 +18378,12 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18346,24 +18391,24 @@
       <c r="A196" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B196" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B196" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -18371,9 +18416,9 @@
       <c r="A197" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B197" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B197" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -18383,12 +18428,12 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18396,9 +18441,9 @@
       <c r="A198" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B198" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B198" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -18408,12 +18453,12 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -18421,24 +18466,24 @@
       <c r="A199" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B199" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B199" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18446,24 +18491,24 @@
       <c r="A200" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B200" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -18476,15 +18521,19 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C201" s="4" t="inlineStr"/>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18492,15 +18541,15 @@
       <c r="A202" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B202" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B202" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr"/>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
@@ -18513,20 +18562,20 @@
       <c r="A203" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B203" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B203" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr"/>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -18539,19 +18588,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C204" s="4" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="C204" s="4" t="inlineStr"/>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -18566,12 +18611,12 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
@@ -18591,12 +18636,12 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
@@ -18616,12 +18661,12 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
@@ -18641,12 +18686,12 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
@@ -18666,17 +18711,17 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18684,24 +18729,24 @@
       <c r="A210" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B210" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B210" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
@@ -18709,18 +18754,43 @@
       <c r="A211" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B211" s="23" t="inlineStr">
+      <c r="B211" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E211" s="4" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B212" s="23" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C211" s="4" t="inlineStr"/>
-      <c r="D211" s="4" t="inlineStr">
+      <c r="C212" s="4" t="inlineStr"/>
+      <c r="D212" s="4" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E211" s="4" t="inlineStr">
+      <c r="E212" s="4" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -23463,7 +23533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23507,7 +23577,7 @@
         <v>46307</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>5</v>
@@ -23521,7 +23591,7 @@
         <v>46308</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>7</v>
@@ -23535,7 +23605,7 @@
         <v>46309</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>8</v>
@@ -23549,7 +23619,7 @@
         <v>46310</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>12</v>
@@ -23563,7 +23633,7 @@
         <v>46311</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>20</v>
@@ -23577,7 +23647,7 @@
         <v>46312</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>28</v>
@@ -23591,7 +23661,7 @@
         <v>46313</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>28</v>
@@ -23605,7 +23675,7 @@
         <v>46314</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>32</v>
@@ -23619,13 +23689,13 @@
         <v>46315</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
@@ -23633,10 +23703,10 @@
         <v>46316</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" s="5" t="n"/>
     </row>
@@ -23645,10 +23715,10 @@
         <v>46317</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" s="5" t="n"/>
     </row>
@@ -23657,10 +23727,10 @@
         <v>46318</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" s="5" t="n"/>
     </row>
@@ -23669,10 +23739,10 @@
         <v>46319</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" s="5" t="n"/>
     </row>
@@ -26024,6 +26094,44 @@
       <c r="H85" s="4" t="inlineStr">
         <is>
           <t>dr1v90 合并 (p2b/p2p 0 违例; d46 verify 16/0; 桥引脚占位)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>D45</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>前端统一 V2 网格 (V1/V2 共用收包→散写→切片; V1 回板即实测 V2 前端)</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>1;2;3</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>dr1v90 e97390e+771abc4 (V1 g2 位流 0 违例 ERAM 不变; voxslice 1.0 运行时网格; 联合复验 d45_g2 5/0 d45_front 17/0 sim_v1 d38 11/0)</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-20.xlsx
+++ b/docs/progress/显性目的进度_2026-10-20.xlsx
@@ -8580,7 +8580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>13/13</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
           <t>12/12</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>11/11</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
@@ -11017,68 +11017,72 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>D50</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>丢帧/迟到率 (最新 0.0012 %)</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr"/>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>推流卡顿修 (网络一抖后积压不消 → 板端最新帧优先 + auto 留 12% 余量)</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 必须</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H75" s="12" t="n">
-        <v>46310</v>
-      </c>
-      <c r="I75" s="4" t="inlineStr"/>
+        <v>46315</v>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>网络差时段复测 (P4 有线/同 AP)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>③ 显示 (按期换后端)</t>
+          <t>② 数据处理</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>V0 2047 · 上屏</t>
+          <t>流畅度</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>3-bit 屏 CPU 板上切片上屏</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>丢帧/迟到率 (最新 0.0012 %)</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H76" s="12" t="n">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="I76" s="4" t="inlineStr"/>
     </row>
@@ -11090,7 +11094,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 上行/桥</t>
+          <t>V0 2047 · 上屏</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -11100,17 +11104,17 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>上行出口 12-bit (2 期加 1.2G)</t>
+          <t>3-bit 屏 CPU 板上切片上屏</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
@@ -11119,7 +11123,7 @@
         </is>
       </c>
       <c r="H77" s="12" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="I77" s="4" t="inlineStr"/>
     </row>
@@ -11141,12 +11145,12 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>桥侧接收核对 12-bit</t>
+          <t>上行出口 12-bit (2 期加 1.2G)</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -11160,7 +11164,7 @@
         </is>
       </c>
       <c r="H78" s="12" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I78" s="4" t="inlineStr"/>
     </row>
@@ -11182,12 +11186,12 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit</t>
+          <t>桥侧接收核对 12-bit</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -11223,12 +11227,12 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>主控↔桥联合仿真</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -11242,7 +11246,7 @@
         </is>
       </c>
       <c r="H80" s="12" t="n">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="I80" s="4" t="inlineStr"/>
     </row>
@@ -11259,33 +11263,33 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>1 期 4,296 片/s 桥链路余量仅 0.40%</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr"/>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>监控</t>
+          <t>主控↔桥联合仿真</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>V1准备 · 必须</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H81" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I81" s="4" t="inlineStr">
-        <is>
-          <t>退路降到 22 Hz（用户定保持 24 Hz）</t>
-        </is>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="I81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -11305,18 +11309,18 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2260 从未收到合法 ACK（疑物理通路）</t>
+          <t>1 期 4,296 片/s 桥链路余量仅 0.40%</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>监控</t>
         </is>
       </c>
       <c r="H82" s="12" t="n">
@@ -11324,7 +11328,7 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>验证板一颗一组针对此问题，回板验证</t>
+          <t>退路降到 22 Hz（用户定保持 24 Hz）</t>
         </is>
       </c>
     </row>
@@ -11336,38 +11340,38 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 主控位流</t>
+          <t>V1 2260 · 上行/桥</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>风险</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>1 期主控整合位流</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>V1准备 · 必须</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>2260 从未收到合法 ACK（疑物理通路）</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr"/>
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H83" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I83" s="4" t="inlineStr"/>
+        <v>46308</v>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>验证板一颗一组针对此问题，回板验证</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -11387,12 +11391,12 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>V1-B1</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>V1 主控/桥位流按投板版出齐 (单面 io25 / PRBS / 面 B 桥)</t>
+          <t>1 期主控整合位流</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -11406,7 +11410,7 @@
         </is>
       </c>
       <c r="H84" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I84" s="4" t="inlineStr"/>
     </row>
@@ -11418,7 +11422,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 双面</t>
+          <t>V1 2260 · 主控位流</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -11428,12 +11432,12 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>V1-B1</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>核实 V1 能否双面 (W6 光电冲突)</t>
+          <t>V1 主控/桥位流按投板版出齐 (单面 io25 / PRBS / 面 B 桥)</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -11469,12 +11473,12 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>D38</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>V1 面 B 软件就绪 (IO 电压开关/面B RTL/桥B/JTAG 两器件/--faces AB)</t>
+          <t>核实 V1 能否双面 (W6 光电冲突)</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -11510,17 +11514,17 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>D40</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>双面主控位流编译通过 (TD hold 修复崩溃)</t>
+          <t>V1 面 B 软件就绪 (IO 电压开关/面B RTL/桥B/JTAG 两器件/--faces AB)</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 可选</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
@@ -11529,7 +11533,7 @@
         </is>
       </c>
       <c r="H87" s="12" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I87" s="4" t="inlineStr"/>
     </row>
@@ -11541,7 +11545,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 全链路/板端后端</t>
+          <t>V1 2260 · 双面</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -11551,17 +11555,17 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D40</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>全链路系统仿真 (主机→2260 模型)</t>
+          <t>双面主控位流编译通过 (TD hold 修复崩溃)</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
+          <t>V1准备 · 可选</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
@@ -11570,7 +11574,7 @@
         </is>
       </c>
       <c r="H88" s="12" t="n">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="I88" s="4" t="inlineStr"/>
     </row>
@@ -11592,12 +11596,12 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>V1 真内容板端通路 (voxslice 加 2260 后端)</t>
+          <t>全链路系统仿真 (主机→2260 模型)</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -11623,7 +11627,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 投板对齐/回板</t>
+          <t>V1 2260 · 全链路/板端后端</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -11633,12 +11637,12 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>V1 回板当天一键 bring-up 脚本</t>
+          <t>V1 真内容板端通路 (voxslice 加 2260 后端)</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -11674,12 +11678,12 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>软件引脚/硬件假设对齐 10-15/16 投板版</t>
+          <t>V1 回板当天一键 bring-up 脚本</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -11693,7 +11697,7 @@
         </is>
       </c>
       <c r="H91" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I91" s="4" t="inlineStr"/>
     </row>
@@ -11715,12 +11719,12 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>主控 IO 1.8V 可行性 (用户定最终 2.5V)</t>
+          <t>软件引脚/硬件假设对齐 10-15/16 投板版</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -11751,33 +11755,33 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>灯板 SDO→SDI 0Ω 在 09-18 图上悬空</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr"/>
-      <c r="G93" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+          <t>主控 IO 1.8V 可行性 (用户定最终 2.5V)</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>V1准备 · 必须</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H93" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t>硬件确认并补 0Ω</t>
-        </is>
-      </c>
+        <v>46314</v>
+      </c>
+      <c r="I93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -11797,12 +11801,12 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>1 期面板映射缺 4 项信息</t>
+          <t>灯板 SDO→SDI 0Ω 在 09-18 图上悬空</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr"/>
@@ -11816,7 +11820,7 @@
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>问硬件同事</t>
+          <t>硬件确认并补 0Ω</t>
         </is>
       </c>
     </row>
@@ -11828,38 +11832,36 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · T2 板/1.2G 上行</t>
+          <t>V1 2260 · 投板对齐/回板</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>风险</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>V2-1</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>T2 自研 SoC 板 (32 bit DDR + PL 读带宽)</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>V2 · 必须</t>
-        </is>
-      </c>
-      <c r="G95" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H95" s="12" t="n"/>
+          <t>1 期面板映射缺 4 项信息</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr"/>
+      <c r="G95" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>46308</v>
+      </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>等硬件线 T2 自研板 (32 bit DDR) 投板/回板</t>
+          <t>问硬件同事</t>
         </is>
       </c>
     </row>
@@ -11881,12 +11883,12 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>V2-2</t>
+          <t>V2-1</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>2 期上行 1.2G 实测</t>
+          <t>T2 自研 SoC 板 (32 bit DDR + PL 读带宽)</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -11902,7 +11904,7 @@
       <c r="H96" s="12" t="n"/>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>等 V1 回板 PRBS 实测, 定 1.2G 还是退 1.0G (R1)</t>
+          <t>等硬件线 T2 自研板 (32 bit DDR) 投板/回板</t>
         </is>
       </c>
     </row>
@@ -11924,12 +11926,12 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>D46</t>
+          <t>V2-2</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>V2 桥补齐 面 B + 1.2G PRBS 误码档 (comm_check --phase v2)</t>
+          <t>2 期上行 1.2G 实测</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -11937,17 +11939,15 @@
           <t>V2 · 必须</t>
         </is>
       </c>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H97" s="12" t="n">
-        <v>46315</v>
-      </c>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H97" s="12" t="n"/>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>V2 桥板引脚 + V2 主控 PRBS 位流</t>
+          <t>等 V1 回板 PRBS 实测, 定 1.2G 还是退 1.0G (R1)</t>
         </is>
       </c>
     </row>
@@ -11964,31 +11964,35 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>D46</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>1.2G 可能过不了</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr"/>
-      <c r="G98" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+          <t>V2 桥补齐 面 B + 1.2G PRBS 误码档 (comm_check --phase v2)</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 必须</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H98" s="12" t="n">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
+          <t>V2 桥板引脚 + V2 主控 PRBS 位流</t>
         </is>
       </c>
     </row>
@@ -12000,38 +12004,38 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 主控位流</t>
+          <t>V2 192×216 · T2 板/1.2G 上行</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>风险</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>V2 主控位流跟上主线 (p2_ul1200_b12_v3)</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>V2 · 必须</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>1.2G 可能过不了</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr"/>
+      <c r="G99" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H99" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I99" s="4" t="inlineStr"/>
+        <v>46308</v>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -12051,12 +12055,12 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>D44</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>V2 双面主控位流 (片上 RAM/时序评估)</t>
+          <t>V2 主控位流跟上主线 (p2_ul1200_b12_v3)</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -12070,7 +12074,7 @@
         </is>
       </c>
       <c r="H100" s="12" t="n">
-        <v>46315</v>
+        <v>46311</v>
       </c>
       <c r="I100" s="4" t="inlineStr"/>
     </row>
@@ -12082,7 +12086,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 面板映射/后端</t>
+          <t>V2 192×216 · 主控位流</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -12092,12 +12096,12 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>V2-3</t>
+          <t>D44</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>2 期 192×216 面板映射</t>
+          <t>V2 双面主控位流 (片上 RAM/时序评估)</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -12111,7 +12115,7 @@
         </is>
       </c>
       <c r="H101" s="12" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I101" s="4" t="inlineStr"/>
     </row>
@@ -12133,12 +12137,12 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>V2-7</t>
+          <t>V2-3</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>板端 voxslice --disp p2 (2 期后端)</t>
+          <t>2 期 192×216 面板映射</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -12174,12 +12178,12 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>D48</t>
+          <t>V2-7</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>V2 双面全链路系统仿真 (PC→主控→桥→2260 模型)</t>
+          <t>板端 voxslice --disp p2 (2 期后端)</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -12193,7 +12197,7 @@
         </is>
       </c>
       <c r="H103" s="12" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I103" s="4" t="inlineStr"/>
     </row>
@@ -12205,7 +12209,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 整机</t>
+          <t>V2 192×216 · 面板映射/后端</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -12215,12 +12219,12 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>V2-4</t>
+          <t>D48</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>2 期 30 Hz 整机上转子</t>
+          <t>V2 双面全链路系统仿真 (PC→主控→桥→2260 模型)</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -12228,17 +12232,15 @@
           <t>V2 · 必须</t>
         </is>
       </c>
-      <c r="G104" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H104" s="12" t="n"/>
-      <c r="I104" s="4" t="inlineStr">
-        <is>
-          <t>等 T2 板 (V2-1) + 1.2G 上行 (V2-2)</t>
-        </is>
-      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="I104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -12248,36 +12250,38 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>画面指标 (各期)</t>
+          <t>V2 192×216 · 整机</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>KR1.6</t>
+          <t>V2-4</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>内容刷新率 (实转上屏) (最新 10.8 fps)</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr"/>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1⬜ V2⬜</t>
-        </is>
-      </c>
-      <c r="H105" s="12" t="n">
-        <v>46307</v>
-      </c>
+          <t>2 期 30 Hz 整机上转子</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 必须</t>
+        </is>
+      </c>
+      <c r="G105" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="n"/>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>等 V1 整机 720 RPM 实转 (验证板 11-10 回板)</t>
+          <t>等 T2 板 (V2-1) + 1.2G 上行 (V2-2)</t>
         </is>
       </c>
     </row>
@@ -12299,18 +12303,18 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>KR2.1</t>
+          <t>KR1.6</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>体帧率 (最新 21.7 Hz)</t>
+          <t>内容刷新率 (实转上屏) (最新 10.8 fps)</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr"/>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1🔵 V2⬜</t>
+          <t>V0✅ V1⬜ V2⬜</t>
         </is>
       </c>
       <c r="H106" s="12" t="n">
@@ -12318,7 +12322,7 @@
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>等 V1 回板实转 720 RPM×358 片</t>
+          <t>等 V1 整机 720 RPM 实转 (验证板 11-10 回板)</t>
         </is>
       </c>
     </row>
@@ -12340,18 +12344,18 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>KR3.1</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>每面像素数 (最新 28800 px)</t>
+          <t>体帧率 (最新 21.7 Hz)</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1✅ V2⬜</t>
+          <t>V0✅ V1🔵 V2⬜</t>
         </is>
       </c>
       <c r="H107" s="12" t="n">
@@ -12359,7 +12363,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>等 2 期 192×216 屏</t>
+          <t>等 V1 回板实转 720 RPM×358 片</t>
         </is>
       </c>
     </row>
@@ -12381,18 +12385,18 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>KR3.2</t>
+          <t>KR3.1</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>每圈片数 (最新 142 片)</t>
+          <t>每面像素数 (最新 28800 px)</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr"/>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1🔵 V2⬜</t>
+          <t>V0✅ V1✅ V2⬜</t>
         </is>
       </c>
       <c r="H108" s="12" t="n">
@@ -12400,7 +12404,7 @@
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>等 V1 回板实测</t>
+          <t>等 2 期 192×216 屏</t>
         </is>
       </c>
     </row>
@@ -12422,18 +12426,18 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>KR4.1</t>
+          <t>KR3.2</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>色深 (最新 3 bit/通道)</t>
+          <t>每圈片数 (最新 142 片)</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1🔵 V2🔵</t>
+          <t>V0✅ V1🔵 V2⬜</t>
         </is>
       </c>
       <c r="H109" s="12" t="n">
@@ -12441,50 +12445,50 @@
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>等 V1 2260 回板上屏</t>
+          <t>等 V1 回板实测</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>④ 运维保障</t>
+          <t>③ 显示 (按期换后端)</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>开机即用</t>
+          <t>画面指标 (各期)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>KR4.1</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>开机自动演示 + 转速门控</t>
-        </is>
-      </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G110" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>色深 (最新 3 bit/通道)</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr"/>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1🔵 V2🔵</t>
         </is>
       </c>
       <c r="H110" s="12" t="n">
         <v>46307</v>
       </c>
-      <c r="I110" s="4" t="inlineStr"/>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>等 V1 2260 回板上屏</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12504,12 +12508,12 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>启动提速 + 启动屏显 (含原 backlog B1)</t>
+          <t>开机自动演示 + 转速门控</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -12523,7 +12527,7 @@
         </is>
       </c>
       <c r="H111" s="12" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="I111" s="4" t="inlineStr"/>
     </row>
@@ -12545,12 +12549,12 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>开机默认动画 = 立方体动图 (用户 10-16 提)</t>
+          <t>启动提速 + 启动屏显 (含原 backlog B1)</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
@@ -12564,7 +12568,7 @@
         </is>
       </c>
       <c r="H112" s="12" t="n">
-        <v>46311</v>
+        <v>46309</v>
       </c>
       <c r="I112" s="4" t="inlineStr"/>
     </row>
@@ -12586,17 +12590,17 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>D47</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>系统从 QSPI 加载 (去 TF/eMMC 准备; 03 板试)</t>
+          <t>开机默认动画 = 立方体动图 (用户 10-16 提)</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>V2 · 加分</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -12605,13 +12609,9 @@
         </is>
       </c>
       <c r="H113" s="12" t="n">
-        <v>46315</v>
-      </c>
-      <c r="I113" s="4" t="inlineStr">
-        <is>
-          <t>T2 板 QSPI 选 64MiB / 厂商驱动提速</t>
-        </is>
-      </c>
+        <v>46311</v>
+      </c>
+      <c r="I113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -12626,29 +12626,37 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>KR8.1</t>
+          <t>D47</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>上电到 0° 片亮起 (停转) (最新 12.4 s)</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr"/>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>系统从 QSPI 加载 (去 TF/eMMC 准备; 03 板试)</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 加分</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H114" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I114" s="4" t="inlineStr"/>
+        <v>46315</v>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>T2 板 QSPI 选 64MiB / 厂商驱动提速</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -12668,22 +12676,22 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>KR8.4</t>
+          <t>KR8.1</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>上电到转稳全亮 (最新 26 s)</t>
+          <t>上电到 0° 片亮起 (停转) (最新 12.4 s)</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>V0— V1— V2—</t>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H115" s="12" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="I115" s="4" t="inlineStr"/>
     </row>
@@ -12695,32 +12703,28 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>联网/找板/自愈</t>
+          <t>开机即用</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>KR8.4</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>开机自连 WiFi</t>
-        </is>
-      </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G116" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>上电到转稳全亮 (最新 26 s)</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>V0— V1— V2—</t>
         </is>
       </c>
       <c r="H116" s="12" t="n">
@@ -12746,12 +12750,12 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS)</t>
+          <t>开机自连 WiFi</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
@@ -12765,7 +12769,7 @@
         </is>
       </c>
       <c r="H117" s="12" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="I117" s="4" t="inlineStr"/>
     </row>
@@ -12787,12 +12791,12 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 (服务监护/看门狗/兜底热点/povnetd 1.2)</t>
+          <t>按名字找板 (mDNS)</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -12806,7 +12810,7 @@
         </is>
       </c>
       <c r="H118" s="12" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="I118" s="4" t="inlineStr"/>
     </row>
@@ -12828,12 +12832,12 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复 ≤30 s (03 长跑断 155 s)</t>
+          <t>不插串口永远连得上 (服务监护/看门狗/兜底热点/povnetd 1.2)</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -12847,7 +12851,7 @@
         </is>
       </c>
       <c r="H119" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I119" s="4" t="inlineStr"/>
     </row>
@@ -12869,12 +12873,12 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>D43</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>povnetd 1.3 网络自愈回归修复</t>
+          <t>WiFi 断线恢复 ≤30 s (03 长跑断 155 s)</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -12905,27 +12909,31 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>KR8.2</t>
+          <t>D43</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>按名字找到板子 (最新 19.8 s)</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr"/>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>povnetd 1.3 网络自愈回归修复</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 必须</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H121" s="12" t="n">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="I121" s="4" t="inlineStr"/>
     </row>
@@ -12937,32 +12945,28 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>远程运维/升级 (含 JTAG 灌桥)</t>
+          <t>联网/找板/自愈</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR8.2</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>转子运维 (netguard-lite / 遥测 / 远程升级)</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G122" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>按名字找到板子 (最新 19.8 s)</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr"/>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H122" s="12" t="n">
@@ -12988,17 +12992,17 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>主控经 JTAG 给桥灌位流 (V1 远程升级软件)</t>
+          <t>转子运维 (netguard-lite / 遥测 / 远程升级)</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
@@ -13007,7 +13011,7 @@
         </is>
       </c>
       <c r="H123" s="12" t="n">
-        <v>46314</v>
+        <v>46309</v>
       </c>
       <c r="I123" s="4" t="inlineStr"/>
     </row>
@@ -13029,17 +13033,17 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>D42</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>03 板软件跟进主线</t>
+          <t>主控经 JTAG 给桥灌位流 (V1 远程升级软件)</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>V0 · 加分</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
@@ -13065,27 +13069,31 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>KR8.3</t>
+          <t>D42</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>需要串口 (1=需要) (最新 0 是/否)</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr"/>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>03 板软件跟进主线</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H125" s="12" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="I125" s="4" t="inlineStr"/>
     </row>
@@ -13107,12 +13115,12 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>KR8.3</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用) (最新 1 是/否)</t>
+          <t>需要串口 (1=需要) (最新 0 是/否)</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr"/>
@@ -13122,7 +13130,7 @@
         </is>
       </c>
       <c r="H126" s="12" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="I126" s="4" t="inlineStr"/>
     </row>
@@ -13144,12 +13152,12 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>KR9.2</t>
+          <t>KR9.1</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>远程升级失败自动回滚 (1=有) (最新 1 是/否)</t>
+          <t>转子遥测可用 (1=可用) (最新 1 是/否)</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr"/>
@@ -13171,40 +13179,34 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>主控↔桥通信</t>
+          <t>远程运维/升级 (含 JTAG 灌桥)</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>KR9.2</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>C1 台架彩排 + 1.2G 误码测试</t>
-        </is>
-      </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>V1准备 · 加分</t>
-        </is>
-      </c>
-      <c r="G128" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H128" s="12" t="n"/>
-      <c r="I128" s="4" t="inlineStr">
-        <is>
-          <t>不做 (用户 10-19 定), 由 D39 到板 comm_check 代替</t>
-        </is>
-      </c>
+          <t>远程升级失败自动回滚 (1=有) (最新 1 是/否)</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr"/>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -13224,28 +13226,30 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信全功能 (配置/状态/错误恢复/升级)</t>
+          <t>C1 台架彩排 + 1.2G 误码测试</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
-        </is>
-      </c>
-      <c r="G129" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H129" s="12" t="n">
-        <v>46312</v>
-      </c>
-      <c r="I129" s="4" t="inlineStr"/>
+          <t>V1准备 · 加分</t>
+        </is>
+      </c>
+      <c r="G129" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="n"/>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>不做 (用户 10-19 定), 由 D39 到板 comm_check 代替</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -13265,12 +13269,12 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 + PRBS 位流</t>
+          <t>SoC↔桥通信全功能 (配置/状态/错误恢复/升级)</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -13284,7 +13288,7 @@
         </is>
       </c>
       <c r="H130" s="12" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="I130" s="4" t="inlineStr"/>
     </row>
@@ -13296,7 +13300,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>可靠性验证 (冷启动/长跑)</t>
+          <t>主控↔桥通信</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
@@ -13306,17 +13310,17 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>V0A</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>V0 重启验收 (不插串口: 找回/守护/开机默认/WiFi/推流/稳定 6 项)</t>
+          <t>SoC↔桥通信专项验证包 + PRBS 位流</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>V0 · 必须</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
@@ -13325,7 +13329,7 @@
         </is>
       </c>
       <c r="H131" s="12" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="I131" s="4" t="inlineStr"/>
     </row>
@@ -13347,12 +13351,12 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>V0A</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>冷启动认不到 TF 卡 (03 停在 u-boot)</t>
+          <t>V0 重启验收 (不插串口: 找回/守护/开机默认/WiFi/推流/稳定 6 项)</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -13366,7 +13370,7 @@
         </is>
       </c>
       <c r="H132" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I132" s="4" t="inlineStr"/>
     </row>
@@ -13388,17 +13392,17 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>D49</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+          <t>冷启动认不到 TF 卡 (03 停在 u-boot)</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>V0 · 加分</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
@@ -13407,7 +13411,7 @@
         </is>
       </c>
       <c r="H133" s="12" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I133" s="4" t="inlineStr"/>
     </row>
@@ -13424,27 +13428,31 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D49</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr"/>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H134" s="12" t="n">
-        <v>46312</v>
+        <v>46315</v>
       </c>
       <c r="I134" s="4" t="inlineStr"/>
     </row>
@@ -13466,12 +13474,12 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
+          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr"/>
@@ -13481,7 +13489,7 @@
         </is>
       </c>
       <c r="H135" s="12" t="n">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="I135" s="4" t="inlineStr"/>
     </row>
@@ -13498,33 +13506,29 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
+          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr"/>
-      <c r="G136" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H136" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I136" s="4" t="inlineStr">
-        <is>
-          <t>T2 板留 eMMC、打胶</t>
-        </is>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="I136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -13534,7 +13538,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>开发环境</t>
+          <t>可靠性验证 (冷启动/长跑)</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
@@ -13544,24 +13548,65 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>D 盘 EIO（IP-guard 驱动）</t>
+          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr"/>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t>监控</t>
+      <c r="G137" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H137" s="12" t="n">
         <v>46308</v>
       </c>
       <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>T2 板留 eMMC、打胶</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>④ 运维保障</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>开发环境</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>风险</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>D 盘 EIO（IP-guard 驱动）</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr"/>
+      <c r="G138" s="8" t="inlineStr">
+        <is>
+          <t>监控</t>
+        </is>
+      </c>
+      <c r="H138" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I138" s="4" t="inlineStr">
         <is>
           <t>看门狗自动重挂 + 构建放 WSL 本地盘</t>
         </is>
@@ -13581,7 +13626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J212"/>
+  <dimension ref="A1:J213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13656,12 +13701,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>48/48</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>KR 25/25 + 交付 22/22 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
+          <t>KR 25/25 + 交付 23/23 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
         </is>
       </c>
       <c r="G4" s="17" t="n">
@@ -13684,16 +13729,16 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>63/69</t>
+          <t>64/70</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>KR 18/24 + 交付 45/45 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
+          <t>KR 18/24 + 交付 46/46 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
         </is>
       </c>
       <c r="G5" s="17" t="n">
@@ -13716,16 +13761,16 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>0.8717948717948718</v>
+        <v>0.8734177215189873</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>68/78</t>
+          <t>69/79</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>KR 17/24 + 交付 51/54 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 17/24 + 交付 52/55 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="17" t="n">
@@ -13859,10 +13904,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>0.913</v>
+        <v>0.9143</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>0.8718</v>
+        <v>0.8734</v>
       </c>
     </row>
     <row r="13">
@@ -14964,26 +15009,26 @@
     </row>
     <row r="59">
       <c r="A59" s="12" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46315</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>D50</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
+          <t>推流卡顿修: 积压在 TCP 缓冲 (板端串行收帧 + auto 无余量); voxslice 1.1 最新帧优先 (不撕裂, 丢帧可计) + 主机 auto 余量 0.88; 02 板注入停顿修前不恢复→修后 ≤0.22 s, 583 auto p50 91→49 ms; 主会话复跑 verify 10/0</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d22_reach/README.md</t>
+          <t>dr1v90 2af5f9f</t>
         </is>
       </c>
     </row>
@@ -14991,24 +15036,24 @@
       <c r="A60" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>D32</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
+          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>dr1v90</t>
+          <t>dr1v90 d22_reach/README.md</t>
         </is>
       </c>
     </row>
@@ -15016,9 +15061,9 @@
       <c r="A61" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -15028,12 +15073,12 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
+          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/acc32_*.log</t>
+          <t>dr1v90</t>
         </is>
       </c>
     </row>
@@ -15041,24 +15086,24 @@
       <c r="A62" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B62" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
+          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>progress/v0_accept/acc32_*.log</t>
         </is>
       </c>
     </row>
@@ -15066,24 +15111,24 @@
       <c r="A63" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>补录</t>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>KR4.2</t>
+          <t>用户</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
+          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15093,22 +15138,22 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>补录</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
+          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -15118,22 +15163,22 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
+          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 card03</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15143,22 +15188,22 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
+          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2b111f0</t>
+          <t>dr1v90 card03</t>
         </is>
       </c>
     </row>
@@ -15168,22 +15213,22 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
+          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
+          <t>dr1v90 2b111f0</t>
         </is>
       </c>
     </row>
@@ -15191,24 +15236,24 @@
       <c r="A68" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B68" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
+          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
         </is>
       </c>
     </row>
@@ -15216,24 +15261,24 @@
       <c r="A69" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
+          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 97a10cf</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15243,22 +15288,22 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
+          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 7253608</t>
+          <t>dr1v90 97a10cf</t>
         </is>
       </c>
     </row>
@@ -15266,24 +15311,24 @@
       <c r="A71" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B71" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D34</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
+          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 7253608</t>
         </is>
       </c>
     </row>
@@ -15291,24 +15336,24 @@
       <c r="A72" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
+          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 23474c7</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15323,17 +15368,17 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
+          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 f2584d9</t>
+          <t>dr1v90 23474c7</t>
         </is>
       </c>
     </row>
@@ -15348,17 +15393,17 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>D38</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
+          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ad201f9</t>
+          <t>dr1v90 f2584d9</t>
         </is>
       </c>
     </row>
@@ -15368,22 +15413,22 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>V1主控</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
+          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>本机构建</t>
+          <t>dr1v90 ad201f9</t>
         </is>
       </c>
     </row>
@@ -15398,17 +15443,17 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V1主控</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
+          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d39-comm b69f6d8</t>
+          <t>本机构建</t>
         </is>
       </c>
     </row>
@@ -15418,22 +15463,22 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>V2-7</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
+          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ff1846a</t>
+          <t>dr1v90 task/d39-comm b69f6d8</t>
         </is>
       </c>
     </row>
@@ -15448,17 +15493,17 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>V2-7</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
+          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3ef6b06</t>
+          <t>dr1v90 ff1846a</t>
         </is>
       </c>
     </row>
@@ -15468,22 +15513,22 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
+          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>progress/d29_coldboot</t>
+          <t>dr1v90 3ef6b06</t>
         </is>
       </c>
     </row>
@@ -15491,24 +15536,24 @@
       <c r="A80" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B80" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>D11;D39</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
+          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>用户 10-19</t>
+          <t>progress/d29_coldboot</t>
         </is>
       </c>
     </row>
@@ -15516,24 +15561,24 @@
       <c r="A81" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D11;D39</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
+          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6333eb5</t>
+          <t>用户 10-19</t>
         </is>
       </c>
     </row>
@@ -15548,67 +15593,67 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>D42;D43</t>
+          <t>D41</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
+          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 8689db2 / 6e6d47b</t>
+          <t>dr1v90 6333eb5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D42;D43</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
+          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1017_03_24h</t>
+          <t>dr1v90 8689db2 / 6e6d47b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46313</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
+          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/SPEC.md</t>
+          <t>progress/soak_v0/1017_03_24h</t>
         </is>
       </c>
     </row>
@@ -15616,24 +15661,24 @@
       <c r="A85" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>V2-5</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
+          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_fmt/README.md</t>
+          <t>dr1v90 d27_link/SPEC.md</t>
         </is>
       </c>
     </row>
@@ -15648,17 +15693,17 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>D28b</t>
+          <t>V2-5</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
+          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/回板当天.md</t>
+          <t>dr1v90 v2_fmt/README.md</t>
         </is>
       </c>
     </row>
@@ -15666,24 +15711,24 @@
       <c r="A87" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>进展</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>D27b</t>
+          <t>D28b</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
+          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/README.md</t>
+          <t>dr1v90 v1_bringup/回板当天.md</t>
         </is>
       </c>
     </row>
@@ -15691,24 +15736,24 @@
       <c r="A88" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>V2-6</t>
+          <t>D27b</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
+          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 gw5a_bridge/p2/README.md</t>
+          <t>dr1v90 d27_link/README.md</t>
         </is>
       </c>
     </row>
@@ -15718,22 +15763,22 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>全套</t>
+          <t>V2-6</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
+          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ~/full_*.log</t>
+          <t>dr1v90 gw5a_bridge/p2/README.md</t>
         </is>
       </c>
     </row>
@@ -15743,22 +15788,22 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>修复</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>全套</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
+          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 slice/SPEC.md §13.2</t>
+          <t>dr1v90 ~/full_*.log</t>
         </is>
       </c>
     </row>
@@ -15768,22 +15813,22 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
+          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1016_wkend_24h</t>
+          <t>dr1v90 slice/SPEC.md §13.2</t>
         </is>
       </c>
     </row>
@@ -15793,7 +15838,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -15803,37 +15848,37 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
+          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1017_*.log</t>
+          <t>progress/soak_v0/1016_wkend_24h</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>部署</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
+          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22c.board.log</t>
+          <t>progress/v0_accept/accept_1017_*.log</t>
         </is>
       </c>
     </row>
@@ -15841,9 +15886,9 @@
       <c r="A94" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -15853,12 +15898,12 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
+          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d22c.board.log</t>
         </is>
       </c>
     </row>
@@ -15866,24 +15911,24 @@
       <c r="A95" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
+          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board5.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15891,9 +15936,9 @@
       <c r="A96" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -15903,12 +15948,12 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
+          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d21.board5.log</t>
         </is>
       </c>
     </row>
@@ -15923,12 +15968,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
+          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -15941,9 +15986,9 @@
       <c r="A98" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -15953,12 +15998,12 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
+          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_A fps_B</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -15966,9 +16011,9 @@
       <c r="A99" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -15978,12 +16023,12 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
+          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_C</t>
+          <t>soak_runs/fps_A fps_B</t>
         </is>
       </c>
     </row>
@@ -15991,24 +16036,24 @@
       <c r="A100" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
+          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20d-ackrps db4ec93</t>
+          <t>soak_runs/fps_C</t>
         </is>
       </c>
     </row>
@@ -16023,17 +16068,17 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
+          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
+          <t>dr1v90 task/d20d-ackrps db4ec93</t>
         </is>
       </c>
     </row>
@@ -16043,22 +16088,22 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
+          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_D</t>
+          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
         </is>
       </c>
     </row>
@@ -16066,9 +16111,9 @@
       <c r="A103" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -16078,12 +16123,12 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
+          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>soak_runs/fps_D</t>
         </is>
       </c>
     </row>
@@ -16091,24 +16136,24 @@
       <c r="A104" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
+          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>~/rv_deploy.board.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16116,24 +16161,24 @@
       <c r="A105" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
+          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_deploy.board.log</t>
         </is>
       </c>
     </row>
@@ -16141,24 +16186,24 @@
       <c r="A106" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>验收</t>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
+          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16168,22 +16213,22 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>开工</t>
+          <t>验收</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>D20e/D23</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
+          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
+          <t>progress/v0_accept/</t>
         </is>
       </c>
     </row>
@@ -16191,24 +16236,24 @@
       <c r="A108" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B108" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>开工</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D20e/D23</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
+          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
         </is>
       </c>
     </row>
@@ -16216,24 +16261,24 @@
       <c r="A109" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B109" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
+          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -16248,12 +16293,12 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
+          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -16266,24 +16311,24 @@
       <c r="A111" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
+          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1016_d20e.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16291,24 +16336,24 @@
       <c r="A112" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>KR7.3/D24</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
+          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>progress/v0_accept/accept_1016_d20e.log</t>
         </is>
       </c>
     </row>
@@ -16316,24 +16361,24 @@
       <c r="A113" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>KR7.3/D24</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
+          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>D:\card03</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16341,24 +16386,24 @@
       <c r="A114" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>D25</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
+          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>D:\card03</t>
         </is>
       </c>
     </row>
@@ -16366,24 +16411,24 @@
       <c r="A115" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D25</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
+          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\cap_COM29.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16398,17 +16443,17 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
+          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20d_ackrps d20c_fps</t>
+          <t>D:\card03\cap_COM29.log</t>
         </is>
       </c>
     </row>
@@ -16416,24 +16461,24 @@
       <c r="A117" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
+          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d12_latency/RESULTS.md</t>
+          <t>dr1v90 d20d_ackrps d20c_fps</t>
         </is>
       </c>
     </row>
@@ -16448,17 +16493,17 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
+          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d9_e2e/</t>
+          <t>dr1v90 d12_latency/RESULTS.md</t>
         </is>
       </c>
     </row>
@@ -16466,24 +16511,24 @@
       <c r="A119" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
+          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\boot03.log</t>
+          <t>dr1v90 d9_e2e/</t>
         </is>
       </c>
     </row>
@@ -16491,24 +16536,24 @@
       <c r="A120" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
+          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
+          <t>D:\card03\boot03.log</t>
         </is>
       </c>
     </row>
@@ -16516,24 +16561,24 @@
       <c r="A121" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>开工</t>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
+          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
+          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
         </is>
       </c>
     </row>
@@ -16543,22 +16588,22 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>方案</t>
+          <t>开工</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
+          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d29_sdboot/PLAN.md</t>
+          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
         </is>
       </c>
     </row>
@@ -16566,24 +16611,24 @@
       <c r="A123" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B123" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>方案</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
+          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/</t>
+          <t>dr1v90 d29_sdboot/PLAN.md</t>
         </is>
       </c>
     </row>
@@ -16591,24 +16636,24 @@
       <c r="A124" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>修复</t>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
+          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
+          <t>dr1v90 v1_bringup/</t>
         </is>
       </c>
     </row>
@@ -16618,22 +16663,22 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>进展</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>V2-3</t>
+          <t>D30</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
+          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_map/DESIGN.md</t>
+          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
         </is>
       </c>
     </row>
@@ -16643,47 +16688,47 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>评估</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>V2-3</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
+          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d31_v1odd/REPORT.md</t>
+          <t>dr1v90 v2_map/DESIGN.md</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="12" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B127" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46311</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>评估</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D31</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
+          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/report.md</t>
+          <t>dr1v90 d31_v1odd/REPORT.md</t>
         </is>
       </c>
     </row>
@@ -16691,24 +16736,24 @@
       <c r="A128" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>QoS</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
+          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>~/qos_runs</t>
+          <t>progress/soak_v0/report.md</t>
         </is>
       </c>
     </row>
@@ -16723,17 +16768,17 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>D16b</t>
+          <t>QoS</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
+          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16b-tile 7936b7e</t>
+          <t>~/qos_runs</t>
         </is>
       </c>
     </row>
@@ -16741,24 +16786,24 @@
       <c r="A130" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B130" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D16b</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
+          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>dr1v90 task/d16b-tile 7936b7e</t>
         </is>
       </c>
     </row>
@@ -16773,12 +16818,12 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
+          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -16791,24 +16836,24 @@
       <c r="A132" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B132" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>V1/V2</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
+          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>budget/rpm_range_2026-10-15.md</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -16816,24 +16861,24 @@
       <c r="A133" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>V1/V2</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
+          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>progress/realspin_v0/</t>
+          <t>budget/rpm_range_2026-10-15.md</t>
         </is>
       </c>
     </row>
@@ -16841,19 +16886,19 @@
       <c r="A134" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B134" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
+          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -16866,24 +16911,24 @@
       <c r="A135" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
+          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20-smooth 83a5fd7</t>
+          <t>progress/realspin_v0/</t>
         </is>
       </c>
     </row>
@@ -16891,24 +16936,24 @@
       <c r="A136" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B136" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
+          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 e215176</t>
+          <t>dr1v90 task/d20-smooth 83a5fd7</t>
         </is>
       </c>
     </row>
@@ -16916,24 +16961,24 @@
       <c r="A137" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
+          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d19-halfrev 1beafa6</t>
+          <t>dr1v90 e215176</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16993,17 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>D20b</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
+          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20b-sim 9081f62</t>
+          <t>dr1v90 task/d19-halfrev 1beafa6</t>
         </is>
       </c>
     </row>
@@ -16968,22 +17013,22 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D20b</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
+          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/merge-d19-d20 106364e</t>
+          <t>dr1v90 task/d20b-sim 9081f62</t>
         </is>
       </c>
     </row>
@@ -16991,24 +17036,24 @@
       <c r="A140" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B140" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>D19/D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
+          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/merge-d19-d20 106364e</t>
         </is>
       </c>
     </row>
@@ -17016,24 +17061,24 @@
       <c r="A141" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D19/D20</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
+          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband adeba44</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -17043,22 +17088,22 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>D20/D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
+          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>~/realspin/tcp</t>
+          <t>dr1v90 task/d21-nband adeba44</t>
         </is>
       </c>
     </row>
@@ -17066,24 +17111,24 @@
       <c r="A143" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B143" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D20/D22</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
+          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>~/realspin/tcp</t>
         </is>
       </c>
     </row>
@@ -17091,9 +17136,9 @@
       <c r="A144" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B144" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B144" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -17103,12 +17148,12 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
+          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach ee4a55c</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -17123,17 +17168,17 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
+          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20c-fps 338eaaf</t>
+          <t>dr1v90 task/d22-reach ee4a55c</t>
         </is>
       </c>
     </row>
@@ -17143,7 +17188,7 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>复验</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -17153,12 +17198,12 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
+          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d20c.v.log</t>
+          <t>dr1v90 task/d20c-fps 338eaaf</t>
         </is>
       </c>
     </row>
@@ -17168,22 +17213,22 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>复验</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
+          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d8-cosim 85dfe51</t>
+          <t>~/rv_d20c.v.log</t>
         </is>
       </c>
     </row>
@@ -17191,9 +17236,9 @@
       <c r="A148" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B148" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -17203,12 +17248,12 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
+          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/d8-cosim 85dfe51</t>
         </is>
       </c>
     </row>
@@ -17216,24 +17261,24 @@
       <c r="A149" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>D22/D20</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
+          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/netdiag_1015_1814</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -17241,24 +17286,24 @@
       <c r="A150" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B150" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22/D20</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
+          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board.log</t>
+          <t>soak_runs/netdiag_1015_1814</t>
         </is>
       </c>
     </row>
@@ -17273,17 +17318,17 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
+          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach</t>
+          <t>~/rv_d21.board.log</t>
         </is>
       </c>
     </row>
@@ -17303,7 +17348,7 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
+          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
@@ -17316,9 +17361,9 @@
       <c r="A153" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B153" s="5" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B153" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -17328,12 +17373,12 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
+          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22.board2.log</t>
+          <t>dr1v90 task/d22-reach</t>
         </is>
       </c>
     </row>
@@ -17343,22 +17388,22 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
+          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>~/d21b_forensic.log</t>
+          <t>~/rv_d22.board2.log</t>
         </is>
       </c>
     </row>
@@ -17373,17 +17418,17 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
+          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach 0d1da09</t>
+          <t>~/d21b_forensic.log</t>
         </is>
       </c>
     </row>
@@ -17393,7 +17438,7 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -17403,12 +17448,12 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
+          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22b.board.log</t>
+          <t>dr1v90 task/d22-reach 0d1da09</t>
         </is>
       </c>
     </row>
@@ -17418,7 +17463,7 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -17428,12 +17473,12 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
+          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach e438a12</t>
+          <t>~/rv_d22b.board.log</t>
         </is>
       </c>
     </row>
@@ -17443,47 +17488,47 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
+          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband 084bba3</t>
+          <t>dr1v90 task/d22-reach e438a12</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B159" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>dr1v90 task/d21-nband 084bba3</t>
         </is>
       </c>
     </row>
@@ -17491,24 +17536,24 @@
       <c r="A160" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B160" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -17516,24 +17561,24 @@
       <c r="A161" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B161" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B161" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17598,7 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
@@ -17566,24 +17611,24 @@
       <c r="A163" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B163" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B163" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -17591,24 +17636,24 @@
       <c r="A164" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B164" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B164" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -17616,9 +17661,9 @@
       <c r="A165" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B165" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -17628,12 +17673,12 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -17641,9 +17686,9 @@
       <c r="A166" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B166" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B166" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -17653,12 +17698,12 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -17666,24 +17711,24 @@
       <c r="A167" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B167" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17691,24 +17736,24 @@
       <c r="A168" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B168" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -17716,24 +17761,24 @@
       <c r="A169" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B169" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B169" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -17741,24 +17786,24 @@
       <c r="A170" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B170" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B170" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17766,9 +17811,9 @@
       <c r="A171" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B171" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -17778,12 +17823,12 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -17791,24 +17836,24 @@
       <c r="A172" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B172" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B172" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -17816,9 +17861,9 @@
       <c r="A173" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B173" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B173" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -17828,12 +17873,12 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -17841,24 +17886,24 @@
       <c r="A174" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B174" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -17866,24 +17911,24 @@
       <c r="A175" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B175" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B175" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -17891,24 +17936,24 @@
       <c r="A176" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B176" s="5" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B176" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
@@ -17916,24 +17961,24 @@
       <c r="A177" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B177" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
@@ -17941,24 +17986,24 @@
       <c r="A178" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B178" s="5" t="inlineStr">
-        <is>
-          <t>开始</t>
+      <c r="B178" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -17966,24 +18011,24 @@
       <c r="A179" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B179" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
@@ -17991,49 +18036,49 @@
       <c r="A180" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B180" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B180" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B181" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -18048,17 +18093,17 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -18073,17 +18118,17 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -18091,9 +18136,9 @@
       <c r="A184" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B184" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -18103,12 +18148,12 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -18116,9 +18161,9 @@
       <c r="A185" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B185" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B185" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -18128,12 +18173,12 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -18141,24 +18186,24 @@
       <c r="A186" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B186" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -18166,9 +18211,9 @@
       <c r="A187" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B187" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B187" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -18178,12 +18223,12 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18198,17 +18243,17 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -18216,9 +18261,9 @@
       <c r="A189" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B189" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -18228,12 +18273,12 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -18253,7 +18298,7 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
@@ -18266,24 +18311,24 @@
       <c r="A191" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B191" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B191" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18291,24 +18336,24 @@
       <c r="A192" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B192" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -18316,24 +18361,24 @@
       <c r="A193" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B193" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B193" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18348,17 +18393,17 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -18366,19 +18411,19 @@
       <c r="A195" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B195" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
@@ -18391,9 +18436,9 @@
       <c r="A196" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B196" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B196" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -18403,12 +18448,12 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18416,24 +18461,24 @@
       <c r="A197" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B197" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B197" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -18441,9 +18486,9 @@
       <c r="A198" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B198" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B198" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -18453,12 +18498,12 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18466,9 +18511,9 @@
       <c r="A199" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B199" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B199" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -18478,12 +18523,12 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -18491,24 +18536,24 @@
       <c r="A200" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B200" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B200" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18516,24 +18561,24 @@
       <c r="A201" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B201" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B201" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -18546,15 +18591,19 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C202" s="4" t="inlineStr"/>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18562,15 +18611,15 @@
       <c r="A203" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B203" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B203" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr"/>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
@@ -18583,20 +18632,20 @@
       <c r="A204" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B204" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B204" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr"/>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -18609,19 +18658,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C205" s="4" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="C205" s="4" t="inlineStr"/>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -18636,12 +18681,12 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
@@ -18661,12 +18706,12 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
@@ -18686,12 +18731,12 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
@@ -18711,12 +18756,12 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
@@ -18736,17 +18781,17 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18754,24 +18799,24 @@
       <c r="A211" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B211" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B211" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
@@ -18779,18 +18824,43 @@
       <c r="A212" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B212" s="23" t="inlineStr">
+      <c r="B212" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B213" s="23" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C212" s="4" t="inlineStr"/>
-      <c r="D212" s="4" t="inlineStr">
+      <c r="C213" s="4" t="inlineStr"/>
+      <c r="D213" s="4" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E212" s="4" t="inlineStr">
+      <c r="E213" s="4" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -23533,7 +23603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23577,7 +23647,7 @@
         <v>46307</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>5</v>
@@ -23591,7 +23661,7 @@
         <v>46308</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>7</v>
@@ -23605,7 +23675,7 @@
         <v>46309</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>8</v>
@@ -23619,7 +23689,7 @@
         <v>46310</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>12</v>
@@ -23633,7 +23703,7 @@
         <v>46311</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>20</v>
@@ -23647,7 +23717,7 @@
         <v>46312</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>28</v>
@@ -23661,7 +23731,7 @@
         <v>46313</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>28</v>
@@ -23675,7 +23745,7 @@
         <v>46314</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>32</v>
@@ -23689,13 +23759,13 @@
         <v>46315</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -23703,10 +23773,10 @@
         <v>46316</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" s="5" t="n"/>
     </row>
@@ -23715,10 +23785,10 @@
         <v>46317</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="5" t="n"/>
     </row>
@@ -23727,10 +23797,10 @@
         <v>46318</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" s="5" t="n"/>
     </row>
@@ -23739,10 +23809,10 @@
         <v>46319</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" s="5" t="n"/>
     </row>
@@ -26132,6 +26202,44 @@
       <c r="H86" s="4" t="inlineStr">
         <is>
           <t>dr1v90 e97390e+771abc4 (V1 g2 位流 0 违例 ERAM 不变; voxslice 1.0 运行时网格; 联合复验 d45_g2 5/0 d45_front 17/0 sim_v1 d38 11/0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>D50</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>推流卡顿修 (网络一抖后积压不消 → 板端最新帧优先 + auto 留 12% 余量)</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>1;5</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>dr1v90 2af5f9f (voxslice 1.1 已上 02 板; 注入停顿后 0.13-0.22 s 恢复, auto p50 40-60 ms; 主会话复验 V1-V8 PASS)</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-20.xlsx
+++ b/docs/progress/显性目的进度_2026-10-20.xlsx
@@ -8580,7 +8580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I138"/>
+  <dimension ref="A1:I140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>14/14</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
           <t>13/13</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>12/12</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
@@ -8752,16 +8752,16 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
+          <t>22/25</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
           <t>21/24</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>20/23</t>
-        </is>
-      </c>
       <c r="E6" s="9" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.875</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -9136,12 +9136,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
@@ -9318,16 +9318,16 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
@@ -11062,68 +11062,72 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>D51</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>丢帧/迟到率 (最新 0.0012 %)</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr"/>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>去 600 rpm 帧率台阶 (300-1200 rpm 帧率随转速连续)</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 必须</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H76" s="12" t="n">
-        <v>46310</v>
-      </c>
-      <c r="I76" s="4" t="inlineStr"/>
+        <v>46315</v>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>真转复测; &gt;1020 rpm 平顶 30 fps (估转速)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>③ 显示 (按期换后端)</t>
+          <t>② 数据处理</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>V0 2047 · 上屏</t>
+          <t>流畅度</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>3-bit 屏 CPU 板上切片上屏</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>丢帧/迟到率 (最新 0.0012 %)</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H77" s="12" t="n">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="I77" s="4" t="inlineStr"/>
     </row>
@@ -11135,7 +11139,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 上行/桥</t>
+          <t>V0 2047 · 上屏</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -11145,17 +11149,17 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>上行出口 12-bit (2 期加 1.2G)</t>
+          <t>3-bit 屏 CPU 板上切片上屏</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
@@ -11164,7 +11168,7 @@
         </is>
       </c>
       <c r="H78" s="12" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="I78" s="4" t="inlineStr"/>
     </row>
@@ -11186,12 +11190,12 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>桥侧接收核对 12-bit</t>
+          <t>上行出口 12-bit (2 期加 1.2G)</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -11205,7 +11209,7 @@
         </is>
       </c>
       <c r="H79" s="12" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I79" s="4" t="inlineStr"/>
     </row>
@@ -11227,12 +11231,12 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit</t>
+          <t>桥侧接收核对 12-bit</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -11268,12 +11272,12 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>主控↔桥联合仿真</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -11287,7 +11291,7 @@
         </is>
       </c>
       <c r="H81" s="12" t="n">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="I81" s="4" t="inlineStr"/>
     </row>
@@ -11304,33 +11308,33 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>1 期 4,296 片/s 桥链路余量仅 0.40%</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="8" t="inlineStr">
-        <is>
-          <t>监控</t>
+          <t>主控↔桥联合仿真</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>V1准备 · 必须</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H82" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I82" s="4" t="inlineStr">
-        <is>
-          <t>退路降到 22 Hz（用户定保持 24 Hz）</t>
-        </is>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="I82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -11350,18 +11354,18 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2260 从未收到合法 ACK（疑物理通路）</t>
+          <t>1 期 4,296 片/s 桥链路余量仅 0.40%</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>监控</t>
         </is>
       </c>
       <c r="H83" s="12" t="n">
@@ -11369,7 +11373,7 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>验证板一颗一组针对此问题，回板验证</t>
+          <t>退路降到 22 Hz（用户定保持 24 Hz）</t>
         </is>
       </c>
     </row>
@@ -11381,38 +11385,38 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 主控位流</t>
+          <t>V1 2260 · 上行/桥</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>风险</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>1 期主控整合位流</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>V1准备 · 必须</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>2260 从未收到合法 ACK（疑物理通路）</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H84" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I84" s="4" t="inlineStr"/>
+        <v>46308</v>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>验证板一颗一组针对此问题，回板验证</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -11432,12 +11436,12 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>V1-B1</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>V1 主控/桥位流按投板版出齐 (单面 io25 / PRBS / 面 B 桥)</t>
+          <t>1 期主控整合位流</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -11451,7 +11455,7 @@
         </is>
       </c>
       <c r="H85" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I85" s="4" t="inlineStr"/>
     </row>
@@ -11463,7 +11467,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 双面</t>
+          <t>V1 2260 · 主控位流</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -11473,12 +11477,12 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>V1-B1</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>核实 V1 能否双面 (W6 光电冲突)</t>
+          <t>V1 主控/桥位流按投板版出齐 (单面 io25 / PRBS / 面 B 桥)</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -11514,12 +11518,12 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>D38</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>V1 面 B 软件就绪 (IO 电压开关/面B RTL/桥B/JTAG 两器件/--faces AB)</t>
+          <t>核实 V1 能否双面 (W6 光电冲突)</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -11555,17 +11559,17 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>D40</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>双面主控位流编译通过 (TD hold 修复崩溃)</t>
+          <t>V1 面 B 软件就绪 (IO 电压开关/面B RTL/桥B/JTAG 两器件/--faces AB)</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 可选</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
@@ -11574,7 +11578,7 @@
         </is>
       </c>
       <c r="H88" s="12" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I88" s="4" t="inlineStr"/>
     </row>
@@ -11586,7 +11590,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 全链路/板端后端</t>
+          <t>V1 2260 · 双面</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -11596,17 +11600,17 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D40</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>全链路系统仿真 (主机→2260 模型)</t>
+          <t>双面主控位流编译通过 (TD hold 修复崩溃)</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
+          <t>V1准备 · 可选</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
@@ -11615,7 +11619,7 @@
         </is>
       </c>
       <c r="H89" s="12" t="n">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="I89" s="4" t="inlineStr"/>
     </row>
@@ -11637,12 +11641,12 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>V1 真内容板端通路 (voxslice 加 2260 后端)</t>
+          <t>全链路系统仿真 (主机→2260 模型)</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -11668,7 +11672,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>V1 2260 · 投板对齐/回板</t>
+          <t>V1 2260 · 全链路/板端后端</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -11678,12 +11682,12 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>V1 回板当天一键 bring-up 脚本</t>
+          <t>V1 真内容板端通路 (voxslice 加 2260 后端)</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -11719,12 +11723,12 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>软件引脚/硬件假设对齐 10-15/16 投板版</t>
+          <t>V1 回板当天一键 bring-up 脚本</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -11738,7 +11742,7 @@
         </is>
       </c>
       <c r="H92" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I92" s="4" t="inlineStr"/>
     </row>
@@ -11760,12 +11764,12 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>主控 IO 1.8V 可行性 (用户定最终 2.5V)</t>
+          <t>软件引脚/硬件假设对齐 10-15/16 投板版</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -11796,33 +11800,33 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>灯板 SDO→SDI 0Ω 在 09-18 图上悬空</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+          <t>主控 IO 1.8V 可行性 (用户定最终 2.5V)</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>V1准备 · 必须</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H94" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>硬件确认并补 0Ω</t>
-        </is>
-      </c>
+        <v>46314</v>
+      </c>
+      <c r="I94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -11842,12 +11846,12 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>1 期面板映射缺 4 项信息</t>
+          <t>灯板 SDO→SDI 0Ω 在 09-18 图上悬空</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr"/>
@@ -11861,7 +11865,7 @@
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>问硬件同事</t>
+          <t>硬件确认并补 0Ω</t>
         </is>
       </c>
     </row>
@@ -11873,38 +11877,36 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · T2 板/1.2G 上行</t>
+          <t>V1 2260 · 投板对齐/回板</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>风险</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>V2-1</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>T2 自研 SoC 板 (32 bit DDR + PL 读带宽)</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>V2 · 必须</t>
-        </is>
-      </c>
-      <c r="G96" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H96" s="12" t="n"/>
+          <t>1 期面板映射缺 4 项信息</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>46308</v>
+      </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>等硬件线 T2 自研板 (32 bit DDR) 投板/回板</t>
+          <t>问硬件同事</t>
         </is>
       </c>
     </row>
@@ -11926,12 +11928,12 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>V2-2</t>
+          <t>V2-1</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>2 期上行 1.2G 实测</t>
+          <t>T2 自研 SoC 板 (32 bit DDR + PL 读带宽)</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -11947,7 +11949,7 @@
       <c r="H97" s="12" t="n"/>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>等 V1 回板 PRBS 实测, 定 1.2G 还是退 1.0G (R1)</t>
+          <t>等硬件线 T2 自研板 (32 bit DDR) 投板/回板</t>
         </is>
       </c>
     </row>
@@ -11969,12 +11971,12 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>D46</t>
+          <t>V2-2</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>V2 桥补齐 面 B + 1.2G PRBS 误码档 (comm_check --phase v2)</t>
+          <t>2 期上行 1.2G 实测</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -11982,17 +11984,15 @@
           <t>V2 · 必须</t>
         </is>
       </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H98" s="12" t="n">
-        <v>46315</v>
-      </c>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H98" s="12" t="n"/>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>V2 桥板引脚 + V2 主控 PRBS 位流</t>
+          <t>等 V1 回板 PRBS 实测, 定 1.2G 还是退 1.0G (R1)</t>
         </is>
       </c>
     </row>
@@ -12009,31 +12009,35 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>D46</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>1.2G 可能过不了</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr"/>
-      <c r="G99" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+          <t>V2 桥补齐 面 B + 1.2G PRBS 误码档 (comm_check --phase v2)</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 必须</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H99" s="12" t="n">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
+          <t>V2 桥板引脚 + V2 主控 PRBS 位流</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12049,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 主控位流</t>
+          <t>V2 192×216 · T2 板/1.2G 上行</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -12055,12 +12059,12 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D52</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>V2 主控位流跟上主线 (p2_ul1200_b12_v3)</t>
+          <t>V2 主控 1.2G PRBS 误码位流 (到板 C3 可用)</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -12074,9 +12078,13 @@
         </is>
       </c>
       <c r="H100" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I100" s="4" t="inlineStr"/>
+        <v>46315</v>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>D53 合后重编; 面 B 无 PRBS</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -12086,38 +12094,38 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 主控位流</t>
+          <t>V2 192×216 · T2 板/1.2G 上行</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>风险</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>D44</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>V2 双面主控位流 (片上 RAM/时序评估)</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>V2 · 必须</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>1.2G 可能过不了</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr"/>
+      <c r="G101" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
         </is>
       </c>
       <c r="H101" s="12" t="n">
-        <v>46315</v>
-      </c>
-      <c r="I101" s="4" t="inlineStr"/>
+        <v>46308</v>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -12127,7 +12135,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 面板映射/后端</t>
+          <t>V2 192×216 · 主控位流</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -12137,12 +12145,12 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>V2-3</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>2 期 192×216 面板映射</t>
+          <t>V2 主控位流跟上主线 (p2_ul1200_b12_v3)</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -12156,7 +12164,7 @@
         </is>
       </c>
       <c r="H102" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I102" s="4" t="inlineStr"/>
     </row>
@@ -12168,7 +12176,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 面板映射/后端</t>
+          <t>V2 192×216 · 主控位流</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
@@ -12178,12 +12186,12 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>V2-7</t>
+          <t>D44</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>板端 voxslice --disp p2 (2 期后端)</t>
+          <t>V2 双面主控位流 (片上 RAM/时序评估)</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -12197,7 +12205,7 @@
         </is>
       </c>
       <c r="H103" s="12" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I103" s="4" t="inlineStr"/>
     </row>
@@ -12219,12 +12227,12 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>D48</t>
+          <t>V2-3</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>V2 双面全链路系统仿真 (PC→主控→桥→2260 模型)</t>
+          <t>2 期 192×216 面板映射</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -12238,7 +12246,7 @@
         </is>
       </c>
       <c r="H104" s="12" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I104" s="4" t="inlineStr"/>
     </row>
@@ -12250,7 +12258,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>V2 192×216 · 整机</t>
+          <t>V2 192×216 · 面板映射/后端</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -12260,12 +12268,12 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>V2-4</t>
+          <t>V2-7</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>2 期 30 Hz 整机上转子</t>
+          <t>板端 voxslice --disp p2 (2 期后端)</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -12273,17 +12281,15 @@
           <t>V2 · 必须</t>
         </is>
       </c>
-      <c r="G105" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H105" s="12" t="n"/>
-      <c r="I105" s="4" t="inlineStr">
-        <is>
-          <t>等 T2 板 (V2-1) + 1.2G 上行 (V2-2)</t>
-        </is>
-      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>46314</v>
+      </c>
+      <c r="I105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -12293,38 +12299,38 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>画面指标 (各期)</t>
+          <t>V2 192×216 · 面板映射/后端</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>KR1.6</t>
+          <t>D48</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>内容刷新率 (实转上屏) (最新 10.8 fps)</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr"/>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1⬜ V2⬜</t>
+          <t>V2 双面全链路系统仿真 (PC→主控→桥→2260 模型)</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 必须</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H106" s="12" t="n">
-        <v>46307</v>
-      </c>
-      <c r="I106" s="4" t="inlineStr">
-        <is>
-          <t>等 V1 整机 720 RPM 实转 (验证板 11-10 回板)</t>
-        </is>
-      </c>
+        <v>46315</v>
+      </c>
+      <c r="I106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -12334,36 +12340,38 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>画面指标 (各期)</t>
+          <t>V2 192×216 · 整机</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>KR2.1</t>
+          <t>V2-4</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>体帧率 (最新 21.7 Hz)</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr"/>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1🔵 V2⬜</t>
-        </is>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>46307</v>
-      </c>
+          <t>2 期 30 Hz 整机上转子</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 必须</t>
+        </is>
+      </c>
+      <c r="G107" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="n"/>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>等 V1 回板实转 720 RPM×358 片</t>
+          <t>等 T2 板 (V2-1) + 1.2G 上行 (V2-2)</t>
         </is>
       </c>
     </row>
@@ -12385,18 +12393,18 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>KR3.1</t>
+          <t>KR1.6</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>每面像素数 (最新 28800 px)</t>
+          <t>内容刷新率 (实转上屏) (最新 10.8 fps)</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr"/>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1✅ V2⬜</t>
+          <t>V0✅ V1⬜ V2⬜</t>
         </is>
       </c>
       <c r="H108" s="12" t="n">
@@ -12404,7 +12412,7 @@
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>等 2 期 192×216 屏</t>
+          <t>等 V1 整机 720 RPM 实转 (验证板 11-10 回板)</t>
         </is>
       </c>
     </row>
@@ -12426,12 +12434,12 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>KR3.2</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>每圈片数 (最新 142 片)</t>
+          <t>体帧率 (最新 21.7 Hz)</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr"/>
@@ -12445,7 +12453,7 @@
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>等 V1 回板实测</t>
+          <t>等 V1 回板实转 720 RPM×358 片</t>
         </is>
       </c>
     </row>
@@ -12467,18 +12475,18 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>KR4.1</t>
+          <t>KR3.1</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>色深 (最新 3 bit/通道)</t>
+          <t>每面像素数 (最新 28800 px)</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>V0✅ V1🔵 V2🔵</t>
+          <t>V0✅ V1✅ V2⬜</t>
         </is>
       </c>
       <c r="H110" s="12" t="n">
@@ -12486,91 +12494,91 @@
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>等 V1 2260 回板上屏</t>
+          <t>等 2 期 192×216 屏</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>④ 运维保障</t>
+          <t>③ 显示 (按期换后端)</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>开机即用</t>
+          <t>画面指标 (各期)</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>KR3.2</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>开机自动演示 + 转速门控</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G111" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>每圈片数 (最新 142 片)</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr"/>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1🔵 V2⬜</t>
         </is>
       </c>
       <c r="H111" s="12" t="n">
         <v>46307</v>
       </c>
-      <c r="I111" s="4" t="inlineStr"/>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>等 V1 回板实测</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>④ 运维保障</t>
+          <t>③ 显示 (按期换后端)</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>开机即用</t>
+          <t>画面指标 (各期)</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>KR4.1</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>启动提速 + 启动屏显 (含原 backlog B1)</t>
-        </is>
-      </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>色深 (最新 3 bit/通道)</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1🔵 V2🔵</t>
         </is>
       </c>
       <c r="H112" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I112" s="4" t="inlineStr"/>
+        <v>46307</v>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>等 V1 2260 回板上屏</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12590,12 +12598,12 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>开机默认动画 = 立方体动图 (用户 10-16 提)</t>
+          <t>开机自动演示 + 转速门控</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
@@ -12609,7 +12617,7 @@
         </is>
       </c>
       <c r="H113" s="12" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="I113" s="4" t="inlineStr"/>
     </row>
@@ -12631,17 +12639,17 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>D47</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>系统从 QSPI 加载 (去 TF/eMMC 准备; 03 板试)</t>
+          <t>启动提速 + 启动屏显 (含原 backlog B1)</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>V2 · 加分</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
@@ -12650,13 +12658,9 @@
         </is>
       </c>
       <c r="H114" s="12" t="n">
-        <v>46315</v>
-      </c>
-      <c r="I114" s="4" t="inlineStr">
-        <is>
-          <t>T2 板 QSPI 选 64MiB / 厂商驱动提速</t>
-        </is>
-      </c>
+        <v>46309</v>
+      </c>
+      <c r="I114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -12671,27 +12675,31 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>KR8.1</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>上电到 0° 片亮起 (停转) (最新 12.4 s)</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr"/>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>开机默认动画 = 立方体动图 (用户 10-16 提)</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 必须</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H115" s="12" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="I115" s="4" t="inlineStr"/>
     </row>
@@ -12708,29 +12716,37 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>KR8.4</t>
+          <t>D47</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>上电到转稳全亮 (最新 26 s)</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr"/>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>V0— V1— V2—</t>
+          <t>系统从 QSPI 加载 (去 TF/eMMC 准备; 03 板试)</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>V2 · 加分</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H116" s="12" t="n">
-        <v>46307</v>
-      </c>
-      <c r="I116" s="4" t="inlineStr"/>
+        <v>46315</v>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>T2 板 QSPI 选 64MiB / 厂商驱动提速</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -12740,36 +12756,32 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>联网/找板/自愈</t>
+          <t>开机即用</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>KR8.1</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>开机自连 WiFi</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G117" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>上电到 0° 片亮起 (停转) (最新 12.4 s)</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr"/>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H117" s="12" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="I117" s="4" t="inlineStr"/>
     </row>
@@ -12781,36 +12793,32 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>联网/找板/自愈</t>
+          <t>开机即用</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>KR8.4</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS)</t>
-        </is>
-      </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>V0 · 必须</t>
-        </is>
-      </c>
-      <c r="G118" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>上电到转稳全亮 (最新 26 s)</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>V0— V1— V2—</t>
         </is>
       </c>
       <c r="H118" s="12" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="I118" s="4" t="inlineStr"/>
     </row>
@@ -12832,12 +12840,12 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 (服务监护/看门狗/兜底热点/povnetd 1.2)</t>
+          <t>开机自连 WiFi</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -12851,7 +12859,7 @@
         </is>
       </c>
       <c r="H119" s="12" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="I119" s="4" t="inlineStr"/>
     </row>
@@ -12873,12 +12881,12 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复 ≤30 s (03 长跑断 155 s)</t>
+          <t>按名字找板 (mDNS)</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -12892,7 +12900,7 @@
         </is>
       </c>
       <c r="H120" s="12" t="n">
-        <v>46314</v>
+        <v>46308</v>
       </c>
       <c r="I120" s="4" t="inlineStr"/>
     </row>
@@ -12914,12 +12922,12 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>D43</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>povnetd 1.3 网络自愈回归修复</t>
+          <t>不插串口永远连得上 (服务监护/看门狗/兜底热点/povnetd 1.2)</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -12933,7 +12941,7 @@
         </is>
       </c>
       <c r="H121" s="12" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="I121" s="4" t="inlineStr"/>
     </row>
@@ -12950,27 +12958,31 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>KR8.2</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>按名字找到板子 (最新 19.8 s)</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr"/>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>WiFi 断线恢复 ≤30 s (03 长跑断 155 s)</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 必须</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H122" s="12" t="n">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="I122" s="4" t="inlineStr"/>
     </row>
@@ -12982,7 +12994,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>远程运维/升级 (含 JTAG 灌桥)</t>
+          <t>联网/找板/自愈</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
@@ -12992,12 +13004,12 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D43</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>转子运维 (netguard-lite / 遥测 / 远程升级)</t>
+          <t>povnetd 1.3 网络自愈回归修复</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
@@ -13011,7 +13023,7 @@
         </is>
       </c>
       <c r="H123" s="12" t="n">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="I123" s="4" t="inlineStr"/>
     </row>
@@ -13023,36 +13035,32 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>远程运维/升级 (含 JTAG 灌桥)</t>
+          <t>联网/找板/自愈</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>KR8.2</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>主控经 JTAG 给桥灌位流 (V1 远程升级软件)</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>V1准备 · 必须</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>按名字找到板子 (最新 19.8 s)</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H124" s="12" t="n">
-        <v>46314</v>
+        <v>46309</v>
       </c>
       <c r="I124" s="4" t="inlineStr"/>
     </row>
@@ -13074,17 +13082,17 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>D42</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>03 板软件跟进主线</t>
+          <t>转子运维 (netguard-lite / 遥测 / 远程升级)</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>V0 · 加分</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
@@ -13093,7 +13101,7 @@
         </is>
       </c>
       <c r="H125" s="12" t="n">
-        <v>46314</v>
+        <v>46309</v>
       </c>
       <c r="I125" s="4" t="inlineStr"/>
     </row>
@@ -13110,27 +13118,31 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>KR8.3</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>需要串口 (1=需要) (最新 0 是/否)</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr"/>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>主控经 JTAG 给桥灌位流 (V1 远程升级软件)</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>V1准备 · 必须</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H126" s="12" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="I126" s="4" t="inlineStr"/>
     </row>
@@ -13147,27 +13159,31 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>D42</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用) (最新 1 是/否)</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr"/>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>03 板软件跟进主线</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H127" s="12" t="n">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="I127" s="4" t="inlineStr"/>
     </row>
@@ -13189,12 +13205,12 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>KR9.2</t>
+          <t>KR8.3</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>远程升级失败自动回滚 (1=有) (最新 1 是/否)</t>
+          <t>需要串口 (1=需要) (最新 0 是/否)</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr"/>
@@ -13204,7 +13220,7 @@
         </is>
       </c>
       <c r="H128" s="12" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="I128" s="4" t="inlineStr"/>
     </row>
@@ -13216,40 +13232,34 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>主控↔桥通信</t>
+          <t>远程运维/升级 (含 JTAG 灌桥)</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>KR9.1</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>C1 台架彩排 + 1.2G 误码测试</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>V1准备 · 加分</t>
-        </is>
-      </c>
-      <c r="G129" s="14" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="H129" s="12" t="n"/>
-      <c r="I129" s="4" t="inlineStr">
-        <is>
-          <t>不做 (用户 10-19 定), 由 D39 到板 comm_check 代替</t>
-        </is>
-      </c>
+          <t>转子遥测可用 (1=可用) (最新 1 是/否)</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr"/>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -13259,36 +13269,32 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>主控↔桥通信</t>
+          <t>远程运维/升级 (含 JTAG 灌桥)</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>KR9.2</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信全功能 (配置/状态/错误恢复/升级)</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>V1准备 · 必须</t>
-        </is>
-      </c>
-      <c r="G130" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>远程升级失败自动回滚 (1=有) (最新 1 是/否)</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr"/>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H130" s="12" t="n">
-        <v>46312</v>
+        <v>46309</v>
       </c>
       <c r="I130" s="4" t="inlineStr"/>
     </row>
@@ -13310,28 +13316,30 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 + PRBS 位流</t>
+          <t>C1 台架彩排 + 1.2G 误码测试</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>V1准备 · 必须</t>
-        </is>
-      </c>
-      <c r="G131" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H131" s="12" t="n">
-        <v>46314</v>
-      </c>
-      <c r="I131" s="4" t="inlineStr"/>
+          <t>V1准备 · 加分</t>
+        </is>
+      </c>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="n"/>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>不做 (用户 10-19 定), 由 D39 到板 comm_check 代替</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -13341,7 +13349,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>可靠性验证 (冷启动/长跑)</t>
+          <t>主控↔桥通信</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -13351,17 +13359,17 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>V0A</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>V0 重启验收 (不插串口: 找回/守护/开机默认/WiFi/推流/稳定 6 项)</t>
+          <t>SoC↔桥通信全功能 (配置/状态/错误恢复/升级)</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>V0 · 必须</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
@@ -13370,7 +13378,7 @@
         </is>
       </c>
       <c r="H132" s="12" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="I132" s="4" t="inlineStr"/>
     </row>
@@ -13382,7 +13390,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>可靠性验证 (冷启动/长跑)</t>
+          <t>主控↔桥通信</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
@@ -13392,17 +13400,17 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>冷启动认不到 TF 卡 (03 停在 u-boot)</t>
+          <t>SoC↔桥通信专项验证包 + PRBS 位流</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>V0 · 必须</t>
+          <t>V1准备 · 必须</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
@@ -13433,17 +13441,17 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>D49</t>
+          <t>V0A</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+          <t>V0 重启验收 (不插串口: 找回/守护/开机默认/WiFi/推流/稳定 6 项)</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>V0 · 加分</t>
+          <t>V0 · 必须</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
@@ -13452,7 +13460,7 @@
         </is>
       </c>
       <c r="H134" s="12" t="n">
-        <v>46315</v>
+        <v>46311</v>
       </c>
       <c r="I134" s="4" t="inlineStr"/>
     </row>
@@ -13469,27 +13477,31 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr"/>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>冷启动认不到 TF 卡 (03 停在 u-boot)</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 必须</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H135" s="12" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I135" s="4" t="inlineStr"/>
     </row>
@@ -13506,27 +13518,31 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>D49</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr"/>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>V0✅ V1✅ V2✅</t>
+          <t>进度看板按大功能重排 (①传递 ②处理 ③显示 ④运维)</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>V0 · 加分</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H136" s="12" t="n">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="I136" s="4" t="inlineStr"/>
     </row>
@@ -13543,33 +13559,29 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
+          <t>连续无故障: 软件链路 (假转, 无人值守) (最新 24 h)</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr"/>
-      <c r="G137" s="13" t="inlineStr">
-        <is>
-          <t>开</t>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
         </is>
       </c>
       <c r="H137" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I137" s="4" t="inlineStr">
-        <is>
-          <t>T2 板留 eMMC、打胶</t>
-        </is>
-      </c>
+        <v>46312</v>
+      </c>
+      <c r="I137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -13579,34 +13591,112 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
+          <t>可靠性验证 (冷启动/长跑)</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>KR7.3</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>连续无故障: 整机实转 (有人值守) (最新 1 h)</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr"/>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>V0✅ V1✅ V2✅</t>
+        </is>
+      </c>
+      <c r="H138" s="12" t="n">
+        <v>46310</v>
+      </c>
+      <c r="I138" s="4" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>④ 运维保障</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>可靠性验证 (冷启动/长跑)</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>风险</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr"/>
+      <c r="G139" s="13" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>T2 板留 eMMC、打胶</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>④ 运维保障</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
           <t>开发环境</t>
         </is>
       </c>
-      <c r="C138" s="5" t="inlineStr">
+      <c r="C140" s="5" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="D138" s="5" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
+      <c r="E140" s="4" t="inlineStr">
         <is>
           <t>D 盘 EIO（IP-guard 驱动）</t>
         </is>
       </c>
-      <c r="F138" s="4" t="inlineStr"/>
-      <c r="G138" s="8" t="inlineStr">
+      <c r="F140" s="4" t="inlineStr"/>
+      <c r="G140" s="8" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
       </c>
-      <c r="H138" s="12" t="n">
+      <c r="H140" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="I138" s="4" t="inlineStr">
+      <c r="I140" s="4" t="inlineStr">
         <is>
           <t>看门狗自动重挂 + 构建放 WSL 本地盘</t>
         </is>
@@ -13626,7 +13716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J213"/>
+  <dimension ref="A1:J215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13701,12 +13791,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>49/49</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>KR 25/25 + 交付 23/23 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
+          <t>KR 25/25 + 交付 24/24 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
         </is>
       </c>
       <c r="G4" s="17" t="n">
@@ -13729,16 +13819,16 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.9154929577464789</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>64/70</t>
+          <t>65/71</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>KR 18/24 + 交付 46/46 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
+          <t>KR 18/24 + 交付 47/47 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
         </is>
       </c>
       <c r="G5" s="17" t="n">
@@ -13761,16 +13851,16 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>0.8734177215189873</v>
+        <v>0.8765432098765432</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>69/79</t>
+          <t>71/81</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>KR 17/24 + 交付 52/55 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 17/24 + 交付 54/57 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="17" t="n">
@@ -13904,10 +13994,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>0.9143</v>
+        <v>0.9155</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>0.8734</v>
+        <v>0.8764999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -15034,51 +15124,51 @@
     </row>
     <row r="60">
       <c r="A60" s="12" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46315</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>D22b</t>
+          <t>D51</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
+          <t>去 600 rpm 帧率台阶: 20 fps 上限是配置非硬件; voxslice 1.2 小数节拍 + max-fps 45; 02 板 634 rpm 9.3→18.6 fps, 1200 rpm 15.1→29.8; 主会话复跑 8/0</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d22_reach/README.md</t>
+          <t>dr1v90</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+        <v>46315</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>D32</t>
+          <t>D52</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
+          <t>V2 主控 1.2G PRBS 位流 (面 A) 0 违例 (过约束 0.1 ns), 端到端仿真 13 lane 0 误码, comm_check v2 演练 86/0; 主会话复跑 13/0</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>dr1v90</t>
+          <t>dr1v90 7affa17</t>
         </is>
       </c>
     </row>
@@ -15093,17 +15183,17 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>D32</t>
+          <t>D22b</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
+          <t>WiFi 断线恢复提速合主线 80aaeaa (复验 d22 12/0, povnetd 自测 22/0): povnetd 1.3 软踢 8/16 s + 硬重连 25 s + 清 ARP/GARP; 03 实测 l2off 68→16 s, gwarp 75→16 s; voxlive 遇 EHOSTUNREACH 刷 ARP; 02 用 install.sh 装上, 02/03 重启后 povnetd 1.3 在跑; AP 本身消失时板子无解</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/acc32_*.log</t>
+          <t>dr1v90 d22_reach/README.md</t>
         </is>
       </c>
     </row>
@@ -15111,24 +15201,24 @@
       <c r="A63" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B63" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
+          <t>开机后约 46 s 推流只收 941 帧/90 s (满速 1350): 连上后前约 9 s 发 0 帧再超时重连, CPU 空闲; 怀疑开机画面 (--first/--start-idle/bootscr --hold 60) 阶段不消费推流; 02 两次验收 A5 FAIL (1243/1241) 同因 → 开 D32</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90</t>
         </is>
       </c>
     </row>
@@ -15136,24 +15226,24 @@
       <c r="A64" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>补录</t>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>KR4.2</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
+          <t>开机画面期间推流立即接上合主线 8bff92e: 根因 bootscr 本机连 voxslice:9500 占到 --hold 60 释放, serve 一次一个客户端; 改为外来客户端接入即断 bootscr; 02/03 卡上 voxslice → 4ac8a7f0 (旧 .bak-d32), 重启验收两块都 6/6, 开机后约 1 min 推流 1351 帧/90 s</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>progress/v0_accept/acc32_*.log</t>
         </is>
       </c>
     </row>
@@ -15161,19 +15251,19 @@
       <c r="A65" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>用户</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
+          <t>用户拍板: 批准 D29 (03 uboot.env 已换, 旧版 .bak-d29, 热重启 OK, 等冷上电 20 次); V1 回板用 D27 套; B1 V1 改奇数档 357/285/209; B2 24 Hz 用满档 (357 档上沿 ≥12 rps, 桥余量约 0.7%, 回板实测); B3 V2 档表 605/513/461 → 开 D34; 并开 D33 主控灌桥位流 / V2-7 板端 2 期后端 / V0 差距盘点</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -15188,22 +15278,22 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>补录</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
+          <t>[V0差距] KR4.2 补录 2047 板上 12-bit(32 bit 像素) WiFi→PL 通路实测 (D15b 3a41eb7); V0 达成率 95.7%→97.8%, 仅剩 D29 冷上电 20 次</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 card03</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -15213,22 +15303,22 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
+          <t>用户确认: SoC 底板 10-15 与桥转接板 10-16 都已投板 (11-10 回板即此版), 不能改图; 软件此前依据 10-12 版 → 开 D36 按新版网表全面对齐, 需硬件改动一律写回板后改板清单; D35 (W6/面 B) 同口径; 新版文件集中在 hw_latest_1016/</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2b111f0</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15238,22 +15328,22 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
+          <t>03 软重启 20/20 进内核+回网 (串口录制换自动重连 cap2.ps1, 旧录制掉电后句柄失效 0 字节); 冷上电改由 USB 继电器 (LCUS-1, 常闭串 24V+) 自动做, 用户已同意采购, 到货后验 20 次</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
+          <t>dr1v90 card03</t>
         </is>
       </c>
     </row>
@@ -15261,24 +15351,24 @@
       <c r="A69" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
+          <t>V1 可装 A/B 两面 (W6=面B TXP7 非光电, 光电 CN3-R82-U12); 位流待改 spin_sync→U12、删 bank11 2047 屏脚; 主会话独立机读网表复核一致</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 2b111f0</t>
         </is>
       </c>
     </row>
@@ -15298,12 +15388,12 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
+          <t>投板版网表对齐: 唯一引脚变化 UL_CHK→R7/T7, 光电 W6→U12, CN3/CN6 101-n 正确 (B3 作废); 改约束已入 task/d36-hwsync 42eca66; 位流重出待用户放行; 回板当天改板清单 PDF 出</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 97a10cf</t>
+          <t>docs progress/回板当天改板清单_2026-10-19.pdf</t>
         </is>
       </c>
     </row>
@@ -15311,24 +15401,24 @@
       <c r="A71" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
+          <t>用户定: V1 主控 bank33 走 1.8V (LVDS18), 桥板方案 A (U18/U19 VCCA 改 1.8V LDO, R236 NC); 底板 100Ω 空贴已确认; R82 改 5.6k; 桥 R235/R223 推荐 2.2k; 改板清单 PDF 已更新</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 7253608</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15336,24 +15426,24 @@
       <c r="A72" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B72" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
+          <t>桥位流四套按投板版重出 (用户放行): e60c 7f612855 / e60p8c d93495b3 / e60 4c74afd7 / e60p8 7bd1967e, 0 违例; task/d36-hwsync 97a10cf 复验中</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>dr1v90 97a10cf</t>
         </is>
       </c>
     </row>
@@ -15368,17 +15458,17 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D34</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
+          <t>V1 357/285/209 奇数档 + 24 Hz 满档; 复验 d25/d23/v1_bringup/d9 全过</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 23474c7</t>
+          <t>dr1v90 7253608</t>
         </is>
       </c>
     </row>
@@ -15386,24 +15476,24 @@
       <c r="A74" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B74" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
+          <t>用户改回: V1 主控 bank33 走 2.5V (H7/H9 专供 J1/J2), 桥板不改; R82 改 2.2k; 1.8V 方案不采用 (备查 d37_io18)</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 f2584d9</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -15418,17 +15508,17 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>D38</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
+          <t>主控 JTAG 灌桥 (bringup --bridge-load sram, 盲灌+JT01-06 判据); 复验 53/0, v1_bringup 96/0</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ad201f9</t>
+          <t>dr1v90 23474c7</t>
         </is>
       </c>
     </row>
@@ -15438,22 +15528,22 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>V1主控</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
+          <t>软件对齐投板版; 桥位流四套重出 0 违例</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>本机构建</t>
+          <t>dr1v90 f2584d9</t>
         </is>
       </c>
     </row>
@@ -15463,22 +15553,22 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
+          <t>V1 面 B 软件就绪 (IO 电压开关/面 B RTL/桥 B/JTAG 两器件链/--faces AB); 面 B 桥 e60cb f919ea30; 双面主控首建 TD 崩溃 (资源 74%, 拥塞), 重跑中</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d39-comm b69f6d8</t>
+          <t>dr1v90 ad201f9</t>
         </is>
       </c>
     </row>
@@ -15488,22 +15578,22 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>V2-7</t>
+          <t>V1主控</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
+          <t>V1 单面主控位流 io25 2b4f3311 (光电 U12, 时序过), io18 备用 6493e837; _work/v1_main_1019</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ff1846a</t>
+          <t>本机构建</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15603,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -15523,12 +15613,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
+          <t>SoC↔桥通信专项验证包 comm_check.sh (不接屏, 自动判 PRBS/边带/寄存器/JTAG/恢复, 13 电平测点); 离线 88/0; 与 D38 冲突由 D39b 合并并出 PRBS 位流; 到板页 progress/到板当天_通信验证.pdf</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3ef6b06</t>
+          <t>dr1v90 task/d39-comm b69f6d8</t>
         </is>
       </c>
     </row>
@@ -15538,22 +15628,22 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>V2-7</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
+          <t>板端 voxslice_p2 驱动 2 期主控 (--disp p2), 端到端逐像素 0 错, V0/V1 行为不变; regress 27/0</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>progress/d29_coldboot</t>
+          <t>dr1v90 ff1846a</t>
         </is>
       </c>
     </row>
@@ -15561,24 +15651,24 @@
       <c r="A81" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B81" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>D11;D39</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
+          <t>通信验证包进主线 + PRBS 位流 (桥 e60cp 6d5b3db3 / 主控 sb_prbs_io25 e7c33e78, 0 违例); 到板即可 comm_check.sh --board &lt;名&gt; --bridge-load sram; 复验 85/0 110/0 76/0</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>用户 10-19</t>
+          <t>dr1v90 3ef6b06</t>
         </is>
       </c>
     </row>
@@ -15588,22 +15678,22 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>合并</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
+          <t>03 手动冷上电 20/20: 每次 U-Boot→读 env OK→boot.scr→进内核→login, 0 次停在 =&gt;, env 读失败 0 (u-boot 早期 -110 探测行仍有, 不影响); 加软重启 20/20, D29 关闭; USB 继电器不再需要</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6333eb5</t>
+          <t>progress/d29_coldboot</t>
         </is>
       </c>
     </row>
@@ -15611,99 +15701,99 @@
       <c r="A83" s="12" t="n">
         <v>46314</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>合并</t>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>D42;D43</t>
+          <t>D11;D39</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
+          <t>用户定 D11 杜邦线 240M 台架不做, 由 D39 到板通信验证代替 (SoC 底板+桥转接板本周到, 真 FPC 800M); D11 改加分项</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 8689db2 / 6e6d47b</t>
+          <t>用户 10-19</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>合并</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D41</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
+          <t>锁相提前量自适应默认改 rate: 正常网络 583/900 rpm 延迟 p50 111/91→69/71 ms, p99 217/200→121/148, D20 6/6 持平; 网络差时段仍不达标 (PC 与板两跳 WiFi); 待拍板 lead 60 / 在途上限 / PC 有线 / 板端最新优先</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1017_03_24h</t>
+          <t>dr1v90 6333eb5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46314</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>合并</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D42;D43</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
+          <t>03 跟进主线 voxslice 64e48c8a; povnetd 1.3 回归 (网关探测阻塞 + SYN 重传误清计数, 10-14 型故障自愈 +17 s) 修为 1.3.1 并部署 03; 主会话复验 19/0 22/0</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/SPEC.md</t>
+          <t>dr1v90 8689db2 / 6e6d47b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>进展</t>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>V2-5</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
+          <t>03 24 h 产品配置长跑 9/10 (主线 3bf094f, voxslice 63e7afea): 停摆 0/死 0, 完成率最低 100%, RSS 23.1 MB 不涨, 30/31 段推流正常; S5 FAIL = 03:00 WiFi 断 (gw 不回 ICMP, povnetd 60 s 后才重连, 两轮 wpa+dhcp, 155 s 恢复; PC 侧 No route to host 约 5 min), 第 6 段推流时长用完仍在重连 rc 2 → 开 D22b 把恢复压到 ≤30 s</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_fmt/README.md</t>
+          <t>progress/soak_v0/1017_03_24h</t>
         </is>
       </c>
     </row>
@@ -15711,24 +15801,24 @@
       <c r="A87" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>D28b</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
+          <t>SoC↔桥边带全功能合主线 (复验含回归全过): 握手/闭环训练+自动重训/桥计数经 B2S 回传 povstat/S2B 桥寄存器读写/2260 表改写 ACK 回读/亮度黑场/看门狗 (修黑场死锁)/停转降亮/版本核对; 综合: 桥 e60c 167.33 MHz 0 违例 (余量 0.40%), 主控 UL_SB SWNS +0.002; 🔴 回板阻塞 SB_RSTN 被 R235 10k 下拉, 现役主控位流不驱动 → 用 D27 主控位流或 FPC63 临时上拉; 待定 H-1~H-4</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/回板当天.md</t>
+          <t>dr1v90 d27_link/SPEC.md</t>
         </is>
       </c>
     </row>
@@ -15736,24 +15826,24 @@
       <c r="A88" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>进展</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>D27b</t>
+          <t>V2-5</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
+          <t>2 期主控字槽序格式器合主线 fb9e6eb (复验含回归全过): ul_fmt_p2 4 列乒乓 + LUT 重排, 真内容 40/12/60 片与 v2_ref 逐组 0 错, 反例全检出; SWNS +0.001 (hclk 真余量约 +0.30); POV_UL_GEOM=p2 改字槽序, 原列序档改名 p2c; 待: 桥 24 链 UL12 解包, 板端 --disp p2</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d27_link/README.md</t>
+          <t>dr1v90 v2_fmt/README.md</t>
         </is>
       </c>
     </row>
@@ -15768,17 +15858,17 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>V2-6</t>
+          <t>D28b</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
+          <t>回板脚本接 D27 合主线 (复验 78/0): 现役套 (023e6582+e60) 必须 FPC63 临时上拉 (脚本问答把关), D27 套 (主控 _sb.bin + 桥 e60c) 闭环训练; D27 套位流本体尚未出 → 开 D27b 出件</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 gw5a_bridge/p2/README.md</t>
+          <t>dr1v90 v1_bringup/回板当天.md</t>
         </is>
       </c>
     </row>
@@ -15786,24 +15876,24 @@
       <c r="A90" s="12" t="n">
         <v>46312</v>
       </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>回归</t>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>全套</t>
+          <t>D27b</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
+          <t>D27 套回板位流出件合主线: 主控 pov_m90_pure_ul800_p1_b12_sb.bin a36365e9 (hclk +0.003 真余量约 +0.30, pclk200 +0.048 比现役 +0.006 宽), 桥 e60c e7289b13 (旧记 394cd71a 只差头部创建时间) / e60p8c bddcece3; 存 _work/d10_v1bit_out/ 与 gw5a_bridge/results/; 回板用 D27 套免 FPC63 飞线</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ~/full_*.log</t>
+          <t>dr1v90 d27_link/README.md</t>
         </is>
       </c>
     </row>
@@ -15813,22 +15903,22 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>修复</t>
+          <t>进展</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>V2-6</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
+          <t>2 期桥合主线: p2 core 24 链 UL12 解包, BSRAM 37/56 (一颗 GW5A-25 够), Gowin 0 违例余量 +0.018 ns CLS 84%; 主控→桥→24×2260 端到端逐像素 0 错 (E1-E4, 反例 4/4); 预存窗口 15.3 rps 时仅 ±0.5 µs (上行占片周期 97.5%), 回板按实测重扫 START; 待硬件: UL_CLK 第 87 对放 3.3V bank, ACK 片外 3×8 选 1, 48 扫表 0x04 推导值; 顺修 D27 verify S 基线</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 slice/SPEC.md §13.2</t>
+          <t>dr1v90 gw5a_bridge/p2/README.md</t>
         </is>
       </c>
     </row>
@@ -15838,22 +15928,22 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>长跑</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>全套</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
+          <t>最新主线 fdb63f4 全套 19 套: 15 过; v2_map G4 / v2_bridge S 为守护误报 (D27b 时序摘要) 已修 d4a4e3a; 🔴 d19 O4_fake / d20_smooth S2 真回归: 假转本地播放换网格率 = 1×转速 (半圈换未生效), 10-16 3cb39fc 时 d19 PASS → 疑 D20e --pl-gate, 已退回 D20e agent 查修</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/1016_wkend_24h</t>
+          <t>dr1v90 ~/full_*.log</t>
         </is>
       </c>
     </row>
@@ -15863,72 +15953,72 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
+          <t>本地播放半圈换回归修复合主线 86caee5 (复验 d19 16/0, d20_smooth, d20d, d20e V1-V5 全过): 根因 2cd422a 对齐放行 (--pl-gate) 对本地帧也生效, 本地 15 fps+margin 0.9 时 m=2 压成 1×转速; 改为只作用推流帧; 02 开机演示配置 (10 fps/20/1.0) 推算不受影响; voxslice 新 md5 63e7afea, 下次部署换</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1017_*.log</t>
+          <t>dr1v90 slice/SPEC.md §13.2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>长跑</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
+          <t>02 24 h 产品配置长跑 PASS 10/10 (主线 8eced5a, PLV=0 max-fps 20 margin 1.0): 停摆 0/死 0, 10 s 窗口完成率最低 100%, 最差小时未完成 0.0011%, 推流 29 段 rc 0 均 16.8 帧/s, 停推 32 次全 300 s 回本地, RSS 23.1→23.1 MB; 注: PC 侧 D 盘 EIO 致 soak.sh 末段退出 (板上照常跑满并自恢复, 日志手动取回判读), ping 只记前 46 次, push.txt 少 3 段</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22c.board.log</t>
+          <t>progress/soak_v0/1016_wkend_24h</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46312</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
+          <t>02/03 卡上 voxslice 换主线 86caee5 版 (63e7afea, 旧版留 .bak-0717), 重启验收: 03 6/6 PASS; 02 A5 首次 1243 帧/90 s (&lt;1260, 开机后 20 s 内推流) 其余全过, 随后连推 3 次 1351/1351/1349 帧 = 满 15 帧/s → 判为开机初期偶发</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>progress/v0_accept/accept_1017_*.log</t>
         </is>
       </c>
     </row>
@@ -15943,17 +16033,17 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
+          <t>上板故障演练 14/14 PASS (povnetd 1.2): 装后重启 88 s; 杀 sshd/mdns/povnetd 60/7/72 s; 杀 wpa ×3 12/32/22 s; 关网卡 ×3 22/32/34 s; 错 SSID→热点→自回 545 s; 看门狗复位 2 项 60/220 s 找回且记非正常结束。用户要求 '不插串口永远连得上' 达成; 合主线回归中</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board5.log</t>
+          <t>~/rv_d22c.board.log</t>
         </is>
       </c>
     </row>
@@ -15968,12 +16058,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
+          <t>不插串口永远连得上 合主线 (上板演练 14/14; 合并回归 D22/rotor_ops/D18/D13/live_push 全过, D13 补丁比较口径剔除 D22 块)。串口可永久拔</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -15986,24 +16076,24 @@
       <c r="A98" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
+          <t>上板 PASS: 假转 5→20→5 斜坡换档 2 次 + 强制轮换 6 次, 跨圈写 0, 超时 0, 对拍 2/0 与 12/0, 完成率 100%, 收尾回默认 0x20471019 (测试解析同 D19 修正)。合并分支 task/merge-d21 全回归 12 套进行中</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d21.board5.log</t>
         </is>
       </c>
     </row>
@@ -16011,24 +16101,24 @@
       <c r="A99" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
+          <t>每圈片数随转速换档合主线 (全回归 12 套通过; D18 V3 允许卡上默认 kit=D19 落后仓库 RTL=D21); 主线 voxslice 已修 sub01 隐患。下一步: V1 12-bit 位流按主线 (D19+D21+D8) 重综合</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_A fps_B</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16036,9 +16126,9 @@
       <c r="A100" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -16048,12 +16138,12 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
+          <t>内容帧率跟转速 voxlive --fps auto 合主线 d3f16f3 (默认不变; 主机空闲时离线复验 PASS, 之前失败为主机忙)。上板 A/B (583 rpm 固定 15 vs auto+板 20/1.0) 进行中</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_C</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16063,22 +16153,22 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>测量</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
+          <t>上板 A/B (假转 583 rpm, 无对拍, 逐帧): A 默认 (推 15 + 板 15/0.9) 14.85/s, 间隔 p50/p95 51.5/103 ms, 节拍偏差 p50/p95 23%/55%; B (推 auto + 板 max-fps 20 / margin 1.0) 19.14/s, 间隔 51.4/51.8 ms, 偏差 0%/1%, 最长 206 ms。B 明显更流畅; 测 C (转速取自板遥测) 后决定改开机默认</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20d-ackrps db4ec93</t>
+          <t>soak_runs/fps_A fps_B</t>
         </is>
       </c>
     </row>
@@ -16086,24 +16176,24 @@
       <c r="A102" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
+          <t>测 C: 不手填转速时 auto 拿不到转速 → 退回 15 fps (povstat UDP 在 WSL NAT 收不到; 且 V0 2047 PL 位流遥测本无转速)。开 D20d: 推流 TCP ACK 扩展回传转速 (新旧兼容) + 默认改 板 max-fps 20/margin 1.0、推流 auto; 同时开 D10 V1 12-bit 位流按主线重综合</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
+          <t>soak_runs/fps_C</t>
         </is>
       </c>
     </row>
@@ -16113,7 +16203,7 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -16123,12 +16213,12 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
+          <t>推流 ACK 扩展回传转速 (帧头 flags bit15 请求 → 板回 0x07+rps×100+max-fps+margin+半圈标志; 新旧三种组合逐字节兼容) + 默认 板 max-fps 20/margin 1.0、推流 --fps auto (不用手填): 离线假转 583 rpm 自动锁 19.49/s std 0.2 ms。复验 + 上板 D 组进行中</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/fps_D</t>
+          <t>dr1v90 task/d20d-ackrps db4ec93</t>
         </is>
       </c>
     </row>
@@ -16136,24 +16226,24 @@
       <c r="A104" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>D20d</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
+          <t>V1 主控 12-bit 位流按主线重综合 8 档时序全收住 (回板主用 ul800_p1_b12 md5 023e6582, 替换作废 df4f0bea); 修 D8 引入的 build.sh set -e 静默退出; 2 期 MAXMISS 系命令配错 (12-bit@800M 本就超片周期), 非回归; 回板步骤 BOARD_DAY.md。注: V1 线速 800M (派活单写 1.2G 是主会话笔误); 缺口: V1 真内容板端通路 (voxslice 只支持 2047 后端) 待立项</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/d10-v1bit 9a9acf8</t>
         </is>
       </c>
     </row>
@@ -16163,22 +16253,22 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
+          <t>上板 D 组 (不手填任何参数): 推流经 ACK 扩展自动拿到转速并锁 19.4 帧/s ✅; 但间隔 p95 103 ms (&gt;5% 帧翻倍), 不如手填转速的 B 组 (p95 51.8) —— 估计转速与实际微差导致周期性滑格, 需相位锁定 (跟板端 ACK 节奏) 作后续。离线复验 (指定 BASE) PASS, 合主线回归中</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>~/rv_deploy.board.log</t>
+          <t>soak_runs/fps_D</t>
         </is>
       </c>
     </row>
@@ -16193,12 +16283,12 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D20d</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
+          <t>ACK 回传转速 + 默认推流 auto / 板 20/1.0 合主线 (合并回归 7 套通过)。卡上部署尚未更新 (下次装卡带上); 后续: 相位锁定消 5% 滑格</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -16213,7 +16303,7 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>验收</t>
+          <t>部署</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -16223,12 +16313,12 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
+          <t>卡上部署更新到主线 1d23e50 (voxslice md5 ecdc246f = 主线, show_boot max-fps 20 / margin 1.0, QoS 0x0F, PL 0x20471019, D22 povreach); D19 上板假转扫点 PASS</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/</t>
+          <t>~/rv_deploy.board.log</t>
         </is>
       </c>
     </row>
@@ -16236,24 +16326,24 @@
       <c r="A108" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>开工</t>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>D20e/D23</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
+          <t>V1 主控位流按主线重综合合主线 (复验 5/5: 构建记录/联合仿真/上行回归/MAXMISS 说明); 回板步骤 d10_v1bit/BOARD_DAY.md</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16261,24 +16351,24 @@
       <c r="A109" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B109" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>验收</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
+          <t>用户重启板子后 V0 验收 6/6 PASS (不插串口): 按名字找回 / 守护进程齐 (voxslice povnetd povreach povmdns povstat) / 开机默认 PL+QoS 0x0F+位流 0x20471019 / WiFi -55 dBm ping 30 丢 0 / 推流 90 s 1339 帧=14.9 帧/s 对端关闭 / 推后 voxslice 不变。首跑遇 D 盘 EIO 中断后重跑; A5 判读正则修正</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>用户</t>
+          <t>progress/v0_accept/</t>
         </is>
       </c>
     </row>
@@ -16286,24 +16376,24 @@
       <c r="A110" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>开工</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D20e/D23</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
+          <t>D20e 推流相位锁定 (消 auto 模式 5% 滑格) + D23 V1 真内容板端通路 并行开工; 用户新提: 开机默认动画要有立方体动图 (待做)</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/d20e-phaselock task/d23-v1content</t>
         </is>
       </c>
     </row>
@@ -16311,24 +16401,24 @@
       <c r="A111" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B111" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>D20e</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
+          <t>用户: 开机动画就用现在这个 (geo_loop, 含线框立方体), 不换; D26 V2 位流构建放行, 主会话后台跑; 新板定名 DR1M90-03, 拷卡包 card_kit_dr1m90-03 待用户管理员运行 make_card.ps1</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>用户</t>
         </is>
       </c>
     </row>
@@ -16336,24 +16426,24 @@
       <c r="A112" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
+          <t>V1 显示后端 voxslice --disp 2260 合主线 a41d63b (独立复验 24/0, 合并后回归 d21/d23 过)</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>progress/v0_accept/accept_1016_d20e.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16368,12 +16458,12 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>KR7.3/D24</t>
+          <t>D20e</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
+          <t>推流相位锁定合主线 c80f5fb: 583 rpm 滑格 5.2%→0.19%, 900 rpm 22%→0.12% (p95 = 理想间隔); 代价 延迟 120→170-250 ms (--phaselock off 可回老行为)</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -16388,22 +16478,22 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>部署</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
+          <t>02 卡上 voxslice 换 D20e 版 (ba243d71, 旧版留 .bak-d20e), 重启后 V0 验收 6/6 PASS (推流 1326 帧/90 s, WiFi -44 dBm 丢 0)</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>D:\card03</t>
+          <t>progress/v0_accept/accept_1016_d20e.log</t>
         </is>
       </c>
     </row>
@@ -16418,12 +16508,12 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>D25</t>
+          <t>KR7.3/D24</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
+          <t>KR7.3 16 位计数回绕修正合主线 (存档无原始计数, 99.84% 无法重算; 38/57 转动行待核); D24 立方体候选合主线, 用户定开机保持 geo_loop</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -16436,9 +16526,9 @@
       <c r="A116" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -16448,12 +16538,12 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
+          <t>第二块板: 公司 DLP 拦 TF 卡文件写入 → WSL 做 512 MB 镜像 + host/flash_card_raw.ps1 块级写, 读回 PASS; 等上电按名字找</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\cap_COM29.log</t>
+          <t>D:\card03</t>
         </is>
       </c>
     </row>
@@ -16461,24 +16551,24 @@
       <c r="A117" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>回归</t>
+          <t>D25</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
+          <t>V1 换档合主线 90b1d79: 358/286/210 档 (阈值 11.6/14.6 rps, 回差), 各档最高转速桥余量 3.9/3.3/2.7%; 不改 RTL 不重出位流; 顺修 --local-always SIGTERM 挂死; 卡上 voxslice 仍 D20e 版 (V0 dump 逐字节同, 不急换)</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20d_ackrps d20c_fps</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -16486,24 +16576,24 @@
       <c r="A118" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
+          <t>用户改供电上电后: mDNS 查不到, 串口 COM29/COM30 (CH342) 140 s 无输出、回车无回显; 后台录串口 2 h + 寻板 3 h; 待用户回来断电重上电</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d12_latency/RESULTS.md</t>
+          <t>D:\card03\cap_COM29.log</t>
         </is>
       </c>
     </row>
@@ -16511,24 +16601,24 @@
       <c r="A119" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>回归</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
+          <t>d20d P2 / d20c F3 帧间隔 std 判据在机器高负载 (load 4-6, D25 全量 + D26 TD) 时偶发超门槛 (4.6/8.3 ms vs &lt;4), 空闲同代码 0.1 ms; 待空闲复测, 必要时改失败重测一次</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d9_e2e/</t>
+          <t>dr1v90 d20d_ackrps d20c_fps</t>
         </is>
       </c>
     </row>
@@ -16536,24 +16626,24 @@
       <c r="A120" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>硬件</t>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>DR1M90-03</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
+          <t>延迟复测合主线: 相位锁定 auto 保持, lock-lead 150→70 ms; 583 rpm 延迟 p50/p95/p99 133/138/155 ms (锁相关 126/127/196, 滑格 2.1%→0.14%); 900 rpm 122/206/276 ms 滑格 0.37%; 帧间隔 p95 = 理想</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>D:\card03\boot03.log</t>
+          <t>dr1v90 d12_latency/RESULTS.md</t>
         </is>
       </c>
     </row>
@@ -16568,17 +16658,17 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
+          <t>V1 端到端仿真合主线: 真内容主机→板端→主控 RTL→上行→桥→6×2260 模型, 逐像素 0 错; 反例 3/3; 358 档只跑回绕窗口 (整圈用 N=16), 只 12-bit/假角度</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
+          <t>dr1v90 d9_e2e/</t>
         </is>
       </c>
     </row>
@@ -16588,22 +16678,22 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>开工</t>
+          <t>硬件</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>DR1M90-03</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
+          <t>03 起来了: 控制台 COM30 (CH342-A); 冷上电 u-boot 报 Card did not respond to voltage select -110 停在 =&gt;, mmc rescan + boot 后正常; 登记 dr1m90-03 (10.10.21.10), V0 验收 6/6 PASS (WiFi -45 dBm, 推流 1351 帧/90 s) → D29 查根因</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
+          <t>D:\card03\boot03.log</t>
         </is>
       </c>
     </row>
@@ -16611,24 +16701,24 @@
       <c r="A123" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>方案</t>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
+          <t>V2 位流按主线重出合主线 c8e8294: 0 违例但余量 0.000 ns (旧 +0.001), 资源略降; D26 agent 遗留的卡死构建进程 (嵌套 flock) 占锁 2.5 h, 已按 PID 清掉</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d29_sdboot/PLAN.md</t>
+          <t>dr1v90 td_pov/pure_ul/results/p2_ul1200_b12_v3</t>
         </is>
       </c>
     </row>
@@ -16636,24 +16726,24 @@
       <c r="A124" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B124" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>开工</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
+          <t>用户: SoC↔桥通信全功能开工, 软件能做的都做, 周一看结果。开 D27 (SoC↔桥全功能, Opus) / D28 (V1 回板一键脚本) / D29 (冷启动认卡); 02 跑 24 h 产品配置长跑 (PLV=0 max-fps 20 margin 1.0, 主线 8eced5a)</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v1_bringup/</t>
+          <t>dr1v90 soak8h/runs/1016_wkend_24h</t>
         </is>
       </c>
     </row>
@@ -16663,22 +16753,22 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>修复</t>
+          <t>方案</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
+          <t>03 冷启动认卡: 热重启 13/13 无法复现, 最可能 u-boot sdhci 首次 mmc_init 间歇失败且 an_bootcmd 无重试; 方案 A 只改卡上 uboot.env 的 bootcmd (mmc rescan 重试 15 次, 其余 49 变量逐字节同, md5 dae13f64), u-boot 提示符手敲已验证; 等用户批准写卡 + 冷上电 20 次验收 (判据 20/20); 发现 03 未装 S00sdoff 钩子</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
+          <t>dr1v90 d29_sdboot/PLAN.md</t>
         </is>
       </c>
     </row>
@@ -16686,24 +16776,24 @@
       <c r="A126" s="12" t="n">
         <v>46311</v>
       </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>进展</t>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>V2-3</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
+          <t>V1 回板一键脚本合主线: bringup.sh S0 前置 → S9 恢复, 每步 CHECK + 失败原因/下一步; 演练 (假寄存器/qemu) 74 PASS, 12 种故障注入全命中; 待真板核: 位流加载/真线速误码/真画面/桥 UART 字符串</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 v2_map/DESIGN.md</t>
+          <t>dr1v90 v1_bringup/</t>
         </is>
       </c>
     </row>
@@ -16713,72 +16803,72 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>评估</t>
+          <t>修复</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>D30</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
+          <t>回归计时判据 (d20d P2 / d20c F3) 抗机器忙合主线: 稳健 std + 失败重测; load 17-31 下 5/5 PASS, 反例全检出</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 d31_v1odd/REPORT.md</t>
+          <t>dr1v90 d20c_fps/test_d30_judge.sh</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="12" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B128" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46311</v>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>进展</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>V2-3</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
+          <t>2 期 192×216 映射离线完成合主线 691a772 (复验 15/15): p2_192x216 profile, 605 档 == 生产表, v2_ref.py/disp_p2.c 与 2 期全链 tb 逐组对拍; 发现 2 期上行 (105.33 µs/片) 比 2260 更紧, 605/512 两档只到 1110 rpm → 建议 605/513/461; 主控缺列序→字槽序格式器 (方案已证); 9 项待硬件确认 (H1-H9); 待用户定档表</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>progress/soak_v0/report.md</t>
+          <t>dr1v90 v2_map/DESIGN.md</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="12" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>测量</t>
+          <t>评估</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>QoS</t>
+          <t>D31</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
+          <t>V1 偶数片数漏柱: 面 A 过转轴, 偶数后半圈与前半圈取样重合; 两面漏柱 358/286/210 = 124/458/1524 → 357/285/209 = 0/62/467; 只改档表不动 RTL, 桥余量略宽; 另: D25 阈值下 12 rps 落在 286 档; 待用户定</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>~/qos_runs</t>
+          <t>dr1v90 d31_v1odd/REPORT.md</t>
         </is>
       </c>
     </row>
@@ -16786,24 +16876,24 @@
       <c r="A130" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>测量</t>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>D16b</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
+          <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16b-tile 7936b7e</t>
+          <t>progress/soak_v0/report.md</t>
         </is>
       </c>
     </row>
@@ -16811,24 +16901,24 @@
       <c r="A131" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B131" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>QoS</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
+          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>~/qos_runs</t>
         </is>
       </c>
     </row>
@@ -16836,24 +16926,24 @@
       <c r="A132" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B132" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D16b</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
+          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>dr1v90 task/d16b-tile 7936b7e</t>
         </is>
       </c>
     </row>
@@ -16861,24 +16951,24 @@
       <c r="A133" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B133" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>V1/V2</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
+          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>budget/rpm_range_2026-10-15.md</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -16886,24 +16976,24 @@
       <c r="A134" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B134" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>KR7.3</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
+          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>progress/realspin_v0/</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -16911,24 +17001,24 @@
       <c r="A135" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B135" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>V1/V2</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
+          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>progress/realspin_v0/</t>
+          <t>budget/rpm_range_2026-10-15.md</t>
         </is>
       </c>
     </row>
@@ -16936,24 +17026,24 @@
       <c r="A136" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>KR7.3</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
+          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20-smooth 83a5fd7</t>
+          <t>progress/realspin_v0/</t>
         </is>
       </c>
     </row>
@@ -16961,24 +17051,24 @@
       <c r="A137" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B137" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
+          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 e215176</t>
+          <t>progress/realspin_v0/</t>
         </is>
       </c>
     </row>
@@ -16993,17 +17083,17 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
+          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d19-halfrev 1beafa6</t>
+          <t>dr1v90 task/d20-smooth 83a5fd7</t>
         </is>
       </c>
     </row>
@@ -17011,24 +17101,24 @@
       <c r="A139" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>D20b</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
+          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20b-sim 9081f62</t>
+          <t>dr1v90 e215176</t>
         </is>
       </c>
     </row>
@@ -17038,7 +17128,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -17048,12 +17138,12 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
+          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/merge-d19-d20 106364e</t>
+          <t>dr1v90 task/d19-halfrev 1beafa6</t>
         </is>
       </c>
     </row>
@@ -17061,24 +17151,24 @@
       <c r="A141" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B141" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>D19/D20</t>
+          <t>D20b</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
+          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>dr1v90 task/d20b-sim 9081f62</t>
         </is>
       </c>
     </row>
@@ -17088,22 +17178,22 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
+          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband adeba44</t>
+          <t>dr1v90 task/merge-d19-d20 106364e</t>
         </is>
       </c>
     </row>
@@ -17111,24 +17201,24 @@
       <c r="A143" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>D20/D22</t>
+          <t>D19/D20</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
+          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>~/realspin/tcp</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -17136,24 +17226,24 @@
       <c r="A144" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B144" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
+          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>用户 10-15</t>
+          <t>dr1v90 task/d21-nband adeba44</t>
         </is>
       </c>
     </row>
@@ -17163,22 +17253,22 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D20/D22</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
+          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach ee4a55c</t>
+          <t>~/realspin/tcp</t>
         </is>
       </c>
     </row>
@@ -17186,24 +17276,24 @@
       <c r="A146" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B146" s="5" t="inlineStr">
-        <is>
-          <t>交付</t>
+      <c r="B146" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
+          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d20c-fps 338eaaf</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -17213,22 +17303,22 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>复验</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>D20c</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
+          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d20c.v.log</t>
+          <t>dr1v90 task/d22-reach ee4a55c</t>
         </is>
       </c>
     </row>
@@ -17243,17 +17333,17 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
+          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d8-cosim 85dfe51</t>
+          <t>dr1v90 task/d20c-fps 338eaaf</t>
         </is>
       </c>
     </row>
@@ -17261,24 +17351,24 @@
       <c r="A149" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B149" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>复验</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
+          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 feature/lvds-b2b</t>
+          <t>~/rv_d20c.v.log</t>
         </is>
       </c>
     </row>
@@ -17288,22 +17378,22 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>测量</t>
+          <t>交付</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>D22/D20</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
+          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>soak_runs/netdiag_1015_1814</t>
+          <t>dr1v90 task/d8-cosim 85dfe51</t>
         </is>
       </c>
     </row>
@@ -17311,24 +17401,24 @@
       <c r="A151" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B151" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
+          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d21.board.log</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -17336,24 +17426,24 @@
       <c r="A152" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B152" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D22/D20</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
+          <t>1 h 产品配置 (无对拍) 推流诊断: 换帧 14.64/s 软件损失 2.4% ✅, 间隔 p99 124 ms ✅, 长停顿 3.7‰ ✅, 最长 495 ms ❌ (门槛 267); PC→板 ping 16781/0 丢; &gt;0.5 s ACK 停顿 46 min 内 4 次 (最长 0.78 s), 同刻 PC→网关 RTT 165-275 ms = PC 侧 WiFi 抖动。周期 3 s 卡顿消失 (确认系对拍)。余项: 0.5-0.8 s 偶发抖动 (播放缓冲 vs 延迟取舍 / PC 有线或专用路由)</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach</t>
+          <t>soak_runs/netdiag_1015_1814</t>
         </is>
       </c>
     </row>
@@ -17368,17 +17458,17 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
+          <t>换档位流 (REV 0x20471021) 上板起步即停摆 (档 0 未换档时写完 47 片后停, 换网格全超时), 仿真全过 → 硅上与仿真不同; D21b 开查根因。另: D21 上板收尾用 m90/up.sh 会让板子没 PL, 已重启回开机默认 (0x20471019 + QoS)</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach</t>
+          <t>~/rv_d21.board.log</t>
         </is>
       </c>
     </row>
@@ -17386,9 +17476,9 @@
       <c r="A154" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B154" s="5" t="inlineStr">
-        <is>
-          <t>验证</t>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -17398,12 +17488,12 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
+          <t>新克隆离线 O6 误 FAIL: hostapd/povreach 二进制 git 模式 644, WSL 本地盘克隆不可执行, qemu 静默拒绝 (板上 autorun 有 chmod, 不受影响); 已修 (git +x, verify chmod), 重跑后自动上板演练</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22.board2.log</t>
+          <t>dr1v90 task/d22-reach</t>
         </is>
       </c>
     </row>
@@ -17411,24 +17501,24 @@
       <c r="A155" s="12" t="n">
         <v>46310</v>
       </c>
-      <c r="B155" s="5" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B155" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
+          <t>首轮上板演练 9 项误 FAIL = 验收脚本 info() 把板上 board_d22.sh info 的非 0 退出码当失败 (内容正常), settle/wait_healthy 恒失败; 板子本身正常 (装好开机 healthy, povreach managed, 看门狗 armed)。已修, 单独重跑全套演练 (~80 min); 期间 D21 取证因同时上板被干扰, 待 D22 后单独跑</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>~/d21b_forensic.log</t>
+          <t>dr1v90 task/d22-reach</t>
         </is>
       </c>
     </row>
@@ -17438,7 +17528,7 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -17448,12 +17538,12 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
+          <t>第二轮上板演练 (单独): 杀 sshd/mdns/povnetd 27-72 s 自愈找回 ✅; 错 SSID → 兜底热点 → 自己回公司网 ✅ (但 23.5 min, 目标 ≤10); 杀 wpa/关网卡、装后重启: 板子恢复了但 mDNS 按名字 240 s 内找不回 ❌ (缓存 IP 可连); 看门狗复位发生但晚于测试判定、卡上未记非正常结束 ❌。交回 D22 agent 修 (mDNS 找回为主)</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach 0d1da09</t>
+          <t>~/rv_d22.board2.log</t>
         </is>
       </c>
     </row>
@@ -17463,22 +17553,22 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
+          <t>板上取证: 显示每圈取满 142 片, 但 s3rt_sys 旁听只认片号 0..47 → PL 每圈 48 触发后停摆; 不带档位 / 补 sub10 都一样 → RTL 旁听上限 (D21 改为按 FBO) 问题。交回 D21b 修 RTL; 板子已重启回默认 0x20471019</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>~/rv_d22b.board.log</t>
+          <t>~/d21b_forensic.log</t>
         </is>
       </c>
     </row>
@@ -17488,7 +17578,7 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>交付</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -17498,12 +17588,12 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
+          <t>按名字找不回的根因: povmdns 在地址回来/重关联时不重新发 IGMP 报告 (重复入组 EADDRINUSE 无报告), 企业 AP 只把组播转给报告过的站点 → mDNS 查询数分钟到不了板。修: 重关联/地址变化时退组再入组 + 宣告 (0/1/3/7/15/30 s) + 每 60 s 刷新; 看门狗读回实际超时并减半到 ≤60 s; 卡上记非正常结束。离线 10/10, 上板复验中</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d22-reach e438a12</t>
+          <t>dr1v90 task/d22-reach 0d1da09</t>
         </is>
       </c>
     </row>
@@ -17513,72 +17603,72 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>根因</t>
+          <t>验证</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
+          <t>第三轮上板演练 9/10: 装后重启 24 s 按名字找回 ✅ (上轮找不回); sshd/mdns/povnetd 杀掉 38-72 s ✅; 关网卡 191 s ✅; 错 SSID→热点→自动回 543 s ✅ (上轮 1411); 看门狗复位 reachkill 54 s / netdstop 213 s 且记非正常结束 ✅ (实际超时 32 s); 仅 kill wpa_supplicant 240 s 内未找回 ❌ (随后恢复), 单独重跑定位中</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d21-nband 084bba3</t>
+          <t>~/rv_d22b.board.log</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B160" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>povnetd 1.2: wpa 进程没了/卡死/接口 down 立即重连 (原来一律等 60 s, 且 60 s 后的重连反把已自愈的连接打断 → 73-240+ s 且不稳); 只丢包仍按 60 s 防误重连; 关键事件写卡 (复位后可查); verify wpakill/ifdown 各连跑 3 次、120 s 内按名字找回。离线 11/11, 上板全套复验中</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>dr1v90 task/d22-reach e438a12</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B161" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+        <v>46310</v>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>停摆根因不在 RTL: voxslice --pl 从不写显示 0x0C sub01 (bpp3), 重新加载位流后显示按 1-bit 片距 0x3000 取片, 旁听按 0x9000 片首只认 1/3 → 每圈 48 触发卡死。主线同有此隐患 (默认开机靠别的程序先写对)。修: pl_setup 先写 sub01; 仿真 +NOBPP3 复现与板上一致; 位流不变。离线 12/12, 排在 D22 后上板</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>dr1v90 task/d21-nband 084bba3</t>
         </is>
       </c>
     </row>
@@ -17586,24 +17676,24 @@
       <c r="A162" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B162" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -17611,24 +17701,24 @@
       <c r="A163" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B163" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B163" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -17636,24 +17726,24 @@
       <c r="A164" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B164" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -17668,17 +17758,17 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -17686,24 +17776,24 @@
       <c r="A166" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B166" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B166" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -17711,9 +17801,9 @@
       <c r="A167" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B167" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -17723,12 +17813,12 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -17736,24 +17826,24 @@
       <c r="A168" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B168" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B168" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -17761,24 +17851,24 @@
       <c r="A169" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B169" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17786,24 +17876,24 @@
       <c r="A170" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B170" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -17811,24 +17901,24 @@
       <c r="A171" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B171" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B171" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -17843,17 +17933,17 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -17861,24 +17951,24 @@
       <c r="A173" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B173" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -17886,24 +17976,24 @@
       <c r="A174" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B174" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -17918,12 +18008,12 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
@@ -17943,17 +18033,17 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -17961,24 +18051,24 @@
       <c r="A177" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B177" s="5" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B177" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -17993,17 +18083,17 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
@@ -18013,22 +18103,22 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>开始</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
@@ -18036,24 +18126,24 @@
       <c r="A180" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B180" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -18061,9 +18151,9 @@
       <c r="A181" s="12" t="n">
         <v>46309</v>
       </c>
-      <c r="B181" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -18073,62 +18163,62 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B182" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B182" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="12" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B183" s="7" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B183" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -18143,17 +18233,17 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -18161,24 +18251,24 @@
       <c r="A185" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B185" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -18188,7 +18278,7 @@
       </c>
       <c r="B186" s="7" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
@@ -18198,12 +18288,12 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -18211,24 +18301,24 @@
       <c r="A187" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B187" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -18243,17 +18333,17 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -18261,24 +18351,24 @@
       <c r="A189" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B189" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B189" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18286,24 +18376,24 @@
       <c r="A190" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B190" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -18311,9 +18401,9 @@
       <c r="A191" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B191" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -18323,12 +18413,12 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -18336,24 +18426,24 @@
       <c r="A192" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B192" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B192" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18361,19 +18451,19 @@
       <c r="A193" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B193" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B193" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
@@ -18393,17 +18483,17 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -18411,19 +18501,19 @@
       <c r="A195" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B195" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B195" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
@@ -18436,24 +18526,24 @@
       <c r="A196" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B196" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -18461,24 +18551,24 @@
       <c r="A197" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B197" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18493,12 +18583,12 @@
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
@@ -18511,24 +18601,24 @@
       <c r="A199" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B199" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B199" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -18536,9 +18626,9 @@
       <c r="A200" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B200" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B200" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -18548,7 +18638,7 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
@@ -18561,24 +18651,24 @@
       <c r="A201" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B201" s="7" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B201" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -18586,19 +18676,19 @@
       <c r="A202" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B202" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B202" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
@@ -18611,20 +18701,24 @@
       <c r="A203" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B203" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="inlineStr"/>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>复验通过</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -18632,20 +18726,24 @@
       <c r="A204" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B204" s="23" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="C204" s="4" t="inlineStr"/>
+      <c r="B204" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18661,12 +18759,12 @@
       <c r="C205" s="4" t="inlineStr"/>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -18674,24 +18772,20 @@
       <c r="A206" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B206" s="22" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C206" s="4" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="B206" s="23" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr"/>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -18704,19 +18798,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C207" s="4" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
+      <c r="C207" s="4" t="inlineStr"/>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -18731,12 +18821,12 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
@@ -18756,12 +18846,12 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
@@ -18781,12 +18871,12 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
@@ -18806,17 +18896,17 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -18824,19 +18914,19 @@
       <c r="A212" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B212" s="8" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B212" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
@@ -18849,18 +18939,68 @@
       <c r="A213" s="12" t="n">
         <v>46308</v>
       </c>
-      <c r="B213" s="23" t="inlineStr">
+      <c r="B213" s="22" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>dr1v90 49031f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B214" s="8" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B215" s="23" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C213" s="4" t="inlineStr"/>
-      <c r="D213" s="4" t="inlineStr">
+      <c r="C215" s="4" t="inlineStr"/>
+      <c r="D215" s="4" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E213" s="4" t="inlineStr">
+      <c r="E215" s="4" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -23603,7 +23743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23647,7 +23787,7 @@
         <v>46307</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>5</v>
@@ -23661,7 +23801,7 @@
         <v>46308</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>7</v>
@@ -23675,7 +23815,7 @@
         <v>46309</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>8</v>
@@ -23689,7 +23829,7 @@
         <v>46310</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>12</v>
@@ -23703,7 +23843,7 @@
         <v>46311</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>20</v>
@@ -23717,7 +23857,7 @@
         <v>46312</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>28</v>
@@ -23731,7 +23871,7 @@
         <v>46313</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>28</v>
@@ -23745,7 +23885,7 @@
         <v>46314</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>32</v>
@@ -23759,13 +23899,13 @@
         <v>46315</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -23773,10 +23913,10 @@
         <v>46316</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" s="5" t="n"/>
     </row>
@@ -23785,10 +23925,10 @@
         <v>46317</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" s="5" t="n"/>
     </row>
@@ -23797,10 +23937,10 @@
         <v>46318</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" s="5" t="n"/>
     </row>
@@ -23809,10 +23949,10 @@
         <v>46319</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D16" s="5" t="n"/>
     </row>
@@ -26240,6 +26380,82 @@
       <c r="H87" s="4" t="inlineStr">
         <is>
           <t>dr1v90 2af5f9f (voxslice 1.1 已上 02 板; 注入停顿后 0.13-0.22 s 恢复, auto p50 40-60 ms; 主会话复验 V1-V8 PASS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>D51</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>去 600 rpm 帧率台阶 (300-1200 rpm 帧率随转速连续)</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>1;5</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>dr1v90 合并 (voxslice 1.2 已上 02 板; 634 rpm 9.3→18.6, 1200 rpm 15.1→29.8; 复验 R1-R5 PASS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>D52</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>V2 主控 1.2G PRBS 误码位流 (到板 C3 可用)</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>2;4;7</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>2期</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F89" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>dr1v90 7affa17 (面 A, 0 违例, bin b7045592; comm_check v2 演练 86/0; 复验 13/0)</t>
         </is>
       </c>
     </row>
